--- a/Processes/SubjectLineBuilder/Stand-Alone/SubjectLineBuilder-Input.xlsx
+++ b/Processes/SubjectLineBuilder/Stand-Alone/SubjectLineBuilder-Input.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Subject Line Input'!$A$1:$AQ$501</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Subject Line Input'!$A$1:$AX$501</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -207,7 +207,7 @@
     </comment>
     <comment ref="I1" authorId="0" shapeId="0">
       <text>
-        <t>Required before starting.</t>
+        <t>Optional. Enter a facility or doctor name for the provider.</t>
       </text>
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
@@ -217,7 +217,7 @@
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Optional. Enter a facility or doctor name for the provider.</t>
+        <t>Required before starting.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -376,6 +376,41 @@
       </text>
     </comment>
     <comment ref="AQ1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Enter a facility or doctor name for the provider.</t>
+      </text>
+    </comment>
+    <comment ref="AR1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Enter a facility or doctor name for the provider.</t>
+      </text>
+    </comment>
+    <comment ref="AS1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Enter a facility or doctor name for the provider.</t>
+      </text>
+    </comment>
+    <comment ref="AT1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Enter a facility or doctor name for the provider.</t>
+      </text>
+    </comment>
+    <comment ref="AU1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Enter a facility or doctor name for the provider.</t>
+      </text>
+    </comment>
+    <comment ref="AV1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Enter a facility or doctor name for the provider.</t>
+      </text>
+    </comment>
+    <comment ref="AW1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Enter a facility or doctor name for the provider.</t>
+      </text>
+    </comment>
+    <comment ref="AX1" authorId="0" shapeId="0">
       <text>
         <t>Optional. Enter a facility or doctor name for the provider.</t>
       </text>
@@ -673,7 +708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ501"/>
+  <dimension ref="A1:AX501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -719,6 +754,13 @@
     <col width="25" customWidth="1" min="41" max="41"/>
     <col width="25" customWidth="1" min="42" max="42"/>
     <col width="25" customWidth="1" min="43" max="43"/>
+    <col width="25" customWidth="1" min="44" max="44"/>
+    <col width="25" customWidth="1" min="45" max="45"/>
+    <col width="25" customWidth="1" min="46" max="46"/>
+    <col width="25" customWidth="1" min="47" max="47"/>
+    <col width="25" customWidth="1" min="48" max="48"/>
+    <col width="25" customWidth="1" min="49" max="49"/>
+    <col width="25" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1">
@@ -744,195 +786,230 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>Claim - Date of injury</t>
+          <t>Claim - Line of insurance (e.g. Workers Comp)</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>Claim - Body part</t>
+          <t>Claim - Date of injury</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>Claim - Injury type</t>
+          <t>Claim - Body part</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
+          <t>Claim - Injury type</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
           <t>Claim - Injury cause</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Claimant - First name</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Claimant - Last name</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Claimant - Date of birth</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Claimant - Gender</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Claimant - Address line 1</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Claimant - Address line 2</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Claimant - City</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Claimant - State</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Claimant - ZIP</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Claimant - Phone</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>Provider - Facility name</t>
         </is>
       </c>
-      <c r="T1" s="2" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>Provider - Doctor first name</t>
         </is>
       </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>Provider - Doctor last name</t>
         </is>
       </c>
-      <c r="V1" s="2" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>Provider - Address</t>
         </is>
       </c>
-      <c r="W1" s="2" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t>Provider - City</t>
         </is>
       </c>
-      <c r="X1" s="2" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t>Provider - State</t>
         </is>
       </c>
-      <c r="Y1" s="2" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t>Provider - ZIP</t>
         </is>
       </c>
-      <c r="Z1" s="2" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t>Provider - Phone</t>
         </is>
       </c>
-      <c r="AA1" s="2" t="inlineStr">
+      <c r="AB1" s="2" t="inlineStr">
         <is>
           <t>Provider - Appointment date</t>
         </is>
       </c>
-      <c r="AB1" s="2" t="inlineStr">
+      <c r="AC1" s="2" t="inlineStr">
         <is>
           <t>Provider - Appointment time</t>
         </is>
       </c>
-      <c r="AC1" s="2" t="inlineStr">
+      <c r="AD1" s="2" t="inlineStr">
         <is>
           <t>Adjuster - First name</t>
         </is>
       </c>
-      <c r="AD1" s="2" t="inlineStr">
+      <c r="AE1" s="2" t="inlineStr">
         <is>
           <t>Adjuster - Last name</t>
         </is>
       </c>
-      <c r="AE1" s="2" t="inlineStr">
+      <c r="AF1" s="2" t="inlineStr">
         <is>
           <t>Adjuster - Email</t>
         </is>
       </c>
-      <c r="AF1" s="2" t="inlineStr">
+      <c r="AG1" s="2" t="inlineStr">
         <is>
           <t>Adjuster - Phone</t>
         </is>
       </c>
-      <c r="AG1" s="2" t="inlineStr">
+      <c r="AH1" s="2" t="inlineStr">
+        <is>
+          <t>Adjuster - Claims office number</t>
+        </is>
+      </c>
+      <c r="AI1" s="2" t="inlineStr">
+        <is>
+          <t>Adjuster - Address line 1</t>
+        </is>
+      </c>
+      <c r="AJ1" s="2" t="inlineStr">
+        <is>
+          <t>Adjuster - Address line 2</t>
+        </is>
+      </c>
+      <c r="AK1" s="2" t="inlineStr">
+        <is>
+          <t>Adjuster - City</t>
+        </is>
+      </c>
+      <c r="AL1" s="2" t="inlineStr">
+        <is>
+          <t>Adjuster - State</t>
+        </is>
+      </c>
+      <c r="AM1" s="2" t="inlineStr">
+        <is>
+          <t>Adjuster - ZIP</t>
+        </is>
+      </c>
+      <c r="AN1" s="2" t="inlineStr">
         <is>
           <t>Adjuster - Requested nurse</t>
         </is>
       </c>
-      <c r="AH1" s="2" t="inlineStr">
+      <c r="AO1" s="2" t="inlineStr">
         <is>
           <t>Adjuster - Referral source</t>
         </is>
       </c>
-      <c r="AI1" s="2" t="inlineStr">
+      <c r="AP1" s="2" t="inlineStr">
         <is>
           <t>Attorney - First name</t>
         </is>
       </c>
-      <c r="AJ1" s="2" t="inlineStr">
+      <c r="AQ1" s="2" t="inlineStr">
         <is>
           <t>Attorney - Last name</t>
         </is>
       </c>
-      <c r="AK1" s="2" t="inlineStr">
+      <c r="AR1" s="2" t="inlineStr">
         <is>
           <t>Attorney - Firm</t>
         </is>
       </c>
-      <c r="AL1" s="2" t="inlineStr">
+      <c r="AS1" s="2" t="inlineStr">
         <is>
           <t>Attorney - Phone</t>
         </is>
       </c>
-      <c r="AM1" s="2" t="inlineStr">
+      <c r="AT1" s="2" t="inlineStr">
         <is>
           <t>Attorney - Address line 1</t>
         </is>
       </c>
-      <c r="AN1" s="2" t="inlineStr">
+      <c r="AU1" s="2" t="inlineStr">
         <is>
           <t>Attorney - Address line 2</t>
         </is>
       </c>
-      <c r="AO1" s="2" t="inlineStr">
+      <c r="AV1" s="2" t="inlineStr">
         <is>
           <t>Attorney - City</t>
         </is>
       </c>
-      <c r="AP1" s="2" t="inlineStr">
+      <c r="AW1" s="2" t="inlineStr">
         <is>
           <t>Attorney - State</t>
         </is>
       </c>
-      <c r="AQ1" s="2" t="inlineStr">
+      <c r="AX1" s="2" t="inlineStr">
         <is>
           <t>Attorney - ZIP</t>
         </is>
@@ -982,6 +1059,13 @@
       <c r="AO2" s="3" t="n"/>
       <c r="AP2" s="3" t="n"/>
       <c r="AQ2" s="3" t="n"/>
+      <c r="AR2" s="3" t="n"/>
+      <c r="AS2" s="3" t="n"/>
+      <c r="AT2" s="3" t="n"/>
+      <c r="AU2" s="3" t="n"/>
+      <c r="AV2" s="3" t="n"/>
+      <c r="AW2" s="3" t="n"/>
+      <c r="AX2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n"/>
@@ -1027,6 +1111,13 @@
       <c r="AO3" s="3" t="n"/>
       <c r="AP3" s="3" t="n"/>
       <c r="AQ3" s="3" t="n"/>
+      <c r="AR3" s="3" t="n"/>
+      <c r="AS3" s="3" t="n"/>
+      <c r="AT3" s="3" t="n"/>
+      <c r="AU3" s="3" t="n"/>
+      <c r="AV3" s="3" t="n"/>
+      <c r="AW3" s="3" t="n"/>
+      <c r="AX3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n"/>
@@ -1072,6 +1163,13 @@
       <c r="AO4" s="3" t="n"/>
       <c r="AP4" s="3" t="n"/>
       <c r="AQ4" s="3" t="n"/>
+      <c r="AR4" s="3" t="n"/>
+      <c r="AS4" s="3" t="n"/>
+      <c r="AT4" s="3" t="n"/>
+      <c r="AU4" s="3" t="n"/>
+      <c r="AV4" s="3" t="n"/>
+      <c r="AW4" s="3" t="n"/>
+      <c r="AX4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
@@ -1117,6 +1215,13 @@
       <c r="AO5" s="3" t="n"/>
       <c r="AP5" s="3" t="n"/>
       <c r="AQ5" s="3" t="n"/>
+      <c r="AR5" s="3" t="n"/>
+      <c r="AS5" s="3" t="n"/>
+      <c r="AT5" s="3" t="n"/>
+      <c r="AU5" s="3" t="n"/>
+      <c r="AV5" s="3" t="n"/>
+      <c r="AW5" s="3" t="n"/>
+      <c r="AX5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n"/>
@@ -1162,6 +1267,13 @@
       <c r="AO6" s="3" t="n"/>
       <c r="AP6" s="3" t="n"/>
       <c r="AQ6" s="3" t="n"/>
+      <c r="AR6" s="3" t="n"/>
+      <c r="AS6" s="3" t="n"/>
+      <c r="AT6" s="3" t="n"/>
+      <c r="AU6" s="3" t="n"/>
+      <c r="AV6" s="3" t="n"/>
+      <c r="AW6" s="3" t="n"/>
+      <c r="AX6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n"/>
@@ -1207,6 +1319,13 @@
       <c r="AO7" s="3" t="n"/>
       <c r="AP7" s="3" t="n"/>
       <c r="AQ7" s="3" t="n"/>
+      <c r="AR7" s="3" t="n"/>
+      <c r="AS7" s="3" t="n"/>
+      <c r="AT7" s="3" t="n"/>
+      <c r="AU7" s="3" t="n"/>
+      <c r="AV7" s="3" t="n"/>
+      <c r="AW7" s="3" t="n"/>
+      <c r="AX7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
@@ -1252,6 +1371,13 @@
       <c r="AO8" s="3" t="n"/>
       <c r="AP8" s="3" t="n"/>
       <c r="AQ8" s="3" t="n"/>
+      <c r="AR8" s="3" t="n"/>
+      <c r="AS8" s="3" t="n"/>
+      <c r="AT8" s="3" t="n"/>
+      <c r="AU8" s="3" t="n"/>
+      <c r="AV8" s="3" t="n"/>
+      <c r="AW8" s="3" t="n"/>
+      <c r="AX8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n"/>
@@ -1297,6 +1423,13 @@
       <c r="AO9" s="3" t="n"/>
       <c r="AP9" s="3" t="n"/>
       <c r="AQ9" s="3" t="n"/>
+      <c r="AR9" s="3" t="n"/>
+      <c r="AS9" s="3" t="n"/>
+      <c r="AT9" s="3" t="n"/>
+      <c r="AU9" s="3" t="n"/>
+      <c r="AV9" s="3" t="n"/>
+      <c r="AW9" s="3" t="n"/>
+      <c r="AX9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n"/>
@@ -1342,6 +1475,13 @@
       <c r="AO10" s="3" t="n"/>
       <c r="AP10" s="3" t="n"/>
       <c r="AQ10" s="3" t="n"/>
+      <c r="AR10" s="3" t="n"/>
+      <c r="AS10" s="3" t="n"/>
+      <c r="AT10" s="3" t="n"/>
+      <c r="AU10" s="3" t="n"/>
+      <c r="AV10" s="3" t="n"/>
+      <c r="AW10" s="3" t="n"/>
+      <c r="AX10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
@@ -1387,6 +1527,13 @@
       <c r="AO11" s="3" t="n"/>
       <c r="AP11" s="3" t="n"/>
       <c r="AQ11" s="3" t="n"/>
+      <c r="AR11" s="3" t="n"/>
+      <c r="AS11" s="3" t="n"/>
+      <c r="AT11" s="3" t="n"/>
+      <c r="AU11" s="3" t="n"/>
+      <c r="AV11" s="3" t="n"/>
+      <c r="AW11" s="3" t="n"/>
+      <c r="AX11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n"/>
@@ -1432,6 +1579,13 @@
       <c r="AO12" s="3" t="n"/>
       <c r="AP12" s="3" t="n"/>
       <c r="AQ12" s="3" t="n"/>
+      <c r="AR12" s="3" t="n"/>
+      <c r="AS12" s="3" t="n"/>
+      <c r="AT12" s="3" t="n"/>
+      <c r="AU12" s="3" t="n"/>
+      <c r="AV12" s="3" t="n"/>
+      <c r="AW12" s="3" t="n"/>
+      <c r="AX12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n"/>
@@ -1477,6 +1631,13 @@
       <c r="AO13" s="3" t="n"/>
       <c r="AP13" s="3" t="n"/>
       <c r="AQ13" s="3" t="n"/>
+      <c r="AR13" s="3" t="n"/>
+      <c r="AS13" s="3" t="n"/>
+      <c r="AT13" s="3" t="n"/>
+      <c r="AU13" s="3" t="n"/>
+      <c r="AV13" s="3" t="n"/>
+      <c r="AW13" s="3" t="n"/>
+      <c r="AX13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n"/>
@@ -1522,6 +1683,13 @@
       <c r="AO14" s="3" t="n"/>
       <c r="AP14" s="3" t="n"/>
       <c r="AQ14" s="3" t="n"/>
+      <c r="AR14" s="3" t="n"/>
+      <c r="AS14" s="3" t="n"/>
+      <c r="AT14" s="3" t="n"/>
+      <c r="AU14" s="3" t="n"/>
+      <c r="AV14" s="3" t="n"/>
+      <c r="AW14" s="3" t="n"/>
+      <c r="AX14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n"/>
@@ -1567,6 +1735,13 @@
       <c r="AO15" s="3" t="n"/>
       <c r="AP15" s="3" t="n"/>
       <c r="AQ15" s="3" t="n"/>
+      <c r="AR15" s="3" t="n"/>
+      <c r="AS15" s="3" t="n"/>
+      <c r="AT15" s="3" t="n"/>
+      <c r="AU15" s="3" t="n"/>
+      <c r="AV15" s="3" t="n"/>
+      <c r="AW15" s="3" t="n"/>
+      <c r="AX15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n"/>
@@ -1612,6 +1787,13 @@
       <c r="AO16" s="3" t="n"/>
       <c r="AP16" s="3" t="n"/>
       <c r="AQ16" s="3" t="n"/>
+      <c r="AR16" s="3" t="n"/>
+      <c r="AS16" s="3" t="n"/>
+      <c r="AT16" s="3" t="n"/>
+      <c r="AU16" s="3" t="n"/>
+      <c r="AV16" s="3" t="n"/>
+      <c r="AW16" s="3" t="n"/>
+      <c r="AX16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n"/>
@@ -1657,6 +1839,13 @@
       <c r="AO17" s="3" t="n"/>
       <c r="AP17" s="3" t="n"/>
       <c r="AQ17" s="3" t="n"/>
+      <c r="AR17" s="3" t="n"/>
+      <c r="AS17" s="3" t="n"/>
+      <c r="AT17" s="3" t="n"/>
+      <c r="AU17" s="3" t="n"/>
+      <c r="AV17" s="3" t="n"/>
+      <c r="AW17" s="3" t="n"/>
+      <c r="AX17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n"/>
@@ -1702,6 +1891,13 @@
       <c r="AO18" s="3" t="n"/>
       <c r="AP18" s="3" t="n"/>
       <c r="AQ18" s="3" t="n"/>
+      <c r="AR18" s="3" t="n"/>
+      <c r="AS18" s="3" t="n"/>
+      <c r="AT18" s="3" t="n"/>
+      <c r="AU18" s="3" t="n"/>
+      <c r="AV18" s="3" t="n"/>
+      <c r="AW18" s="3" t="n"/>
+      <c r="AX18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n"/>
@@ -1747,6 +1943,13 @@
       <c r="AO19" s="3" t="n"/>
       <c r="AP19" s="3" t="n"/>
       <c r="AQ19" s="3" t="n"/>
+      <c r="AR19" s="3" t="n"/>
+      <c r="AS19" s="3" t="n"/>
+      <c r="AT19" s="3" t="n"/>
+      <c r="AU19" s="3" t="n"/>
+      <c r="AV19" s="3" t="n"/>
+      <c r="AW19" s="3" t="n"/>
+      <c r="AX19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n"/>
@@ -1792,6 +1995,13 @@
       <c r="AO20" s="3" t="n"/>
       <c r="AP20" s="3" t="n"/>
       <c r="AQ20" s="3" t="n"/>
+      <c r="AR20" s="3" t="n"/>
+      <c r="AS20" s="3" t="n"/>
+      <c r="AT20" s="3" t="n"/>
+      <c r="AU20" s="3" t="n"/>
+      <c r="AV20" s="3" t="n"/>
+      <c r="AW20" s="3" t="n"/>
+      <c r="AX20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n"/>
@@ -1837,6 +2047,13 @@
       <c r="AO21" s="3" t="n"/>
       <c r="AP21" s="3" t="n"/>
       <c r="AQ21" s="3" t="n"/>
+      <c r="AR21" s="3" t="n"/>
+      <c r="AS21" s="3" t="n"/>
+      <c r="AT21" s="3" t="n"/>
+      <c r="AU21" s="3" t="n"/>
+      <c r="AV21" s="3" t="n"/>
+      <c r="AW21" s="3" t="n"/>
+      <c r="AX21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n"/>
@@ -1882,6 +2099,13 @@
       <c r="AO22" s="3" t="n"/>
       <c r="AP22" s="3" t="n"/>
       <c r="AQ22" s="3" t="n"/>
+      <c r="AR22" s="3" t="n"/>
+      <c r="AS22" s="3" t="n"/>
+      <c r="AT22" s="3" t="n"/>
+      <c r="AU22" s="3" t="n"/>
+      <c r="AV22" s="3" t="n"/>
+      <c r="AW22" s="3" t="n"/>
+      <c r="AX22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n"/>
@@ -1927,6 +2151,13 @@
       <c r="AO23" s="3" t="n"/>
       <c r="AP23" s="3" t="n"/>
       <c r="AQ23" s="3" t="n"/>
+      <c r="AR23" s="3" t="n"/>
+      <c r="AS23" s="3" t="n"/>
+      <c r="AT23" s="3" t="n"/>
+      <c r="AU23" s="3" t="n"/>
+      <c r="AV23" s="3" t="n"/>
+      <c r="AW23" s="3" t="n"/>
+      <c r="AX23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n"/>
@@ -1972,6 +2203,13 @@
       <c r="AO24" s="3" t="n"/>
       <c r="AP24" s="3" t="n"/>
       <c r="AQ24" s="3" t="n"/>
+      <c r="AR24" s="3" t="n"/>
+      <c r="AS24" s="3" t="n"/>
+      <c r="AT24" s="3" t="n"/>
+      <c r="AU24" s="3" t="n"/>
+      <c r="AV24" s="3" t="n"/>
+      <c r="AW24" s="3" t="n"/>
+      <c r="AX24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n"/>
@@ -2017,6 +2255,13 @@
       <c r="AO25" s="3" t="n"/>
       <c r="AP25" s="3" t="n"/>
       <c r="AQ25" s="3" t="n"/>
+      <c r="AR25" s="3" t="n"/>
+      <c r="AS25" s="3" t="n"/>
+      <c r="AT25" s="3" t="n"/>
+      <c r="AU25" s="3" t="n"/>
+      <c r="AV25" s="3" t="n"/>
+      <c r="AW25" s="3" t="n"/>
+      <c r="AX25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n"/>
@@ -2062,6 +2307,13 @@
       <c r="AO26" s="3" t="n"/>
       <c r="AP26" s="3" t="n"/>
       <c r="AQ26" s="3" t="n"/>
+      <c r="AR26" s="3" t="n"/>
+      <c r="AS26" s="3" t="n"/>
+      <c r="AT26" s="3" t="n"/>
+      <c r="AU26" s="3" t="n"/>
+      <c r="AV26" s="3" t="n"/>
+      <c r="AW26" s="3" t="n"/>
+      <c r="AX26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n"/>
@@ -2107,6 +2359,13 @@
       <c r="AO27" s="3" t="n"/>
       <c r="AP27" s="3" t="n"/>
       <c r="AQ27" s="3" t="n"/>
+      <c r="AR27" s="3" t="n"/>
+      <c r="AS27" s="3" t="n"/>
+      <c r="AT27" s="3" t="n"/>
+      <c r="AU27" s="3" t="n"/>
+      <c r="AV27" s="3" t="n"/>
+      <c r="AW27" s="3" t="n"/>
+      <c r="AX27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n"/>
@@ -2152,6 +2411,13 @@
       <c r="AO28" s="3" t="n"/>
       <c r="AP28" s="3" t="n"/>
       <c r="AQ28" s="3" t="n"/>
+      <c r="AR28" s="3" t="n"/>
+      <c r="AS28" s="3" t="n"/>
+      <c r="AT28" s="3" t="n"/>
+      <c r="AU28" s="3" t="n"/>
+      <c r="AV28" s="3" t="n"/>
+      <c r="AW28" s="3" t="n"/>
+      <c r="AX28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n"/>
@@ -2197,6 +2463,13 @@
       <c r="AO29" s="3" t="n"/>
       <c r="AP29" s="3" t="n"/>
       <c r="AQ29" s="3" t="n"/>
+      <c r="AR29" s="3" t="n"/>
+      <c r="AS29" s="3" t="n"/>
+      <c r="AT29" s="3" t="n"/>
+      <c r="AU29" s="3" t="n"/>
+      <c r="AV29" s="3" t="n"/>
+      <c r="AW29" s="3" t="n"/>
+      <c r="AX29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n"/>
@@ -2242,6 +2515,13 @@
       <c r="AO30" s="3" t="n"/>
       <c r="AP30" s="3" t="n"/>
       <c r="AQ30" s="3" t="n"/>
+      <c r="AR30" s="3" t="n"/>
+      <c r="AS30" s="3" t="n"/>
+      <c r="AT30" s="3" t="n"/>
+      <c r="AU30" s="3" t="n"/>
+      <c r="AV30" s="3" t="n"/>
+      <c r="AW30" s="3" t="n"/>
+      <c r="AX30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n"/>
@@ -2287,6 +2567,13 @@
       <c r="AO31" s="3" t="n"/>
       <c r="AP31" s="3" t="n"/>
       <c r="AQ31" s="3" t="n"/>
+      <c r="AR31" s="3" t="n"/>
+      <c r="AS31" s="3" t="n"/>
+      <c r="AT31" s="3" t="n"/>
+      <c r="AU31" s="3" t="n"/>
+      <c r="AV31" s="3" t="n"/>
+      <c r="AW31" s="3" t="n"/>
+      <c r="AX31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n"/>
@@ -2332,6 +2619,13 @@
       <c r="AO32" s="3" t="n"/>
       <c r="AP32" s="3" t="n"/>
       <c r="AQ32" s="3" t="n"/>
+      <c r="AR32" s="3" t="n"/>
+      <c r="AS32" s="3" t="n"/>
+      <c r="AT32" s="3" t="n"/>
+      <c r="AU32" s="3" t="n"/>
+      <c r="AV32" s="3" t="n"/>
+      <c r="AW32" s="3" t="n"/>
+      <c r="AX32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n"/>
@@ -2377,6 +2671,13 @@
       <c r="AO33" s="3" t="n"/>
       <c r="AP33" s="3" t="n"/>
       <c r="AQ33" s="3" t="n"/>
+      <c r="AR33" s="3" t="n"/>
+      <c r="AS33" s="3" t="n"/>
+      <c r="AT33" s="3" t="n"/>
+      <c r="AU33" s="3" t="n"/>
+      <c r="AV33" s="3" t="n"/>
+      <c r="AW33" s="3" t="n"/>
+      <c r="AX33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n"/>
@@ -2422,6 +2723,13 @@
       <c r="AO34" s="3" t="n"/>
       <c r="AP34" s="3" t="n"/>
       <c r="AQ34" s="3" t="n"/>
+      <c r="AR34" s="3" t="n"/>
+      <c r="AS34" s="3" t="n"/>
+      <c r="AT34" s="3" t="n"/>
+      <c r="AU34" s="3" t="n"/>
+      <c r="AV34" s="3" t="n"/>
+      <c r="AW34" s="3" t="n"/>
+      <c r="AX34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n"/>
@@ -2467,6 +2775,13 @@
       <c r="AO35" s="3" t="n"/>
       <c r="AP35" s="3" t="n"/>
       <c r="AQ35" s="3" t="n"/>
+      <c r="AR35" s="3" t="n"/>
+      <c r="AS35" s="3" t="n"/>
+      <c r="AT35" s="3" t="n"/>
+      <c r="AU35" s="3" t="n"/>
+      <c r="AV35" s="3" t="n"/>
+      <c r="AW35" s="3" t="n"/>
+      <c r="AX35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n"/>
@@ -2512,6 +2827,13 @@
       <c r="AO36" s="3" t="n"/>
       <c r="AP36" s="3" t="n"/>
       <c r="AQ36" s="3" t="n"/>
+      <c r="AR36" s="3" t="n"/>
+      <c r="AS36" s="3" t="n"/>
+      <c r="AT36" s="3" t="n"/>
+      <c r="AU36" s="3" t="n"/>
+      <c r="AV36" s="3" t="n"/>
+      <c r="AW36" s="3" t="n"/>
+      <c r="AX36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n"/>
@@ -2557,6 +2879,13 @@
       <c r="AO37" s="3" t="n"/>
       <c r="AP37" s="3" t="n"/>
       <c r="AQ37" s="3" t="n"/>
+      <c r="AR37" s="3" t="n"/>
+      <c r="AS37" s="3" t="n"/>
+      <c r="AT37" s="3" t="n"/>
+      <c r="AU37" s="3" t="n"/>
+      <c r="AV37" s="3" t="n"/>
+      <c r="AW37" s="3" t="n"/>
+      <c r="AX37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n"/>
@@ -2602,6 +2931,13 @@
       <c r="AO38" s="3" t="n"/>
       <c r="AP38" s="3" t="n"/>
       <c r="AQ38" s="3" t="n"/>
+      <c r="AR38" s="3" t="n"/>
+      <c r="AS38" s="3" t="n"/>
+      <c r="AT38" s="3" t="n"/>
+      <c r="AU38" s="3" t="n"/>
+      <c r="AV38" s="3" t="n"/>
+      <c r="AW38" s="3" t="n"/>
+      <c r="AX38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n"/>
@@ -2647,6 +2983,13 @@
       <c r="AO39" s="3" t="n"/>
       <c r="AP39" s="3" t="n"/>
       <c r="AQ39" s="3" t="n"/>
+      <c r="AR39" s="3" t="n"/>
+      <c r="AS39" s="3" t="n"/>
+      <c r="AT39" s="3" t="n"/>
+      <c r="AU39" s="3" t="n"/>
+      <c r="AV39" s="3" t="n"/>
+      <c r="AW39" s="3" t="n"/>
+      <c r="AX39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n"/>
@@ -2692,6 +3035,13 @@
       <c r="AO40" s="3" t="n"/>
       <c r="AP40" s="3" t="n"/>
       <c r="AQ40" s="3" t="n"/>
+      <c r="AR40" s="3" t="n"/>
+      <c r="AS40" s="3" t="n"/>
+      <c r="AT40" s="3" t="n"/>
+      <c r="AU40" s="3" t="n"/>
+      <c r="AV40" s="3" t="n"/>
+      <c r="AW40" s="3" t="n"/>
+      <c r="AX40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n"/>
@@ -2737,6 +3087,13 @@
       <c r="AO41" s="3" t="n"/>
       <c r="AP41" s="3" t="n"/>
       <c r="AQ41" s="3" t="n"/>
+      <c r="AR41" s="3" t="n"/>
+      <c r="AS41" s="3" t="n"/>
+      <c r="AT41" s="3" t="n"/>
+      <c r="AU41" s="3" t="n"/>
+      <c r="AV41" s="3" t="n"/>
+      <c r="AW41" s="3" t="n"/>
+      <c r="AX41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n"/>
@@ -2782,6 +3139,13 @@
       <c r="AO42" s="3" t="n"/>
       <c r="AP42" s="3" t="n"/>
       <c r="AQ42" s="3" t="n"/>
+      <c r="AR42" s="3" t="n"/>
+      <c r="AS42" s="3" t="n"/>
+      <c r="AT42" s="3" t="n"/>
+      <c r="AU42" s="3" t="n"/>
+      <c r="AV42" s="3" t="n"/>
+      <c r="AW42" s="3" t="n"/>
+      <c r="AX42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n"/>
@@ -2827,6 +3191,13 @@
       <c r="AO43" s="3" t="n"/>
       <c r="AP43" s="3" t="n"/>
       <c r="AQ43" s="3" t="n"/>
+      <c r="AR43" s="3" t="n"/>
+      <c r="AS43" s="3" t="n"/>
+      <c r="AT43" s="3" t="n"/>
+      <c r="AU43" s="3" t="n"/>
+      <c r="AV43" s="3" t="n"/>
+      <c r="AW43" s="3" t="n"/>
+      <c r="AX43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n"/>
@@ -2872,6 +3243,13 @@
       <c r="AO44" s="3" t="n"/>
       <c r="AP44" s="3" t="n"/>
       <c r="AQ44" s="3" t="n"/>
+      <c r="AR44" s="3" t="n"/>
+      <c r="AS44" s="3" t="n"/>
+      <c r="AT44" s="3" t="n"/>
+      <c r="AU44" s="3" t="n"/>
+      <c r="AV44" s="3" t="n"/>
+      <c r="AW44" s="3" t="n"/>
+      <c r="AX44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n"/>
@@ -2917,6 +3295,13 @@
       <c r="AO45" s="3" t="n"/>
       <c r="AP45" s="3" t="n"/>
       <c r="AQ45" s="3" t="n"/>
+      <c r="AR45" s="3" t="n"/>
+      <c r="AS45" s="3" t="n"/>
+      <c r="AT45" s="3" t="n"/>
+      <c r="AU45" s="3" t="n"/>
+      <c r="AV45" s="3" t="n"/>
+      <c r="AW45" s="3" t="n"/>
+      <c r="AX45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n"/>
@@ -2962,6 +3347,13 @@
       <c r="AO46" s="3" t="n"/>
       <c r="AP46" s="3" t="n"/>
       <c r="AQ46" s="3" t="n"/>
+      <c r="AR46" s="3" t="n"/>
+      <c r="AS46" s="3" t="n"/>
+      <c r="AT46" s="3" t="n"/>
+      <c r="AU46" s="3" t="n"/>
+      <c r="AV46" s="3" t="n"/>
+      <c r="AW46" s="3" t="n"/>
+      <c r="AX46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n"/>
@@ -3007,6 +3399,13 @@
       <c r="AO47" s="3" t="n"/>
       <c r="AP47" s="3" t="n"/>
       <c r="AQ47" s="3" t="n"/>
+      <c r="AR47" s="3" t="n"/>
+      <c r="AS47" s="3" t="n"/>
+      <c r="AT47" s="3" t="n"/>
+      <c r="AU47" s="3" t="n"/>
+      <c r="AV47" s="3" t="n"/>
+      <c r="AW47" s="3" t="n"/>
+      <c r="AX47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n"/>
@@ -3052,6 +3451,13 @@
       <c r="AO48" s="3" t="n"/>
       <c r="AP48" s="3" t="n"/>
       <c r="AQ48" s="3" t="n"/>
+      <c r="AR48" s="3" t="n"/>
+      <c r="AS48" s="3" t="n"/>
+      <c r="AT48" s="3" t="n"/>
+      <c r="AU48" s="3" t="n"/>
+      <c r="AV48" s="3" t="n"/>
+      <c r="AW48" s="3" t="n"/>
+      <c r="AX48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n"/>
@@ -3097,6 +3503,13 @@
       <c r="AO49" s="3" t="n"/>
       <c r="AP49" s="3" t="n"/>
       <c r="AQ49" s="3" t="n"/>
+      <c r="AR49" s="3" t="n"/>
+      <c r="AS49" s="3" t="n"/>
+      <c r="AT49" s="3" t="n"/>
+      <c r="AU49" s="3" t="n"/>
+      <c r="AV49" s="3" t="n"/>
+      <c r="AW49" s="3" t="n"/>
+      <c r="AX49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n"/>
@@ -3142,6 +3555,13 @@
       <c r="AO50" s="3" t="n"/>
       <c r="AP50" s="3" t="n"/>
       <c r="AQ50" s="3" t="n"/>
+      <c r="AR50" s="3" t="n"/>
+      <c r="AS50" s="3" t="n"/>
+      <c r="AT50" s="3" t="n"/>
+      <c r="AU50" s="3" t="n"/>
+      <c r="AV50" s="3" t="n"/>
+      <c r="AW50" s="3" t="n"/>
+      <c r="AX50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n"/>
@@ -3187,6 +3607,13 @@
       <c r="AO51" s="3" t="n"/>
       <c r="AP51" s="3" t="n"/>
       <c r="AQ51" s="3" t="n"/>
+      <c r="AR51" s="3" t="n"/>
+      <c r="AS51" s="3" t="n"/>
+      <c r="AT51" s="3" t="n"/>
+      <c r="AU51" s="3" t="n"/>
+      <c r="AV51" s="3" t="n"/>
+      <c r="AW51" s="3" t="n"/>
+      <c r="AX51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n"/>
@@ -3232,6 +3659,13 @@
       <c r="AO52" s="3" t="n"/>
       <c r="AP52" s="3" t="n"/>
       <c r="AQ52" s="3" t="n"/>
+      <c r="AR52" s="3" t="n"/>
+      <c r="AS52" s="3" t="n"/>
+      <c r="AT52" s="3" t="n"/>
+      <c r="AU52" s="3" t="n"/>
+      <c r="AV52" s="3" t="n"/>
+      <c r="AW52" s="3" t="n"/>
+      <c r="AX52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n"/>
@@ -3277,6 +3711,13 @@
       <c r="AO53" s="3" t="n"/>
       <c r="AP53" s="3" t="n"/>
       <c r="AQ53" s="3" t="n"/>
+      <c r="AR53" s="3" t="n"/>
+      <c r="AS53" s="3" t="n"/>
+      <c r="AT53" s="3" t="n"/>
+      <c r="AU53" s="3" t="n"/>
+      <c r="AV53" s="3" t="n"/>
+      <c r="AW53" s="3" t="n"/>
+      <c r="AX53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n"/>
@@ -3322,6 +3763,13 @@
       <c r="AO54" s="3" t="n"/>
       <c r="AP54" s="3" t="n"/>
       <c r="AQ54" s="3" t="n"/>
+      <c r="AR54" s="3" t="n"/>
+      <c r="AS54" s="3" t="n"/>
+      <c r="AT54" s="3" t="n"/>
+      <c r="AU54" s="3" t="n"/>
+      <c r="AV54" s="3" t="n"/>
+      <c r="AW54" s="3" t="n"/>
+      <c r="AX54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n"/>
@@ -3367,6 +3815,13 @@
       <c r="AO55" s="3" t="n"/>
       <c r="AP55" s="3" t="n"/>
       <c r="AQ55" s="3" t="n"/>
+      <c r="AR55" s="3" t="n"/>
+      <c r="AS55" s="3" t="n"/>
+      <c r="AT55" s="3" t="n"/>
+      <c r="AU55" s="3" t="n"/>
+      <c r="AV55" s="3" t="n"/>
+      <c r="AW55" s="3" t="n"/>
+      <c r="AX55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n"/>
@@ -3412,6 +3867,13 @@
       <c r="AO56" s="3" t="n"/>
       <c r="AP56" s="3" t="n"/>
       <c r="AQ56" s="3" t="n"/>
+      <c r="AR56" s="3" t="n"/>
+      <c r="AS56" s="3" t="n"/>
+      <c r="AT56" s="3" t="n"/>
+      <c r="AU56" s="3" t="n"/>
+      <c r="AV56" s="3" t="n"/>
+      <c r="AW56" s="3" t="n"/>
+      <c r="AX56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n"/>
@@ -3457,6 +3919,13 @@
       <c r="AO57" s="3" t="n"/>
       <c r="AP57" s="3" t="n"/>
       <c r="AQ57" s="3" t="n"/>
+      <c r="AR57" s="3" t="n"/>
+      <c r="AS57" s="3" t="n"/>
+      <c r="AT57" s="3" t="n"/>
+      <c r="AU57" s="3" t="n"/>
+      <c r="AV57" s="3" t="n"/>
+      <c r="AW57" s="3" t="n"/>
+      <c r="AX57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n"/>
@@ -3502,6 +3971,13 @@
       <c r="AO58" s="3" t="n"/>
       <c r="AP58" s="3" t="n"/>
       <c r="AQ58" s="3" t="n"/>
+      <c r="AR58" s="3" t="n"/>
+      <c r="AS58" s="3" t="n"/>
+      <c r="AT58" s="3" t="n"/>
+      <c r="AU58" s="3" t="n"/>
+      <c r="AV58" s="3" t="n"/>
+      <c r="AW58" s="3" t="n"/>
+      <c r="AX58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n"/>
@@ -3547,6 +4023,13 @@
       <c r="AO59" s="3" t="n"/>
       <c r="AP59" s="3" t="n"/>
       <c r="AQ59" s="3" t="n"/>
+      <c r="AR59" s="3" t="n"/>
+      <c r="AS59" s="3" t="n"/>
+      <c r="AT59" s="3" t="n"/>
+      <c r="AU59" s="3" t="n"/>
+      <c r="AV59" s="3" t="n"/>
+      <c r="AW59" s="3" t="n"/>
+      <c r="AX59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n"/>
@@ -3592,6 +4075,13 @@
       <c r="AO60" s="3" t="n"/>
       <c r="AP60" s="3" t="n"/>
       <c r="AQ60" s="3" t="n"/>
+      <c r="AR60" s="3" t="n"/>
+      <c r="AS60" s="3" t="n"/>
+      <c r="AT60" s="3" t="n"/>
+      <c r="AU60" s="3" t="n"/>
+      <c r="AV60" s="3" t="n"/>
+      <c r="AW60" s="3" t="n"/>
+      <c r="AX60" s="3" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n"/>
@@ -3637,6 +4127,13 @@
       <c r="AO61" s="3" t="n"/>
       <c r="AP61" s="3" t="n"/>
       <c r="AQ61" s="3" t="n"/>
+      <c r="AR61" s="3" t="n"/>
+      <c r="AS61" s="3" t="n"/>
+      <c r="AT61" s="3" t="n"/>
+      <c r="AU61" s="3" t="n"/>
+      <c r="AV61" s="3" t="n"/>
+      <c r="AW61" s="3" t="n"/>
+      <c r="AX61" s="3" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n"/>
@@ -3682,6 +4179,13 @@
       <c r="AO62" s="3" t="n"/>
       <c r="AP62" s="3" t="n"/>
       <c r="AQ62" s="3" t="n"/>
+      <c r="AR62" s="3" t="n"/>
+      <c r="AS62" s="3" t="n"/>
+      <c r="AT62" s="3" t="n"/>
+      <c r="AU62" s="3" t="n"/>
+      <c r="AV62" s="3" t="n"/>
+      <c r="AW62" s="3" t="n"/>
+      <c r="AX62" s="3" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n"/>
@@ -3727,6 +4231,13 @@
       <c r="AO63" s="3" t="n"/>
       <c r="AP63" s="3" t="n"/>
       <c r="AQ63" s="3" t="n"/>
+      <c r="AR63" s="3" t="n"/>
+      <c r="AS63" s="3" t="n"/>
+      <c r="AT63" s="3" t="n"/>
+      <c r="AU63" s="3" t="n"/>
+      <c r="AV63" s="3" t="n"/>
+      <c r="AW63" s="3" t="n"/>
+      <c r="AX63" s="3" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n"/>
@@ -3772,6 +4283,13 @@
       <c r="AO64" s="3" t="n"/>
       <c r="AP64" s="3" t="n"/>
       <c r="AQ64" s="3" t="n"/>
+      <c r="AR64" s="3" t="n"/>
+      <c r="AS64" s="3" t="n"/>
+      <c r="AT64" s="3" t="n"/>
+      <c r="AU64" s="3" t="n"/>
+      <c r="AV64" s="3" t="n"/>
+      <c r="AW64" s="3" t="n"/>
+      <c r="AX64" s="3" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n"/>
@@ -3817,6 +4335,13 @@
       <c r="AO65" s="3" t="n"/>
       <c r="AP65" s="3" t="n"/>
       <c r="AQ65" s="3" t="n"/>
+      <c r="AR65" s="3" t="n"/>
+      <c r="AS65" s="3" t="n"/>
+      <c r="AT65" s="3" t="n"/>
+      <c r="AU65" s="3" t="n"/>
+      <c r="AV65" s="3" t="n"/>
+      <c r="AW65" s="3" t="n"/>
+      <c r="AX65" s="3" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n"/>
@@ -3862,6 +4387,13 @@
       <c r="AO66" s="3" t="n"/>
       <c r="AP66" s="3" t="n"/>
       <c r="AQ66" s="3" t="n"/>
+      <c r="AR66" s="3" t="n"/>
+      <c r="AS66" s="3" t="n"/>
+      <c r="AT66" s="3" t="n"/>
+      <c r="AU66" s="3" t="n"/>
+      <c r="AV66" s="3" t="n"/>
+      <c r="AW66" s="3" t="n"/>
+      <c r="AX66" s="3" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n"/>
@@ -3907,6 +4439,13 @@
       <c r="AO67" s="3" t="n"/>
       <c r="AP67" s="3" t="n"/>
       <c r="AQ67" s="3" t="n"/>
+      <c r="AR67" s="3" t="n"/>
+      <c r="AS67" s="3" t="n"/>
+      <c r="AT67" s="3" t="n"/>
+      <c r="AU67" s="3" t="n"/>
+      <c r="AV67" s="3" t="n"/>
+      <c r="AW67" s="3" t="n"/>
+      <c r="AX67" s="3" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n"/>
@@ -3952,6 +4491,13 @@
       <c r="AO68" s="3" t="n"/>
       <c r="AP68" s="3" t="n"/>
       <c r="AQ68" s="3" t="n"/>
+      <c r="AR68" s="3" t="n"/>
+      <c r="AS68" s="3" t="n"/>
+      <c r="AT68" s="3" t="n"/>
+      <c r="AU68" s="3" t="n"/>
+      <c r="AV68" s="3" t="n"/>
+      <c r="AW68" s="3" t="n"/>
+      <c r="AX68" s="3" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n"/>
@@ -3997,6 +4543,13 @@
       <c r="AO69" s="3" t="n"/>
       <c r="AP69" s="3" t="n"/>
       <c r="AQ69" s="3" t="n"/>
+      <c r="AR69" s="3" t="n"/>
+      <c r="AS69" s="3" t="n"/>
+      <c r="AT69" s="3" t="n"/>
+      <c r="AU69" s="3" t="n"/>
+      <c r="AV69" s="3" t="n"/>
+      <c r="AW69" s="3" t="n"/>
+      <c r="AX69" s="3" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n"/>
@@ -4042,6 +4595,13 @@
       <c r="AO70" s="3" t="n"/>
       <c r="AP70" s="3" t="n"/>
       <c r="AQ70" s="3" t="n"/>
+      <c r="AR70" s="3" t="n"/>
+      <c r="AS70" s="3" t="n"/>
+      <c r="AT70" s="3" t="n"/>
+      <c r="AU70" s="3" t="n"/>
+      <c r="AV70" s="3" t="n"/>
+      <c r="AW70" s="3" t="n"/>
+      <c r="AX70" s="3" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n"/>
@@ -4087,6 +4647,13 @@
       <c r="AO71" s="3" t="n"/>
       <c r="AP71" s="3" t="n"/>
       <c r="AQ71" s="3" t="n"/>
+      <c r="AR71" s="3" t="n"/>
+      <c r="AS71" s="3" t="n"/>
+      <c r="AT71" s="3" t="n"/>
+      <c r="AU71" s="3" t="n"/>
+      <c r="AV71" s="3" t="n"/>
+      <c r="AW71" s="3" t="n"/>
+      <c r="AX71" s="3" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n"/>
@@ -4132,6 +4699,13 @@
       <c r="AO72" s="3" t="n"/>
       <c r="AP72" s="3" t="n"/>
       <c r="AQ72" s="3" t="n"/>
+      <c r="AR72" s="3" t="n"/>
+      <c r="AS72" s="3" t="n"/>
+      <c r="AT72" s="3" t="n"/>
+      <c r="AU72" s="3" t="n"/>
+      <c r="AV72" s="3" t="n"/>
+      <c r="AW72" s="3" t="n"/>
+      <c r="AX72" s="3" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n"/>
@@ -4177,6 +4751,13 @@
       <c r="AO73" s="3" t="n"/>
       <c r="AP73" s="3" t="n"/>
       <c r="AQ73" s="3" t="n"/>
+      <c r="AR73" s="3" t="n"/>
+      <c r="AS73" s="3" t="n"/>
+      <c r="AT73" s="3" t="n"/>
+      <c r="AU73" s="3" t="n"/>
+      <c r="AV73" s="3" t="n"/>
+      <c r="AW73" s="3" t="n"/>
+      <c r="AX73" s="3" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n"/>
@@ -4222,6 +4803,13 @@
       <c r="AO74" s="3" t="n"/>
       <c r="AP74" s="3" t="n"/>
       <c r="AQ74" s="3" t="n"/>
+      <c r="AR74" s="3" t="n"/>
+      <c r="AS74" s="3" t="n"/>
+      <c r="AT74" s="3" t="n"/>
+      <c r="AU74" s="3" t="n"/>
+      <c r="AV74" s="3" t="n"/>
+      <c r="AW74" s="3" t="n"/>
+      <c r="AX74" s="3" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n"/>
@@ -4267,6 +4855,13 @@
       <c r="AO75" s="3" t="n"/>
       <c r="AP75" s="3" t="n"/>
       <c r="AQ75" s="3" t="n"/>
+      <c r="AR75" s="3" t="n"/>
+      <c r="AS75" s="3" t="n"/>
+      <c r="AT75" s="3" t="n"/>
+      <c r="AU75" s="3" t="n"/>
+      <c r="AV75" s="3" t="n"/>
+      <c r="AW75" s="3" t="n"/>
+      <c r="AX75" s="3" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n"/>
@@ -4312,6 +4907,13 @@
       <c r="AO76" s="3" t="n"/>
       <c r="AP76" s="3" t="n"/>
       <c r="AQ76" s="3" t="n"/>
+      <c r="AR76" s="3" t="n"/>
+      <c r="AS76" s="3" t="n"/>
+      <c r="AT76" s="3" t="n"/>
+      <c r="AU76" s="3" t="n"/>
+      <c r="AV76" s="3" t="n"/>
+      <c r="AW76" s="3" t="n"/>
+      <c r="AX76" s="3" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n"/>
@@ -4357,6 +4959,13 @@
       <c r="AO77" s="3" t="n"/>
       <c r="AP77" s="3" t="n"/>
       <c r="AQ77" s="3" t="n"/>
+      <c r="AR77" s="3" t="n"/>
+      <c r="AS77" s="3" t="n"/>
+      <c r="AT77" s="3" t="n"/>
+      <c r="AU77" s="3" t="n"/>
+      <c r="AV77" s="3" t="n"/>
+      <c r="AW77" s="3" t="n"/>
+      <c r="AX77" s="3" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n"/>
@@ -4402,6 +5011,13 @@
       <c r="AO78" s="3" t="n"/>
       <c r="AP78" s="3" t="n"/>
       <c r="AQ78" s="3" t="n"/>
+      <c r="AR78" s="3" t="n"/>
+      <c r="AS78" s="3" t="n"/>
+      <c r="AT78" s="3" t="n"/>
+      <c r="AU78" s="3" t="n"/>
+      <c r="AV78" s="3" t="n"/>
+      <c r="AW78" s="3" t="n"/>
+      <c r="AX78" s="3" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n"/>
@@ -4447,6 +5063,13 @@
       <c r="AO79" s="3" t="n"/>
       <c r="AP79" s="3" t="n"/>
       <c r="AQ79" s="3" t="n"/>
+      <c r="AR79" s="3" t="n"/>
+      <c r="AS79" s="3" t="n"/>
+      <c r="AT79" s="3" t="n"/>
+      <c r="AU79" s="3" t="n"/>
+      <c r="AV79" s="3" t="n"/>
+      <c r="AW79" s="3" t="n"/>
+      <c r="AX79" s="3" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n"/>
@@ -4492,6 +5115,13 @@
       <c r="AO80" s="3" t="n"/>
       <c r="AP80" s="3" t="n"/>
       <c r="AQ80" s="3" t="n"/>
+      <c r="AR80" s="3" t="n"/>
+      <c r="AS80" s="3" t="n"/>
+      <c r="AT80" s="3" t="n"/>
+      <c r="AU80" s="3" t="n"/>
+      <c r="AV80" s="3" t="n"/>
+      <c r="AW80" s="3" t="n"/>
+      <c r="AX80" s="3" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n"/>
@@ -4537,6 +5167,13 @@
       <c r="AO81" s="3" t="n"/>
       <c r="AP81" s="3" t="n"/>
       <c r="AQ81" s="3" t="n"/>
+      <c r="AR81" s="3" t="n"/>
+      <c r="AS81" s="3" t="n"/>
+      <c r="AT81" s="3" t="n"/>
+      <c r="AU81" s="3" t="n"/>
+      <c r="AV81" s="3" t="n"/>
+      <c r="AW81" s="3" t="n"/>
+      <c r="AX81" s="3" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n"/>
@@ -4582,6 +5219,13 @@
       <c r="AO82" s="3" t="n"/>
       <c r="AP82" s="3" t="n"/>
       <c r="AQ82" s="3" t="n"/>
+      <c r="AR82" s="3" t="n"/>
+      <c r="AS82" s="3" t="n"/>
+      <c r="AT82" s="3" t="n"/>
+      <c r="AU82" s="3" t="n"/>
+      <c r="AV82" s="3" t="n"/>
+      <c r="AW82" s="3" t="n"/>
+      <c r="AX82" s="3" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n"/>
@@ -4627,6 +5271,13 @@
       <c r="AO83" s="3" t="n"/>
       <c r="AP83" s="3" t="n"/>
       <c r="AQ83" s="3" t="n"/>
+      <c r="AR83" s="3" t="n"/>
+      <c r="AS83" s="3" t="n"/>
+      <c r="AT83" s="3" t="n"/>
+      <c r="AU83" s="3" t="n"/>
+      <c r="AV83" s="3" t="n"/>
+      <c r="AW83" s="3" t="n"/>
+      <c r="AX83" s="3" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n"/>
@@ -4672,6 +5323,13 @@
       <c r="AO84" s="3" t="n"/>
       <c r="AP84" s="3" t="n"/>
       <c r="AQ84" s="3" t="n"/>
+      <c r="AR84" s="3" t="n"/>
+      <c r="AS84" s="3" t="n"/>
+      <c r="AT84" s="3" t="n"/>
+      <c r="AU84" s="3" t="n"/>
+      <c r="AV84" s="3" t="n"/>
+      <c r="AW84" s="3" t="n"/>
+      <c r="AX84" s="3" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n"/>
@@ -4717,6 +5375,13 @@
       <c r="AO85" s="3" t="n"/>
       <c r="AP85" s="3" t="n"/>
       <c r="AQ85" s="3" t="n"/>
+      <c r="AR85" s="3" t="n"/>
+      <c r="AS85" s="3" t="n"/>
+      <c r="AT85" s="3" t="n"/>
+      <c r="AU85" s="3" t="n"/>
+      <c r="AV85" s="3" t="n"/>
+      <c r="AW85" s="3" t="n"/>
+      <c r="AX85" s="3" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n"/>
@@ -4762,6 +5427,13 @@
       <c r="AO86" s="3" t="n"/>
       <c r="AP86" s="3" t="n"/>
       <c r="AQ86" s="3" t="n"/>
+      <c r="AR86" s="3" t="n"/>
+      <c r="AS86" s="3" t="n"/>
+      <c r="AT86" s="3" t="n"/>
+      <c r="AU86" s="3" t="n"/>
+      <c r="AV86" s="3" t="n"/>
+      <c r="AW86" s="3" t="n"/>
+      <c r="AX86" s="3" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n"/>
@@ -4807,6 +5479,13 @@
       <c r="AO87" s="3" t="n"/>
       <c r="AP87" s="3" t="n"/>
       <c r="AQ87" s="3" t="n"/>
+      <c r="AR87" s="3" t="n"/>
+      <c r="AS87" s="3" t="n"/>
+      <c r="AT87" s="3" t="n"/>
+      <c r="AU87" s="3" t="n"/>
+      <c r="AV87" s="3" t="n"/>
+      <c r="AW87" s="3" t="n"/>
+      <c r="AX87" s="3" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n"/>
@@ -4852,6 +5531,13 @@
       <c r="AO88" s="3" t="n"/>
       <c r="AP88" s="3" t="n"/>
       <c r="AQ88" s="3" t="n"/>
+      <c r="AR88" s="3" t="n"/>
+      <c r="AS88" s="3" t="n"/>
+      <c r="AT88" s="3" t="n"/>
+      <c r="AU88" s="3" t="n"/>
+      <c r="AV88" s="3" t="n"/>
+      <c r="AW88" s="3" t="n"/>
+      <c r="AX88" s="3" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n"/>
@@ -4897,6 +5583,13 @@
       <c r="AO89" s="3" t="n"/>
       <c r="AP89" s="3" t="n"/>
       <c r="AQ89" s="3" t="n"/>
+      <c r="AR89" s="3" t="n"/>
+      <c r="AS89" s="3" t="n"/>
+      <c r="AT89" s="3" t="n"/>
+      <c r="AU89" s="3" t="n"/>
+      <c r="AV89" s="3" t="n"/>
+      <c r="AW89" s="3" t="n"/>
+      <c r="AX89" s="3" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n"/>
@@ -4942,6 +5635,13 @@
       <c r="AO90" s="3" t="n"/>
       <c r="AP90" s="3" t="n"/>
       <c r="AQ90" s="3" t="n"/>
+      <c r="AR90" s="3" t="n"/>
+      <c r="AS90" s="3" t="n"/>
+      <c r="AT90" s="3" t="n"/>
+      <c r="AU90" s="3" t="n"/>
+      <c r="AV90" s="3" t="n"/>
+      <c r="AW90" s="3" t="n"/>
+      <c r="AX90" s="3" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n"/>
@@ -4987,6 +5687,13 @@
       <c r="AO91" s="3" t="n"/>
       <c r="AP91" s="3" t="n"/>
       <c r="AQ91" s="3" t="n"/>
+      <c r="AR91" s="3" t="n"/>
+      <c r="AS91" s="3" t="n"/>
+      <c r="AT91" s="3" t="n"/>
+      <c r="AU91" s="3" t="n"/>
+      <c r="AV91" s="3" t="n"/>
+      <c r="AW91" s="3" t="n"/>
+      <c r="AX91" s="3" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n"/>
@@ -5032,6 +5739,13 @@
       <c r="AO92" s="3" t="n"/>
       <c r="AP92" s="3" t="n"/>
       <c r="AQ92" s="3" t="n"/>
+      <c r="AR92" s="3" t="n"/>
+      <c r="AS92" s="3" t="n"/>
+      <c r="AT92" s="3" t="n"/>
+      <c r="AU92" s="3" t="n"/>
+      <c r="AV92" s="3" t="n"/>
+      <c r="AW92" s="3" t="n"/>
+      <c r="AX92" s="3" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n"/>
@@ -5077,6 +5791,13 @@
       <c r="AO93" s="3" t="n"/>
       <c r="AP93" s="3" t="n"/>
       <c r="AQ93" s="3" t="n"/>
+      <c r="AR93" s="3" t="n"/>
+      <c r="AS93" s="3" t="n"/>
+      <c r="AT93" s="3" t="n"/>
+      <c r="AU93" s="3" t="n"/>
+      <c r="AV93" s="3" t="n"/>
+      <c r="AW93" s="3" t="n"/>
+      <c r="AX93" s="3" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n"/>
@@ -5122,6 +5843,13 @@
       <c r="AO94" s="3" t="n"/>
       <c r="AP94" s="3" t="n"/>
       <c r="AQ94" s="3" t="n"/>
+      <c r="AR94" s="3" t="n"/>
+      <c r="AS94" s="3" t="n"/>
+      <c r="AT94" s="3" t="n"/>
+      <c r="AU94" s="3" t="n"/>
+      <c r="AV94" s="3" t="n"/>
+      <c r="AW94" s="3" t="n"/>
+      <c r="AX94" s="3" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n"/>
@@ -5167,6 +5895,13 @@
       <c r="AO95" s="3" t="n"/>
       <c r="AP95" s="3" t="n"/>
       <c r="AQ95" s="3" t="n"/>
+      <c r="AR95" s="3" t="n"/>
+      <c r="AS95" s="3" t="n"/>
+      <c r="AT95" s="3" t="n"/>
+      <c r="AU95" s="3" t="n"/>
+      <c r="AV95" s="3" t="n"/>
+      <c r="AW95" s="3" t="n"/>
+      <c r="AX95" s="3" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n"/>
@@ -5212,6 +5947,13 @@
       <c r="AO96" s="3" t="n"/>
       <c r="AP96" s="3" t="n"/>
       <c r="AQ96" s="3" t="n"/>
+      <c r="AR96" s="3" t="n"/>
+      <c r="AS96" s="3" t="n"/>
+      <c r="AT96" s="3" t="n"/>
+      <c r="AU96" s="3" t="n"/>
+      <c r="AV96" s="3" t="n"/>
+      <c r="AW96" s="3" t="n"/>
+      <c r="AX96" s="3" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n"/>
@@ -5257,6 +5999,13 @@
       <c r="AO97" s="3" t="n"/>
       <c r="AP97" s="3" t="n"/>
       <c r="AQ97" s="3" t="n"/>
+      <c r="AR97" s="3" t="n"/>
+      <c r="AS97" s="3" t="n"/>
+      <c r="AT97" s="3" t="n"/>
+      <c r="AU97" s="3" t="n"/>
+      <c r="AV97" s="3" t="n"/>
+      <c r="AW97" s="3" t="n"/>
+      <c r="AX97" s="3" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n"/>
@@ -5302,6 +6051,13 @@
       <c r="AO98" s="3" t="n"/>
       <c r="AP98" s="3" t="n"/>
       <c r="AQ98" s="3" t="n"/>
+      <c r="AR98" s="3" t="n"/>
+      <c r="AS98" s="3" t="n"/>
+      <c r="AT98" s="3" t="n"/>
+      <c r="AU98" s="3" t="n"/>
+      <c r="AV98" s="3" t="n"/>
+      <c r="AW98" s="3" t="n"/>
+      <c r="AX98" s="3" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n"/>
@@ -5347,6 +6103,13 @@
       <c r="AO99" s="3" t="n"/>
       <c r="AP99" s="3" t="n"/>
       <c r="AQ99" s="3" t="n"/>
+      <c r="AR99" s="3" t="n"/>
+      <c r="AS99" s="3" t="n"/>
+      <c r="AT99" s="3" t="n"/>
+      <c r="AU99" s="3" t="n"/>
+      <c r="AV99" s="3" t="n"/>
+      <c r="AW99" s="3" t="n"/>
+      <c r="AX99" s="3" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n"/>
@@ -5392,6 +6155,13 @@
       <c r="AO100" s="3" t="n"/>
       <c r="AP100" s="3" t="n"/>
       <c r="AQ100" s="3" t="n"/>
+      <c r="AR100" s="3" t="n"/>
+      <c r="AS100" s="3" t="n"/>
+      <c r="AT100" s="3" t="n"/>
+      <c r="AU100" s="3" t="n"/>
+      <c r="AV100" s="3" t="n"/>
+      <c r="AW100" s="3" t="n"/>
+      <c r="AX100" s="3" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n"/>
@@ -5437,6 +6207,13 @@
       <c r="AO101" s="3" t="n"/>
       <c r="AP101" s="3" t="n"/>
       <c r="AQ101" s="3" t="n"/>
+      <c r="AR101" s="3" t="n"/>
+      <c r="AS101" s="3" t="n"/>
+      <c r="AT101" s="3" t="n"/>
+      <c r="AU101" s="3" t="n"/>
+      <c r="AV101" s="3" t="n"/>
+      <c r="AW101" s="3" t="n"/>
+      <c r="AX101" s="3" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n"/>
@@ -5482,6 +6259,13 @@
       <c r="AO102" s="3" t="n"/>
       <c r="AP102" s="3" t="n"/>
       <c r="AQ102" s="3" t="n"/>
+      <c r="AR102" s="3" t="n"/>
+      <c r="AS102" s="3" t="n"/>
+      <c r="AT102" s="3" t="n"/>
+      <c r="AU102" s="3" t="n"/>
+      <c r="AV102" s="3" t="n"/>
+      <c r="AW102" s="3" t="n"/>
+      <c r="AX102" s="3" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n"/>
@@ -5527,6 +6311,13 @@
       <c r="AO103" s="3" t="n"/>
       <c r="AP103" s="3" t="n"/>
       <c r="AQ103" s="3" t="n"/>
+      <c r="AR103" s="3" t="n"/>
+      <c r="AS103" s="3" t="n"/>
+      <c r="AT103" s="3" t="n"/>
+      <c r="AU103" s="3" t="n"/>
+      <c r="AV103" s="3" t="n"/>
+      <c r="AW103" s="3" t="n"/>
+      <c r="AX103" s="3" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n"/>
@@ -5572,6 +6363,13 @@
       <c r="AO104" s="3" t="n"/>
       <c r="AP104" s="3" t="n"/>
       <c r="AQ104" s="3" t="n"/>
+      <c r="AR104" s="3" t="n"/>
+      <c r="AS104" s="3" t="n"/>
+      <c r="AT104" s="3" t="n"/>
+      <c r="AU104" s="3" t="n"/>
+      <c r="AV104" s="3" t="n"/>
+      <c r="AW104" s="3" t="n"/>
+      <c r="AX104" s="3" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n"/>
@@ -5617,6 +6415,13 @@
       <c r="AO105" s="3" t="n"/>
       <c r="AP105" s="3" t="n"/>
       <c r="AQ105" s="3" t="n"/>
+      <c r="AR105" s="3" t="n"/>
+      <c r="AS105" s="3" t="n"/>
+      <c r="AT105" s="3" t="n"/>
+      <c r="AU105" s="3" t="n"/>
+      <c r="AV105" s="3" t="n"/>
+      <c r="AW105" s="3" t="n"/>
+      <c r="AX105" s="3" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n"/>
@@ -5662,6 +6467,13 @@
       <c r="AO106" s="3" t="n"/>
       <c r="AP106" s="3" t="n"/>
       <c r="AQ106" s="3" t="n"/>
+      <c r="AR106" s="3" t="n"/>
+      <c r="AS106" s="3" t="n"/>
+      <c r="AT106" s="3" t="n"/>
+      <c r="AU106" s="3" t="n"/>
+      <c r="AV106" s="3" t="n"/>
+      <c r="AW106" s="3" t="n"/>
+      <c r="AX106" s="3" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n"/>
@@ -5707,6 +6519,13 @@
       <c r="AO107" s="3" t="n"/>
       <c r="AP107" s="3" t="n"/>
       <c r="AQ107" s="3" t="n"/>
+      <c r="AR107" s="3" t="n"/>
+      <c r="AS107" s="3" t="n"/>
+      <c r="AT107" s="3" t="n"/>
+      <c r="AU107" s="3" t="n"/>
+      <c r="AV107" s="3" t="n"/>
+      <c r="AW107" s="3" t="n"/>
+      <c r="AX107" s="3" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n"/>
@@ -5752,6 +6571,13 @@
       <c r="AO108" s="3" t="n"/>
       <c r="AP108" s="3" t="n"/>
       <c r="AQ108" s="3" t="n"/>
+      <c r="AR108" s="3" t="n"/>
+      <c r="AS108" s="3" t="n"/>
+      <c r="AT108" s="3" t="n"/>
+      <c r="AU108" s="3" t="n"/>
+      <c r="AV108" s="3" t="n"/>
+      <c r="AW108" s="3" t="n"/>
+      <c r="AX108" s="3" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n"/>
@@ -5797,6 +6623,13 @@
       <c r="AO109" s="3" t="n"/>
       <c r="AP109" s="3" t="n"/>
       <c r="AQ109" s="3" t="n"/>
+      <c r="AR109" s="3" t="n"/>
+      <c r="AS109" s="3" t="n"/>
+      <c r="AT109" s="3" t="n"/>
+      <c r="AU109" s="3" t="n"/>
+      <c r="AV109" s="3" t="n"/>
+      <c r="AW109" s="3" t="n"/>
+      <c r="AX109" s="3" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n"/>
@@ -5842,6 +6675,13 @@
       <c r="AO110" s="3" t="n"/>
       <c r="AP110" s="3" t="n"/>
       <c r="AQ110" s="3" t="n"/>
+      <c r="AR110" s="3" t="n"/>
+      <c r="AS110" s="3" t="n"/>
+      <c r="AT110" s="3" t="n"/>
+      <c r="AU110" s="3" t="n"/>
+      <c r="AV110" s="3" t="n"/>
+      <c r="AW110" s="3" t="n"/>
+      <c r="AX110" s="3" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n"/>
@@ -5887,6 +6727,13 @@
       <c r="AO111" s="3" t="n"/>
       <c r="AP111" s="3" t="n"/>
       <c r="AQ111" s="3" t="n"/>
+      <c r="AR111" s="3" t="n"/>
+      <c r="AS111" s="3" t="n"/>
+      <c r="AT111" s="3" t="n"/>
+      <c r="AU111" s="3" t="n"/>
+      <c r="AV111" s="3" t="n"/>
+      <c r="AW111" s="3" t="n"/>
+      <c r="AX111" s="3" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n"/>
@@ -5932,6 +6779,13 @@
       <c r="AO112" s="3" t="n"/>
       <c r="AP112" s="3" t="n"/>
       <c r="AQ112" s="3" t="n"/>
+      <c r="AR112" s="3" t="n"/>
+      <c r="AS112" s="3" t="n"/>
+      <c r="AT112" s="3" t="n"/>
+      <c r="AU112" s="3" t="n"/>
+      <c r="AV112" s="3" t="n"/>
+      <c r="AW112" s="3" t="n"/>
+      <c r="AX112" s="3" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n"/>
@@ -5977,6 +6831,13 @@
       <c r="AO113" s="3" t="n"/>
       <c r="AP113" s="3" t="n"/>
       <c r="AQ113" s="3" t="n"/>
+      <c r="AR113" s="3" t="n"/>
+      <c r="AS113" s="3" t="n"/>
+      <c r="AT113" s="3" t="n"/>
+      <c r="AU113" s="3" t="n"/>
+      <c r="AV113" s="3" t="n"/>
+      <c r="AW113" s="3" t="n"/>
+      <c r="AX113" s="3" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n"/>
@@ -6022,6 +6883,13 @@
       <c r="AO114" s="3" t="n"/>
       <c r="AP114" s="3" t="n"/>
       <c r="AQ114" s="3" t="n"/>
+      <c r="AR114" s="3" t="n"/>
+      <c r="AS114" s="3" t="n"/>
+      <c r="AT114" s="3" t="n"/>
+      <c r="AU114" s="3" t="n"/>
+      <c r="AV114" s="3" t="n"/>
+      <c r="AW114" s="3" t="n"/>
+      <c r="AX114" s="3" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n"/>
@@ -6067,6 +6935,13 @@
       <c r="AO115" s="3" t="n"/>
       <c r="AP115" s="3" t="n"/>
       <c r="AQ115" s="3" t="n"/>
+      <c r="AR115" s="3" t="n"/>
+      <c r="AS115" s="3" t="n"/>
+      <c r="AT115" s="3" t="n"/>
+      <c r="AU115" s="3" t="n"/>
+      <c r="AV115" s="3" t="n"/>
+      <c r="AW115" s="3" t="n"/>
+      <c r="AX115" s="3" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n"/>
@@ -6112,6 +6987,13 @@
       <c r="AO116" s="3" t="n"/>
       <c r="AP116" s="3" t="n"/>
       <c r="AQ116" s="3" t="n"/>
+      <c r="AR116" s="3" t="n"/>
+      <c r="AS116" s="3" t="n"/>
+      <c r="AT116" s="3" t="n"/>
+      <c r="AU116" s="3" t="n"/>
+      <c r="AV116" s="3" t="n"/>
+      <c r="AW116" s="3" t="n"/>
+      <c r="AX116" s="3" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n"/>
@@ -6157,6 +7039,13 @@
       <c r="AO117" s="3" t="n"/>
       <c r="AP117" s="3" t="n"/>
       <c r="AQ117" s="3" t="n"/>
+      <c r="AR117" s="3" t="n"/>
+      <c r="AS117" s="3" t="n"/>
+      <c r="AT117" s="3" t="n"/>
+      <c r="AU117" s="3" t="n"/>
+      <c r="AV117" s="3" t="n"/>
+      <c r="AW117" s="3" t="n"/>
+      <c r="AX117" s="3" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n"/>
@@ -6202,6 +7091,13 @@
       <c r="AO118" s="3" t="n"/>
       <c r="AP118" s="3" t="n"/>
       <c r="AQ118" s="3" t="n"/>
+      <c r="AR118" s="3" t="n"/>
+      <c r="AS118" s="3" t="n"/>
+      <c r="AT118" s="3" t="n"/>
+      <c r="AU118" s="3" t="n"/>
+      <c r="AV118" s="3" t="n"/>
+      <c r="AW118" s="3" t="n"/>
+      <c r="AX118" s="3" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n"/>
@@ -6247,6 +7143,13 @@
       <c r="AO119" s="3" t="n"/>
       <c r="AP119" s="3" t="n"/>
       <c r="AQ119" s="3" t="n"/>
+      <c r="AR119" s="3" t="n"/>
+      <c r="AS119" s="3" t="n"/>
+      <c r="AT119" s="3" t="n"/>
+      <c r="AU119" s="3" t="n"/>
+      <c r="AV119" s="3" t="n"/>
+      <c r="AW119" s="3" t="n"/>
+      <c r="AX119" s="3" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n"/>
@@ -6292,6 +7195,13 @@
       <c r="AO120" s="3" t="n"/>
       <c r="AP120" s="3" t="n"/>
       <c r="AQ120" s="3" t="n"/>
+      <c r="AR120" s="3" t="n"/>
+      <c r="AS120" s="3" t="n"/>
+      <c r="AT120" s="3" t="n"/>
+      <c r="AU120" s="3" t="n"/>
+      <c r="AV120" s="3" t="n"/>
+      <c r="AW120" s="3" t="n"/>
+      <c r="AX120" s="3" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n"/>
@@ -6337,6 +7247,13 @@
       <c r="AO121" s="3" t="n"/>
       <c r="AP121" s="3" t="n"/>
       <c r="AQ121" s="3" t="n"/>
+      <c r="AR121" s="3" t="n"/>
+      <c r="AS121" s="3" t="n"/>
+      <c r="AT121" s="3" t="n"/>
+      <c r="AU121" s="3" t="n"/>
+      <c r="AV121" s="3" t="n"/>
+      <c r="AW121" s="3" t="n"/>
+      <c r="AX121" s="3" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n"/>
@@ -6382,6 +7299,13 @@
       <c r="AO122" s="3" t="n"/>
       <c r="AP122" s="3" t="n"/>
       <c r="AQ122" s="3" t="n"/>
+      <c r="AR122" s="3" t="n"/>
+      <c r="AS122" s="3" t="n"/>
+      <c r="AT122" s="3" t="n"/>
+      <c r="AU122" s="3" t="n"/>
+      <c r="AV122" s="3" t="n"/>
+      <c r="AW122" s="3" t="n"/>
+      <c r="AX122" s="3" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n"/>
@@ -6427,6 +7351,13 @@
       <c r="AO123" s="3" t="n"/>
       <c r="AP123" s="3" t="n"/>
       <c r="AQ123" s="3" t="n"/>
+      <c r="AR123" s="3" t="n"/>
+      <c r="AS123" s="3" t="n"/>
+      <c r="AT123" s="3" t="n"/>
+      <c r="AU123" s="3" t="n"/>
+      <c r="AV123" s="3" t="n"/>
+      <c r="AW123" s="3" t="n"/>
+      <c r="AX123" s="3" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n"/>
@@ -6472,6 +7403,13 @@
       <c r="AO124" s="3" t="n"/>
       <c r="AP124" s="3" t="n"/>
       <c r="AQ124" s="3" t="n"/>
+      <c r="AR124" s="3" t="n"/>
+      <c r="AS124" s="3" t="n"/>
+      <c r="AT124" s="3" t="n"/>
+      <c r="AU124" s="3" t="n"/>
+      <c r="AV124" s="3" t="n"/>
+      <c r="AW124" s="3" t="n"/>
+      <c r="AX124" s="3" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n"/>
@@ -6517,6 +7455,13 @@
       <c r="AO125" s="3" t="n"/>
       <c r="AP125" s="3" t="n"/>
       <c r="AQ125" s="3" t="n"/>
+      <c r="AR125" s="3" t="n"/>
+      <c r="AS125" s="3" t="n"/>
+      <c r="AT125" s="3" t="n"/>
+      <c r="AU125" s="3" t="n"/>
+      <c r="AV125" s="3" t="n"/>
+      <c r="AW125" s="3" t="n"/>
+      <c r="AX125" s="3" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n"/>
@@ -6562,6 +7507,13 @@
       <c r="AO126" s="3" t="n"/>
       <c r="AP126" s="3" t="n"/>
       <c r="AQ126" s="3" t="n"/>
+      <c r="AR126" s="3" t="n"/>
+      <c r="AS126" s="3" t="n"/>
+      <c r="AT126" s="3" t="n"/>
+      <c r="AU126" s="3" t="n"/>
+      <c r="AV126" s="3" t="n"/>
+      <c r="AW126" s="3" t="n"/>
+      <c r="AX126" s="3" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n"/>
@@ -6607,6 +7559,13 @@
       <c r="AO127" s="3" t="n"/>
       <c r="AP127" s="3" t="n"/>
       <c r="AQ127" s="3" t="n"/>
+      <c r="AR127" s="3" t="n"/>
+      <c r="AS127" s="3" t="n"/>
+      <c r="AT127" s="3" t="n"/>
+      <c r="AU127" s="3" t="n"/>
+      <c r="AV127" s="3" t="n"/>
+      <c r="AW127" s="3" t="n"/>
+      <c r="AX127" s="3" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n"/>
@@ -6652,6 +7611,13 @@
       <c r="AO128" s="3" t="n"/>
       <c r="AP128" s="3" t="n"/>
       <c r="AQ128" s="3" t="n"/>
+      <c r="AR128" s="3" t="n"/>
+      <c r="AS128" s="3" t="n"/>
+      <c r="AT128" s="3" t="n"/>
+      <c r="AU128" s="3" t="n"/>
+      <c r="AV128" s="3" t="n"/>
+      <c r="AW128" s="3" t="n"/>
+      <c r="AX128" s="3" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n"/>
@@ -6697,6 +7663,13 @@
       <c r="AO129" s="3" t="n"/>
       <c r="AP129" s="3" t="n"/>
       <c r="AQ129" s="3" t="n"/>
+      <c r="AR129" s="3" t="n"/>
+      <c r="AS129" s="3" t="n"/>
+      <c r="AT129" s="3" t="n"/>
+      <c r="AU129" s="3" t="n"/>
+      <c r="AV129" s="3" t="n"/>
+      <c r="AW129" s="3" t="n"/>
+      <c r="AX129" s="3" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n"/>
@@ -6742,6 +7715,13 @@
       <c r="AO130" s="3" t="n"/>
       <c r="AP130" s="3" t="n"/>
       <c r="AQ130" s="3" t="n"/>
+      <c r="AR130" s="3" t="n"/>
+      <c r="AS130" s="3" t="n"/>
+      <c r="AT130" s="3" t="n"/>
+      <c r="AU130" s="3" t="n"/>
+      <c r="AV130" s="3" t="n"/>
+      <c r="AW130" s="3" t="n"/>
+      <c r="AX130" s="3" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n"/>
@@ -6787,6 +7767,13 @@
       <c r="AO131" s="3" t="n"/>
       <c r="AP131" s="3" t="n"/>
       <c r="AQ131" s="3" t="n"/>
+      <c r="AR131" s="3" t="n"/>
+      <c r="AS131" s="3" t="n"/>
+      <c r="AT131" s="3" t="n"/>
+      <c r="AU131" s="3" t="n"/>
+      <c r="AV131" s="3" t="n"/>
+      <c r="AW131" s="3" t="n"/>
+      <c r="AX131" s="3" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n"/>
@@ -6832,6 +7819,13 @@
       <c r="AO132" s="3" t="n"/>
       <c r="AP132" s="3" t="n"/>
       <c r="AQ132" s="3" t="n"/>
+      <c r="AR132" s="3" t="n"/>
+      <c r="AS132" s="3" t="n"/>
+      <c r="AT132" s="3" t="n"/>
+      <c r="AU132" s="3" t="n"/>
+      <c r="AV132" s="3" t="n"/>
+      <c r="AW132" s="3" t="n"/>
+      <c r="AX132" s="3" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n"/>
@@ -6877,6 +7871,13 @@
       <c r="AO133" s="3" t="n"/>
       <c r="AP133" s="3" t="n"/>
       <c r="AQ133" s="3" t="n"/>
+      <c r="AR133" s="3" t="n"/>
+      <c r="AS133" s="3" t="n"/>
+      <c r="AT133" s="3" t="n"/>
+      <c r="AU133" s="3" t="n"/>
+      <c r="AV133" s="3" t="n"/>
+      <c r="AW133" s="3" t="n"/>
+      <c r="AX133" s="3" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n"/>
@@ -6922,6 +7923,13 @@
       <c r="AO134" s="3" t="n"/>
       <c r="AP134" s="3" t="n"/>
       <c r="AQ134" s="3" t="n"/>
+      <c r="AR134" s="3" t="n"/>
+      <c r="AS134" s="3" t="n"/>
+      <c r="AT134" s="3" t="n"/>
+      <c r="AU134" s="3" t="n"/>
+      <c r="AV134" s="3" t="n"/>
+      <c r="AW134" s="3" t="n"/>
+      <c r="AX134" s="3" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n"/>
@@ -6967,6 +7975,13 @@
       <c r="AO135" s="3" t="n"/>
       <c r="AP135" s="3" t="n"/>
       <c r="AQ135" s="3" t="n"/>
+      <c r="AR135" s="3" t="n"/>
+      <c r="AS135" s="3" t="n"/>
+      <c r="AT135" s="3" t="n"/>
+      <c r="AU135" s="3" t="n"/>
+      <c r="AV135" s="3" t="n"/>
+      <c r="AW135" s="3" t="n"/>
+      <c r="AX135" s="3" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n"/>
@@ -7012,6 +8027,13 @@
       <c r="AO136" s="3" t="n"/>
       <c r="AP136" s="3" t="n"/>
       <c r="AQ136" s="3" t="n"/>
+      <c r="AR136" s="3" t="n"/>
+      <c r="AS136" s="3" t="n"/>
+      <c r="AT136" s="3" t="n"/>
+      <c r="AU136" s="3" t="n"/>
+      <c r="AV136" s="3" t="n"/>
+      <c r="AW136" s="3" t="n"/>
+      <c r="AX136" s="3" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n"/>
@@ -7057,6 +8079,13 @@
       <c r="AO137" s="3" t="n"/>
       <c r="AP137" s="3" t="n"/>
       <c r="AQ137" s="3" t="n"/>
+      <c r="AR137" s="3" t="n"/>
+      <c r="AS137" s="3" t="n"/>
+      <c r="AT137" s="3" t="n"/>
+      <c r="AU137" s="3" t="n"/>
+      <c r="AV137" s="3" t="n"/>
+      <c r="AW137" s="3" t="n"/>
+      <c r="AX137" s="3" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n"/>
@@ -7102,6 +8131,13 @@
       <c r="AO138" s="3" t="n"/>
       <c r="AP138" s="3" t="n"/>
       <c r="AQ138" s="3" t="n"/>
+      <c r="AR138" s="3" t="n"/>
+      <c r="AS138" s="3" t="n"/>
+      <c r="AT138" s="3" t="n"/>
+      <c r="AU138" s="3" t="n"/>
+      <c r="AV138" s="3" t="n"/>
+      <c r="AW138" s="3" t="n"/>
+      <c r="AX138" s="3" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n"/>
@@ -7147,6 +8183,13 @@
       <c r="AO139" s="3" t="n"/>
       <c r="AP139" s="3" t="n"/>
       <c r="AQ139" s="3" t="n"/>
+      <c r="AR139" s="3" t="n"/>
+      <c r="AS139" s="3" t="n"/>
+      <c r="AT139" s="3" t="n"/>
+      <c r="AU139" s="3" t="n"/>
+      <c r="AV139" s="3" t="n"/>
+      <c r="AW139" s="3" t="n"/>
+      <c r="AX139" s="3" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n"/>
@@ -7192,6 +8235,13 @@
       <c r="AO140" s="3" t="n"/>
       <c r="AP140" s="3" t="n"/>
       <c r="AQ140" s="3" t="n"/>
+      <c r="AR140" s="3" t="n"/>
+      <c r="AS140" s="3" t="n"/>
+      <c r="AT140" s="3" t="n"/>
+      <c r="AU140" s="3" t="n"/>
+      <c r="AV140" s="3" t="n"/>
+      <c r="AW140" s="3" t="n"/>
+      <c r="AX140" s="3" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n"/>
@@ -7237,6 +8287,13 @@
       <c r="AO141" s="3" t="n"/>
       <c r="AP141" s="3" t="n"/>
       <c r="AQ141" s="3" t="n"/>
+      <c r="AR141" s="3" t="n"/>
+      <c r="AS141" s="3" t="n"/>
+      <c r="AT141" s="3" t="n"/>
+      <c r="AU141" s="3" t="n"/>
+      <c r="AV141" s="3" t="n"/>
+      <c r="AW141" s="3" t="n"/>
+      <c r="AX141" s="3" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n"/>
@@ -7282,6 +8339,13 @@
       <c r="AO142" s="3" t="n"/>
       <c r="AP142" s="3" t="n"/>
       <c r="AQ142" s="3" t="n"/>
+      <c r="AR142" s="3" t="n"/>
+      <c r="AS142" s="3" t="n"/>
+      <c r="AT142" s="3" t="n"/>
+      <c r="AU142" s="3" t="n"/>
+      <c r="AV142" s="3" t="n"/>
+      <c r="AW142" s="3" t="n"/>
+      <c r="AX142" s="3" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n"/>
@@ -7327,6 +8391,13 @@
       <c r="AO143" s="3" t="n"/>
       <c r="AP143" s="3" t="n"/>
       <c r="AQ143" s="3" t="n"/>
+      <c r="AR143" s="3" t="n"/>
+      <c r="AS143" s="3" t="n"/>
+      <c r="AT143" s="3" t="n"/>
+      <c r="AU143" s="3" t="n"/>
+      <c r="AV143" s="3" t="n"/>
+      <c r="AW143" s="3" t="n"/>
+      <c r="AX143" s="3" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n"/>
@@ -7372,6 +8443,13 @@
       <c r="AO144" s="3" t="n"/>
       <c r="AP144" s="3" t="n"/>
       <c r="AQ144" s="3" t="n"/>
+      <c r="AR144" s="3" t="n"/>
+      <c r="AS144" s="3" t="n"/>
+      <c r="AT144" s="3" t="n"/>
+      <c r="AU144" s="3" t="n"/>
+      <c r="AV144" s="3" t="n"/>
+      <c r="AW144" s="3" t="n"/>
+      <c r="AX144" s="3" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n"/>
@@ -7417,6 +8495,13 @@
       <c r="AO145" s="3" t="n"/>
       <c r="AP145" s="3" t="n"/>
       <c r="AQ145" s="3" t="n"/>
+      <c r="AR145" s="3" t="n"/>
+      <c r="AS145" s="3" t="n"/>
+      <c r="AT145" s="3" t="n"/>
+      <c r="AU145" s="3" t="n"/>
+      <c r="AV145" s="3" t="n"/>
+      <c r="AW145" s="3" t="n"/>
+      <c r="AX145" s="3" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n"/>
@@ -7462,6 +8547,13 @@
       <c r="AO146" s="3" t="n"/>
       <c r="AP146" s="3" t="n"/>
       <c r="AQ146" s="3" t="n"/>
+      <c r="AR146" s="3" t="n"/>
+      <c r="AS146" s="3" t="n"/>
+      <c r="AT146" s="3" t="n"/>
+      <c r="AU146" s="3" t="n"/>
+      <c r="AV146" s="3" t="n"/>
+      <c r="AW146" s="3" t="n"/>
+      <c r="AX146" s="3" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n"/>
@@ -7507,6 +8599,13 @@
       <c r="AO147" s="3" t="n"/>
       <c r="AP147" s="3" t="n"/>
       <c r="AQ147" s="3" t="n"/>
+      <c r="AR147" s="3" t="n"/>
+      <c r="AS147" s="3" t="n"/>
+      <c r="AT147" s="3" t="n"/>
+      <c r="AU147" s="3" t="n"/>
+      <c r="AV147" s="3" t="n"/>
+      <c r="AW147" s="3" t="n"/>
+      <c r="AX147" s="3" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n"/>
@@ -7552,6 +8651,13 @@
       <c r="AO148" s="3" t="n"/>
       <c r="AP148" s="3" t="n"/>
       <c r="AQ148" s="3" t="n"/>
+      <c r="AR148" s="3" t="n"/>
+      <c r="AS148" s="3" t="n"/>
+      <c r="AT148" s="3" t="n"/>
+      <c r="AU148" s="3" t="n"/>
+      <c r="AV148" s="3" t="n"/>
+      <c r="AW148" s="3" t="n"/>
+      <c r="AX148" s="3" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n"/>
@@ -7597,6 +8703,13 @@
       <c r="AO149" s="3" t="n"/>
       <c r="AP149" s="3" t="n"/>
       <c r="AQ149" s="3" t="n"/>
+      <c r="AR149" s="3" t="n"/>
+      <c r="AS149" s="3" t="n"/>
+      <c r="AT149" s="3" t="n"/>
+      <c r="AU149" s="3" t="n"/>
+      <c r="AV149" s="3" t="n"/>
+      <c r="AW149" s="3" t="n"/>
+      <c r="AX149" s="3" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n"/>
@@ -7642,6 +8755,13 @@
       <c r="AO150" s="3" t="n"/>
       <c r="AP150" s="3" t="n"/>
       <c r="AQ150" s="3" t="n"/>
+      <c r="AR150" s="3" t="n"/>
+      <c r="AS150" s="3" t="n"/>
+      <c r="AT150" s="3" t="n"/>
+      <c r="AU150" s="3" t="n"/>
+      <c r="AV150" s="3" t="n"/>
+      <c r="AW150" s="3" t="n"/>
+      <c r="AX150" s="3" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n"/>
@@ -7687,6 +8807,13 @@
       <c r="AO151" s="3" t="n"/>
       <c r="AP151" s="3" t="n"/>
       <c r="AQ151" s="3" t="n"/>
+      <c r="AR151" s="3" t="n"/>
+      <c r="AS151" s="3" t="n"/>
+      <c r="AT151" s="3" t="n"/>
+      <c r="AU151" s="3" t="n"/>
+      <c r="AV151" s="3" t="n"/>
+      <c r="AW151" s="3" t="n"/>
+      <c r="AX151" s="3" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n"/>
@@ -7732,6 +8859,13 @@
       <c r="AO152" s="3" t="n"/>
       <c r="AP152" s="3" t="n"/>
       <c r="AQ152" s="3" t="n"/>
+      <c r="AR152" s="3" t="n"/>
+      <c r="AS152" s="3" t="n"/>
+      <c r="AT152" s="3" t="n"/>
+      <c r="AU152" s="3" t="n"/>
+      <c r="AV152" s="3" t="n"/>
+      <c r="AW152" s="3" t="n"/>
+      <c r="AX152" s="3" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n"/>
@@ -7777,6 +8911,13 @@
       <c r="AO153" s="3" t="n"/>
       <c r="AP153" s="3" t="n"/>
       <c r="AQ153" s="3" t="n"/>
+      <c r="AR153" s="3" t="n"/>
+      <c r="AS153" s="3" t="n"/>
+      <c r="AT153" s="3" t="n"/>
+      <c r="AU153" s="3" t="n"/>
+      <c r="AV153" s="3" t="n"/>
+      <c r="AW153" s="3" t="n"/>
+      <c r="AX153" s="3" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n"/>
@@ -7822,6 +8963,13 @@
       <c r="AO154" s="3" t="n"/>
       <c r="AP154" s="3" t="n"/>
       <c r="AQ154" s="3" t="n"/>
+      <c r="AR154" s="3" t="n"/>
+      <c r="AS154" s="3" t="n"/>
+      <c r="AT154" s="3" t="n"/>
+      <c r="AU154" s="3" t="n"/>
+      <c r="AV154" s="3" t="n"/>
+      <c r="AW154" s="3" t="n"/>
+      <c r="AX154" s="3" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n"/>
@@ -7867,6 +9015,13 @@
       <c r="AO155" s="3" t="n"/>
       <c r="AP155" s="3" t="n"/>
       <c r="AQ155" s="3" t="n"/>
+      <c r="AR155" s="3" t="n"/>
+      <c r="AS155" s="3" t="n"/>
+      <c r="AT155" s="3" t="n"/>
+      <c r="AU155" s="3" t="n"/>
+      <c r="AV155" s="3" t="n"/>
+      <c r="AW155" s="3" t="n"/>
+      <c r="AX155" s="3" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n"/>
@@ -7912,6 +9067,13 @@
       <c r="AO156" s="3" t="n"/>
       <c r="AP156" s="3" t="n"/>
       <c r="AQ156" s="3" t="n"/>
+      <c r="AR156" s="3" t="n"/>
+      <c r="AS156" s="3" t="n"/>
+      <c r="AT156" s="3" t="n"/>
+      <c r="AU156" s="3" t="n"/>
+      <c r="AV156" s="3" t="n"/>
+      <c r="AW156" s="3" t="n"/>
+      <c r="AX156" s="3" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n"/>
@@ -7957,6 +9119,13 @@
       <c r="AO157" s="3" t="n"/>
       <c r="AP157" s="3" t="n"/>
       <c r="AQ157" s="3" t="n"/>
+      <c r="AR157" s="3" t="n"/>
+      <c r="AS157" s="3" t="n"/>
+      <c r="AT157" s="3" t="n"/>
+      <c r="AU157" s="3" t="n"/>
+      <c r="AV157" s="3" t="n"/>
+      <c r="AW157" s="3" t="n"/>
+      <c r="AX157" s="3" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n"/>
@@ -8002,6 +9171,13 @@
       <c r="AO158" s="3" t="n"/>
       <c r="AP158" s="3" t="n"/>
       <c r="AQ158" s="3" t="n"/>
+      <c r="AR158" s="3" t="n"/>
+      <c r="AS158" s="3" t="n"/>
+      <c r="AT158" s="3" t="n"/>
+      <c r="AU158" s="3" t="n"/>
+      <c r="AV158" s="3" t="n"/>
+      <c r="AW158" s="3" t="n"/>
+      <c r="AX158" s="3" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n"/>
@@ -8047,6 +9223,13 @@
       <c r="AO159" s="3" t="n"/>
       <c r="AP159" s="3" t="n"/>
       <c r="AQ159" s="3" t="n"/>
+      <c r="AR159" s="3" t="n"/>
+      <c r="AS159" s="3" t="n"/>
+      <c r="AT159" s="3" t="n"/>
+      <c r="AU159" s="3" t="n"/>
+      <c r="AV159" s="3" t="n"/>
+      <c r="AW159" s="3" t="n"/>
+      <c r="AX159" s="3" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n"/>
@@ -8092,6 +9275,13 @@
       <c r="AO160" s="3" t="n"/>
       <c r="AP160" s="3" t="n"/>
       <c r="AQ160" s="3" t="n"/>
+      <c r="AR160" s="3" t="n"/>
+      <c r="AS160" s="3" t="n"/>
+      <c r="AT160" s="3" t="n"/>
+      <c r="AU160" s="3" t="n"/>
+      <c r="AV160" s="3" t="n"/>
+      <c r="AW160" s="3" t="n"/>
+      <c r="AX160" s="3" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="3" t="n"/>
@@ -8137,6 +9327,13 @@
       <c r="AO161" s="3" t="n"/>
       <c r="AP161" s="3" t="n"/>
       <c r="AQ161" s="3" t="n"/>
+      <c r="AR161" s="3" t="n"/>
+      <c r="AS161" s="3" t="n"/>
+      <c r="AT161" s="3" t="n"/>
+      <c r="AU161" s="3" t="n"/>
+      <c r="AV161" s="3" t="n"/>
+      <c r="AW161" s="3" t="n"/>
+      <c r="AX161" s="3" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="3" t="n"/>
@@ -8182,6 +9379,13 @@
       <c r="AO162" s="3" t="n"/>
       <c r="AP162" s="3" t="n"/>
       <c r="AQ162" s="3" t="n"/>
+      <c r="AR162" s="3" t="n"/>
+      <c r="AS162" s="3" t="n"/>
+      <c r="AT162" s="3" t="n"/>
+      <c r="AU162" s="3" t="n"/>
+      <c r="AV162" s="3" t="n"/>
+      <c r="AW162" s="3" t="n"/>
+      <c r="AX162" s="3" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="n"/>
@@ -8227,6 +9431,13 @@
       <c r="AO163" s="3" t="n"/>
       <c r="AP163" s="3" t="n"/>
       <c r="AQ163" s="3" t="n"/>
+      <c r="AR163" s="3" t="n"/>
+      <c r="AS163" s="3" t="n"/>
+      <c r="AT163" s="3" t="n"/>
+      <c r="AU163" s="3" t="n"/>
+      <c r="AV163" s="3" t="n"/>
+      <c r="AW163" s="3" t="n"/>
+      <c r="AX163" s="3" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n"/>
@@ -8272,6 +9483,13 @@
       <c r="AO164" s="3" t="n"/>
       <c r="AP164" s="3" t="n"/>
       <c r="AQ164" s="3" t="n"/>
+      <c r="AR164" s="3" t="n"/>
+      <c r="AS164" s="3" t="n"/>
+      <c r="AT164" s="3" t="n"/>
+      <c r="AU164" s="3" t="n"/>
+      <c r="AV164" s="3" t="n"/>
+      <c r="AW164" s="3" t="n"/>
+      <c r="AX164" s="3" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="n"/>
@@ -8317,6 +9535,13 @@
       <c r="AO165" s="3" t="n"/>
       <c r="AP165" s="3" t="n"/>
       <c r="AQ165" s="3" t="n"/>
+      <c r="AR165" s="3" t="n"/>
+      <c r="AS165" s="3" t="n"/>
+      <c r="AT165" s="3" t="n"/>
+      <c r="AU165" s="3" t="n"/>
+      <c r="AV165" s="3" t="n"/>
+      <c r="AW165" s="3" t="n"/>
+      <c r="AX165" s="3" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n"/>
@@ -8362,6 +9587,13 @@
       <c r="AO166" s="3" t="n"/>
       <c r="AP166" s="3" t="n"/>
       <c r="AQ166" s="3" t="n"/>
+      <c r="AR166" s="3" t="n"/>
+      <c r="AS166" s="3" t="n"/>
+      <c r="AT166" s="3" t="n"/>
+      <c r="AU166" s="3" t="n"/>
+      <c r="AV166" s="3" t="n"/>
+      <c r="AW166" s="3" t="n"/>
+      <c r="AX166" s="3" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n"/>
@@ -8407,6 +9639,13 @@
       <c r="AO167" s="3" t="n"/>
       <c r="AP167" s="3" t="n"/>
       <c r="AQ167" s="3" t="n"/>
+      <c r="AR167" s="3" t="n"/>
+      <c r="AS167" s="3" t="n"/>
+      <c r="AT167" s="3" t="n"/>
+      <c r="AU167" s="3" t="n"/>
+      <c r="AV167" s="3" t="n"/>
+      <c r="AW167" s="3" t="n"/>
+      <c r="AX167" s="3" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="3" t="n"/>
@@ -8452,6 +9691,13 @@
       <c r="AO168" s="3" t="n"/>
       <c r="AP168" s="3" t="n"/>
       <c r="AQ168" s="3" t="n"/>
+      <c r="AR168" s="3" t="n"/>
+      <c r="AS168" s="3" t="n"/>
+      <c r="AT168" s="3" t="n"/>
+      <c r="AU168" s="3" t="n"/>
+      <c r="AV168" s="3" t="n"/>
+      <c r="AW168" s="3" t="n"/>
+      <c r="AX168" s="3" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="3" t="n"/>
@@ -8497,6 +9743,13 @@
       <c r="AO169" s="3" t="n"/>
       <c r="AP169" s="3" t="n"/>
       <c r="AQ169" s="3" t="n"/>
+      <c r="AR169" s="3" t="n"/>
+      <c r="AS169" s="3" t="n"/>
+      <c r="AT169" s="3" t="n"/>
+      <c r="AU169" s="3" t="n"/>
+      <c r="AV169" s="3" t="n"/>
+      <c r="AW169" s="3" t="n"/>
+      <c r="AX169" s="3" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="n"/>
@@ -8542,6 +9795,13 @@
       <c r="AO170" s="3" t="n"/>
       <c r="AP170" s="3" t="n"/>
       <c r="AQ170" s="3" t="n"/>
+      <c r="AR170" s="3" t="n"/>
+      <c r="AS170" s="3" t="n"/>
+      <c r="AT170" s="3" t="n"/>
+      <c r="AU170" s="3" t="n"/>
+      <c r="AV170" s="3" t="n"/>
+      <c r="AW170" s="3" t="n"/>
+      <c r="AX170" s="3" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="n"/>
@@ -8587,6 +9847,13 @@
       <c r="AO171" s="3" t="n"/>
       <c r="AP171" s="3" t="n"/>
       <c r="AQ171" s="3" t="n"/>
+      <c r="AR171" s="3" t="n"/>
+      <c r="AS171" s="3" t="n"/>
+      <c r="AT171" s="3" t="n"/>
+      <c r="AU171" s="3" t="n"/>
+      <c r="AV171" s="3" t="n"/>
+      <c r="AW171" s="3" t="n"/>
+      <c r="AX171" s="3" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="n"/>
@@ -8632,6 +9899,13 @@
       <c r="AO172" s="3" t="n"/>
       <c r="AP172" s="3" t="n"/>
       <c r="AQ172" s="3" t="n"/>
+      <c r="AR172" s="3" t="n"/>
+      <c r="AS172" s="3" t="n"/>
+      <c r="AT172" s="3" t="n"/>
+      <c r="AU172" s="3" t="n"/>
+      <c r="AV172" s="3" t="n"/>
+      <c r="AW172" s="3" t="n"/>
+      <c r="AX172" s="3" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="n"/>
@@ -8677,6 +9951,13 @@
       <c r="AO173" s="3" t="n"/>
       <c r="AP173" s="3" t="n"/>
       <c r="AQ173" s="3" t="n"/>
+      <c r="AR173" s="3" t="n"/>
+      <c r="AS173" s="3" t="n"/>
+      <c r="AT173" s="3" t="n"/>
+      <c r="AU173" s="3" t="n"/>
+      <c r="AV173" s="3" t="n"/>
+      <c r="AW173" s="3" t="n"/>
+      <c r="AX173" s="3" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="n"/>
@@ -8722,6 +10003,13 @@
       <c r="AO174" s="3" t="n"/>
       <c r="AP174" s="3" t="n"/>
       <c r="AQ174" s="3" t="n"/>
+      <c r="AR174" s="3" t="n"/>
+      <c r="AS174" s="3" t="n"/>
+      <c r="AT174" s="3" t="n"/>
+      <c r="AU174" s="3" t="n"/>
+      <c r="AV174" s="3" t="n"/>
+      <c r="AW174" s="3" t="n"/>
+      <c r="AX174" s="3" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="3" t="n"/>
@@ -8767,6 +10055,13 @@
       <c r="AO175" s="3" t="n"/>
       <c r="AP175" s="3" t="n"/>
       <c r="AQ175" s="3" t="n"/>
+      <c r="AR175" s="3" t="n"/>
+      <c r="AS175" s="3" t="n"/>
+      <c r="AT175" s="3" t="n"/>
+      <c r="AU175" s="3" t="n"/>
+      <c r="AV175" s="3" t="n"/>
+      <c r="AW175" s="3" t="n"/>
+      <c r="AX175" s="3" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="3" t="n"/>
@@ -8812,6 +10107,13 @@
       <c r="AO176" s="3" t="n"/>
       <c r="AP176" s="3" t="n"/>
       <c r="AQ176" s="3" t="n"/>
+      <c r="AR176" s="3" t="n"/>
+      <c r="AS176" s="3" t="n"/>
+      <c r="AT176" s="3" t="n"/>
+      <c r="AU176" s="3" t="n"/>
+      <c r="AV176" s="3" t="n"/>
+      <c r="AW176" s="3" t="n"/>
+      <c r="AX176" s="3" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="n"/>
@@ -8857,6 +10159,13 @@
       <c r="AO177" s="3" t="n"/>
       <c r="AP177" s="3" t="n"/>
       <c r="AQ177" s="3" t="n"/>
+      <c r="AR177" s="3" t="n"/>
+      <c r="AS177" s="3" t="n"/>
+      <c r="AT177" s="3" t="n"/>
+      <c r="AU177" s="3" t="n"/>
+      <c r="AV177" s="3" t="n"/>
+      <c r="AW177" s="3" t="n"/>
+      <c r="AX177" s="3" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="n"/>
@@ -8902,6 +10211,13 @@
       <c r="AO178" s="3" t="n"/>
       <c r="AP178" s="3" t="n"/>
       <c r="AQ178" s="3" t="n"/>
+      <c r="AR178" s="3" t="n"/>
+      <c r="AS178" s="3" t="n"/>
+      <c r="AT178" s="3" t="n"/>
+      <c r="AU178" s="3" t="n"/>
+      <c r="AV178" s="3" t="n"/>
+      <c r="AW178" s="3" t="n"/>
+      <c r="AX178" s="3" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="n"/>
@@ -8947,6 +10263,13 @@
       <c r="AO179" s="3" t="n"/>
       <c r="AP179" s="3" t="n"/>
       <c r="AQ179" s="3" t="n"/>
+      <c r="AR179" s="3" t="n"/>
+      <c r="AS179" s="3" t="n"/>
+      <c r="AT179" s="3" t="n"/>
+      <c r="AU179" s="3" t="n"/>
+      <c r="AV179" s="3" t="n"/>
+      <c r="AW179" s="3" t="n"/>
+      <c r="AX179" s="3" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="n"/>
@@ -8992,6 +10315,13 @@
       <c r="AO180" s="3" t="n"/>
       <c r="AP180" s="3" t="n"/>
       <c r="AQ180" s="3" t="n"/>
+      <c r="AR180" s="3" t="n"/>
+      <c r="AS180" s="3" t="n"/>
+      <c r="AT180" s="3" t="n"/>
+      <c r="AU180" s="3" t="n"/>
+      <c r="AV180" s="3" t="n"/>
+      <c r="AW180" s="3" t="n"/>
+      <c r="AX180" s="3" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="n"/>
@@ -9037,6 +10367,13 @@
       <c r="AO181" s="3" t="n"/>
       <c r="AP181" s="3" t="n"/>
       <c r="AQ181" s="3" t="n"/>
+      <c r="AR181" s="3" t="n"/>
+      <c r="AS181" s="3" t="n"/>
+      <c r="AT181" s="3" t="n"/>
+      <c r="AU181" s="3" t="n"/>
+      <c r="AV181" s="3" t="n"/>
+      <c r="AW181" s="3" t="n"/>
+      <c r="AX181" s="3" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="3" t="n"/>
@@ -9082,6 +10419,13 @@
       <c r="AO182" s="3" t="n"/>
       <c r="AP182" s="3" t="n"/>
       <c r="AQ182" s="3" t="n"/>
+      <c r="AR182" s="3" t="n"/>
+      <c r="AS182" s="3" t="n"/>
+      <c r="AT182" s="3" t="n"/>
+      <c r="AU182" s="3" t="n"/>
+      <c r="AV182" s="3" t="n"/>
+      <c r="AW182" s="3" t="n"/>
+      <c r="AX182" s="3" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="3" t="n"/>
@@ -9127,6 +10471,13 @@
       <c r="AO183" s="3" t="n"/>
       <c r="AP183" s="3" t="n"/>
       <c r="AQ183" s="3" t="n"/>
+      <c r="AR183" s="3" t="n"/>
+      <c r="AS183" s="3" t="n"/>
+      <c r="AT183" s="3" t="n"/>
+      <c r="AU183" s="3" t="n"/>
+      <c r="AV183" s="3" t="n"/>
+      <c r="AW183" s="3" t="n"/>
+      <c r="AX183" s="3" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="n"/>
@@ -9172,6 +10523,13 @@
       <c r="AO184" s="3" t="n"/>
       <c r="AP184" s="3" t="n"/>
       <c r="AQ184" s="3" t="n"/>
+      <c r="AR184" s="3" t="n"/>
+      <c r="AS184" s="3" t="n"/>
+      <c r="AT184" s="3" t="n"/>
+      <c r="AU184" s="3" t="n"/>
+      <c r="AV184" s="3" t="n"/>
+      <c r="AW184" s="3" t="n"/>
+      <c r="AX184" s="3" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="n"/>
@@ -9217,6 +10575,13 @@
       <c r="AO185" s="3" t="n"/>
       <c r="AP185" s="3" t="n"/>
       <c r="AQ185" s="3" t="n"/>
+      <c r="AR185" s="3" t="n"/>
+      <c r="AS185" s="3" t="n"/>
+      <c r="AT185" s="3" t="n"/>
+      <c r="AU185" s="3" t="n"/>
+      <c r="AV185" s="3" t="n"/>
+      <c r="AW185" s="3" t="n"/>
+      <c r="AX185" s="3" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="n"/>
@@ -9262,6 +10627,13 @@
       <c r="AO186" s="3" t="n"/>
       <c r="AP186" s="3" t="n"/>
       <c r="AQ186" s="3" t="n"/>
+      <c r="AR186" s="3" t="n"/>
+      <c r="AS186" s="3" t="n"/>
+      <c r="AT186" s="3" t="n"/>
+      <c r="AU186" s="3" t="n"/>
+      <c r="AV186" s="3" t="n"/>
+      <c r="AW186" s="3" t="n"/>
+      <c r="AX186" s="3" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="n"/>
@@ -9307,6 +10679,13 @@
       <c r="AO187" s="3" t="n"/>
       <c r="AP187" s="3" t="n"/>
       <c r="AQ187" s="3" t="n"/>
+      <c r="AR187" s="3" t="n"/>
+      <c r="AS187" s="3" t="n"/>
+      <c r="AT187" s="3" t="n"/>
+      <c r="AU187" s="3" t="n"/>
+      <c r="AV187" s="3" t="n"/>
+      <c r="AW187" s="3" t="n"/>
+      <c r="AX187" s="3" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="n"/>
@@ -9352,6 +10731,13 @@
       <c r="AO188" s="3" t="n"/>
       <c r="AP188" s="3" t="n"/>
       <c r="AQ188" s="3" t="n"/>
+      <c r="AR188" s="3" t="n"/>
+      <c r="AS188" s="3" t="n"/>
+      <c r="AT188" s="3" t="n"/>
+      <c r="AU188" s="3" t="n"/>
+      <c r="AV188" s="3" t="n"/>
+      <c r="AW188" s="3" t="n"/>
+      <c r="AX188" s="3" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="3" t="n"/>
@@ -9397,6 +10783,13 @@
       <c r="AO189" s="3" t="n"/>
       <c r="AP189" s="3" t="n"/>
       <c r="AQ189" s="3" t="n"/>
+      <c r="AR189" s="3" t="n"/>
+      <c r="AS189" s="3" t="n"/>
+      <c r="AT189" s="3" t="n"/>
+      <c r="AU189" s="3" t="n"/>
+      <c r="AV189" s="3" t="n"/>
+      <c r="AW189" s="3" t="n"/>
+      <c r="AX189" s="3" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="3" t="n"/>
@@ -9442,6 +10835,13 @@
       <c r="AO190" s="3" t="n"/>
       <c r="AP190" s="3" t="n"/>
       <c r="AQ190" s="3" t="n"/>
+      <c r="AR190" s="3" t="n"/>
+      <c r="AS190" s="3" t="n"/>
+      <c r="AT190" s="3" t="n"/>
+      <c r="AU190" s="3" t="n"/>
+      <c r="AV190" s="3" t="n"/>
+      <c r="AW190" s="3" t="n"/>
+      <c r="AX190" s="3" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="n"/>
@@ -9487,6 +10887,13 @@
       <c r="AO191" s="3" t="n"/>
       <c r="AP191" s="3" t="n"/>
       <c r="AQ191" s="3" t="n"/>
+      <c r="AR191" s="3" t="n"/>
+      <c r="AS191" s="3" t="n"/>
+      <c r="AT191" s="3" t="n"/>
+      <c r="AU191" s="3" t="n"/>
+      <c r="AV191" s="3" t="n"/>
+      <c r="AW191" s="3" t="n"/>
+      <c r="AX191" s="3" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="n"/>
@@ -9532,6 +10939,13 @@
       <c r="AO192" s="3" t="n"/>
       <c r="AP192" s="3" t="n"/>
       <c r="AQ192" s="3" t="n"/>
+      <c r="AR192" s="3" t="n"/>
+      <c r="AS192" s="3" t="n"/>
+      <c r="AT192" s="3" t="n"/>
+      <c r="AU192" s="3" t="n"/>
+      <c r="AV192" s="3" t="n"/>
+      <c r="AW192" s="3" t="n"/>
+      <c r="AX192" s="3" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="n"/>
@@ -9577,6 +10991,13 @@
       <c r="AO193" s="3" t="n"/>
       <c r="AP193" s="3" t="n"/>
       <c r="AQ193" s="3" t="n"/>
+      <c r="AR193" s="3" t="n"/>
+      <c r="AS193" s="3" t="n"/>
+      <c r="AT193" s="3" t="n"/>
+      <c r="AU193" s="3" t="n"/>
+      <c r="AV193" s="3" t="n"/>
+      <c r="AW193" s="3" t="n"/>
+      <c r="AX193" s="3" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="n"/>
@@ -9622,6 +11043,13 @@
       <c r="AO194" s="3" t="n"/>
       <c r="AP194" s="3" t="n"/>
       <c r="AQ194" s="3" t="n"/>
+      <c r="AR194" s="3" t="n"/>
+      <c r="AS194" s="3" t="n"/>
+      <c r="AT194" s="3" t="n"/>
+      <c r="AU194" s="3" t="n"/>
+      <c r="AV194" s="3" t="n"/>
+      <c r="AW194" s="3" t="n"/>
+      <c r="AX194" s="3" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="n"/>
@@ -9667,6 +11095,13 @@
       <c r="AO195" s="3" t="n"/>
       <c r="AP195" s="3" t="n"/>
       <c r="AQ195" s="3" t="n"/>
+      <c r="AR195" s="3" t="n"/>
+      <c r="AS195" s="3" t="n"/>
+      <c r="AT195" s="3" t="n"/>
+      <c r="AU195" s="3" t="n"/>
+      <c r="AV195" s="3" t="n"/>
+      <c r="AW195" s="3" t="n"/>
+      <c r="AX195" s="3" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="3" t="n"/>
@@ -9712,6 +11147,13 @@
       <c r="AO196" s="3" t="n"/>
       <c r="AP196" s="3" t="n"/>
       <c r="AQ196" s="3" t="n"/>
+      <c r="AR196" s="3" t="n"/>
+      <c r="AS196" s="3" t="n"/>
+      <c r="AT196" s="3" t="n"/>
+      <c r="AU196" s="3" t="n"/>
+      <c r="AV196" s="3" t="n"/>
+      <c r="AW196" s="3" t="n"/>
+      <c r="AX196" s="3" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="3" t="n"/>
@@ -9757,6 +11199,13 @@
       <c r="AO197" s="3" t="n"/>
       <c r="AP197" s="3" t="n"/>
       <c r="AQ197" s="3" t="n"/>
+      <c r="AR197" s="3" t="n"/>
+      <c r="AS197" s="3" t="n"/>
+      <c r="AT197" s="3" t="n"/>
+      <c r="AU197" s="3" t="n"/>
+      <c r="AV197" s="3" t="n"/>
+      <c r="AW197" s="3" t="n"/>
+      <c r="AX197" s="3" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="3" t="n"/>
@@ -9802,6 +11251,13 @@
       <c r="AO198" s="3" t="n"/>
       <c r="AP198" s="3" t="n"/>
       <c r="AQ198" s="3" t="n"/>
+      <c r="AR198" s="3" t="n"/>
+      <c r="AS198" s="3" t="n"/>
+      <c r="AT198" s="3" t="n"/>
+      <c r="AU198" s="3" t="n"/>
+      <c r="AV198" s="3" t="n"/>
+      <c r="AW198" s="3" t="n"/>
+      <c r="AX198" s="3" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="n"/>
@@ -9847,6 +11303,13 @@
       <c r="AO199" s="3" t="n"/>
       <c r="AP199" s="3" t="n"/>
       <c r="AQ199" s="3" t="n"/>
+      <c r="AR199" s="3" t="n"/>
+      <c r="AS199" s="3" t="n"/>
+      <c r="AT199" s="3" t="n"/>
+      <c r="AU199" s="3" t="n"/>
+      <c r="AV199" s="3" t="n"/>
+      <c r="AW199" s="3" t="n"/>
+      <c r="AX199" s="3" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="3" t="n"/>
@@ -9892,6 +11355,13 @@
       <c r="AO200" s="3" t="n"/>
       <c r="AP200" s="3" t="n"/>
       <c r="AQ200" s="3" t="n"/>
+      <c r="AR200" s="3" t="n"/>
+      <c r="AS200" s="3" t="n"/>
+      <c r="AT200" s="3" t="n"/>
+      <c r="AU200" s="3" t="n"/>
+      <c r="AV200" s="3" t="n"/>
+      <c r="AW200" s="3" t="n"/>
+      <c r="AX200" s="3" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="3" t="n"/>
@@ -9937,6 +11407,13 @@
       <c r="AO201" s="3" t="n"/>
       <c r="AP201" s="3" t="n"/>
       <c r="AQ201" s="3" t="n"/>
+      <c r="AR201" s="3" t="n"/>
+      <c r="AS201" s="3" t="n"/>
+      <c r="AT201" s="3" t="n"/>
+      <c r="AU201" s="3" t="n"/>
+      <c r="AV201" s="3" t="n"/>
+      <c r="AW201" s="3" t="n"/>
+      <c r="AX201" s="3" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="n"/>
@@ -9982,6 +11459,13 @@
       <c r="AO202" s="3" t="n"/>
       <c r="AP202" s="3" t="n"/>
       <c r="AQ202" s="3" t="n"/>
+      <c r="AR202" s="3" t="n"/>
+      <c r="AS202" s="3" t="n"/>
+      <c r="AT202" s="3" t="n"/>
+      <c r="AU202" s="3" t="n"/>
+      <c r="AV202" s="3" t="n"/>
+      <c r="AW202" s="3" t="n"/>
+      <c r="AX202" s="3" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="3" t="n"/>
@@ -10027,6 +11511,13 @@
       <c r="AO203" s="3" t="n"/>
       <c r="AP203" s="3" t="n"/>
       <c r="AQ203" s="3" t="n"/>
+      <c r="AR203" s="3" t="n"/>
+      <c r="AS203" s="3" t="n"/>
+      <c r="AT203" s="3" t="n"/>
+      <c r="AU203" s="3" t="n"/>
+      <c r="AV203" s="3" t="n"/>
+      <c r="AW203" s="3" t="n"/>
+      <c r="AX203" s="3" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="3" t="n"/>
@@ -10072,6 +11563,13 @@
       <c r="AO204" s="3" t="n"/>
       <c r="AP204" s="3" t="n"/>
       <c r="AQ204" s="3" t="n"/>
+      <c r="AR204" s="3" t="n"/>
+      <c r="AS204" s="3" t="n"/>
+      <c r="AT204" s="3" t="n"/>
+      <c r="AU204" s="3" t="n"/>
+      <c r="AV204" s="3" t="n"/>
+      <c r="AW204" s="3" t="n"/>
+      <c r="AX204" s="3" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="3" t="n"/>
@@ -10117,6 +11615,13 @@
       <c r="AO205" s="3" t="n"/>
       <c r="AP205" s="3" t="n"/>
       <c r="AQ205" s="3" t="n"/>
+      <c r="AR205" s="3" t="n"/>
+      <c r="AS205" s="3" t="n"/>
+      <c r="AT205" s="3" t="n"/>
+      <c r="AU205" s="3" t="n"/>
+      <c r="AV205" s="3" t="n"/>
+      <c r="AW205" s="3" t="n"/>
+      <c r="AX205" s="3" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="3" t="n"/>
@@ -10162,6 +11667,13 @@
       <c r="AO206" s="3" t="n"/>
       <c r="AP206" s="3" t="n"/>
       <c r="AQ206" s="3" t="n"/>
+      <c r="AR206" s="3" t="n"/>
+      <c r="AS206" s="3" t="n"/>
+      <c r="AT206" s="3" t="n"/>
+      <c r="AU206" s="3" t="n"/>
+      <c r="AV206" s="3" t="n"/>
+      <c r="AW206" s="3" t="n"/>
+      <c r="AX206" s="3" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="3" t="n"/>
@@ -10207,6 +11719,13 @@
       <c r="AO207" s="3" t="n"/>
       <c r="AP207" s="3" t="n"/>
       <c r="AQ207" s="3" t="n"/>
+      <c r="AR207" s="3" t="n"/>
+      <c r="AS207" s="3" t="n"/>
+      <c r="AT207" s="3" t="n"/>
+      <c r="AU207" s="3" t="n"/>
+      <c r="AV207" s="3" t="n"/>
+      <c r="AW207" s="3" t="n"/>
+      <c r="AX207" s="3" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="3" t="n"/>
@@ -10252,6 +11771,13 @@
       <c r="AO208" s="3" t="n"/>
       <c r="AP208" s="3" t="n"/>
       <c r="AQ208" s="3" t="n"/>
+      <c r="AR208" s="3" t="n"/>
+      <c r="AS208" s="3" t="n"/>
+      <c r="AT208" s="3" t="n"/>
+      <c r="AU208" s="3" t="n"/>
+      <c r="AV208" s="3" t="n"/>
+      <c r="AW208" s="3" t="n"/>
+      <c r="AX208" s="3" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="3" t="n"/>
@@ -10297,6 +11823,13 @@
       <c r="AO209" s="3" t="n"/>
       <c r="AP209" s="3" t="n"/>
       <c r="AQ209" s="3" t="n"/>
+      <c r="AR209" s="3" t="n"/>
+      <c r="AS209" s="3" t="n"/>
+      <c r="AT209" s="3" t="n"/>
+      <c r="AU209" s="3" t="n"/>
+      <c r="AV209" s="3" t="n"/>
+      <c r="AW209" s="3" t="n"/>
+      <c r="AX209" s="3" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="3" t="n"/>
@@ -10342,6 +11875,13 @@
       <c r="AO210" s="3" t="n"/>
       <c r="AP210" s="3" t="n"/>
       <c r="AQ210" s="3" t="n"/>
+      <c r="AR210" s="3" t="n"/>
+      <c r="AS210" s="3" t="n"/>
+      <c r="AT210" s="3" t="n"/>
+      <c r="AU210" s="3" t="n"/>
+      <c r="AV210" s="3" t="n"/>
+      <c r="AW210" s="3" t="n"/>
+      <c r="AX210" s="3" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="3" t="n"/>
@@ -10387,6 +11927,13 @@
       <c r="AO211" s="3" t="n"/>
       <c r="AP211" s="3" t="n"/>
       <c r="AQ211" s="3" t="n"/>
+      <c r="AR211" s="3" t="n"/>
+      <c r="AS211" s="3" t="n"/>
+      <c r="AT211" s="3" t="n"/>
+      <c r="AU211" s="3" t="n"/>
+      <c r="AV211" s="3" t="n"/>
+      <c r="AW211" s="3" t="n"/>
+      <c r="AX211" s="3" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="3" t="n"/>
@@ -10432,6 +11979,13 @@
       <c r="AO212" s="3" t="n"/>
       <c r="AP212" s="3" t="n"/>
       <c r="AQ212" s="3" t="n"/>
+      <c r="AR212" s="3" t="n"/>
+      <c r="AS212" s="3" t="n"/>
+      <c r="AT212" s="3" t="n"/>
+      <c r="AU212" s="3" t="n"/>
+      <c r="AV212" s="3" t="n"/>
+      <c r="AW212" s="3" t="n"/>
+      <c r="AX212" s="3" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="3" t="n"/>
@@ -10477,6 +12031,13 @@
       <c r="AO213" s="3" t="n"/>
       <c r="AP213" s="3" t="n"/>
       <c r="AQ213" s="3" t="n"/>
+      <c r="AR213" s="3" t="n"/>
+      <c r="AS213" s="3" t="n"/>
+      <c r="AT213" s="3" t="n"/>
+      <c r="AU213" s="3" t="n"/>
+      <c r="AV213" s="3" t="n"/>
+      <c r="AW213" s="3" t="n"/>
+      <c r="AX213" s="3" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="3" t="n"/>
@@ -10522,6 +12083,13 @@
       <c r="AO214" s="3" t="n"/>
       <c r="AP214" s="3" t="n"/>
       <c r="AQ214" s="3" t="n"/>
+      <c r="AR214" s="3" t="n"/>
+      <c r="AS214" s="3" t="n"/>
+      <c r="AT214" s="3" t="n"/>
+      <c r="AU214" s="3" t="n"/>
+      <c r="AV214" s="3" t="n"/>
+      <c r="AW214" s="3" t="n"/>
+      <c r="AX214" s="3" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="3" t="n"/>
@@ -10567,6 +12135,13 @@
       <c r="AO215" s="3" t="n"/>
       <c r="AP215" s="3" t="n"/>
       <c r="AQ215" s="3" t="n"/>
+      <c r="AR215" s="3" t="n"/>
+      <c r="AS215" s="3" t="n"/>
+      <c r="AT215" s="3" t="n"/>
+      <c r="AU215" s="3" t="n"/>
+      <c r="AV215" s="3" t="n"/>
+      <c r="AW215" s="3" t="n"/>
+      <c r="AX215" s="3" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="3" t="n"/>
@@ -10612,6 +12187,13 @@
       <c r="AO216" s="3" t="n"/>
       <c r="AP216" s="3" t="n"/>
       <c r="AQ216" s="3" t="n"/>
+      <c r="AR216" s="3" t="n"/>
+      <c r="AS216" s="3" t="n"/>
+      <c r="AT216" s="3" t="n"/>
+      <c r="AU216" s="3" t="n"/>
+      <c r="AV216" s="3" t="n"/>
+      <c r="AW216" s="3" t="n"/>
+      <c r="AX216" s="3" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="3" t="n"/>
@@ -10657,6 +12239,13 @@
       <c r="AO217" s="3" t="n"/>
       <c r="AP217" s="3" t="n"/>
       <c r="AQ217" s="3" t="n"/>
+      <c r="AR217" s="3" t="n"/>
+      <c r="AS217" s="3" t="n"/>
+      <c r="AT217" s="3" t="n"/>
+      <c r="AU217" s="3" t="n"/>
+      <c r="AV217" s="3" t="n"/>
+      <c r="AW217" s="3" t="n"/>
+      <c r="AX217" s="3" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="3" t="n"/>
@@ -10702,6 +12291,13 @@
       <c r="AO218" s="3" t="n"/>
       <c r="AP218" s="3" t="n"/>
       <c r="AQ218" s="3" t="n"/>
+      <c r="AR218" s="3" t="n"/>
+      <c r="AS218" s="3" t="n"/>
+      <c r="AT218" s="3" t="n"/>
+      <c r="AU218" s="3" t="n"/>
+      <c r="AV218" s="3" t="n"/>
+      <c r="AW218" s="3" t="n"/>
+      <c r="AX218" s="3" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="3" t="n"/>
@@ -10747,6 +12343,13 @@
       <c r="AO219" s="3" t="n"/>
       <c r="AP219" s="3" t="n"/>
       <c r="AQ219" s="3" t="n"/>
+      <c r="AR219" s="3" t="n"/>
+      <c r="AS219" s="3" t="n"/>
+      <c r="AT219" s="3" t="n"/>
+      <c r="AU219" s="3" t="n"/>
+      <c r="AV219" s="3" t="n"/>
+      <c r="AW219" s="3" t="n"/>
+      <c r="AX219" s="3" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="3" t="n"/>
@@ -10792,6 +12395,13 @@
       <c r="AO220" s="3" t="n"/>
       <c r="AP220" s="3" t="n"/>
       <c r="AQ220" s="3" t="n"/>
+      <c r="AR220" s="3" t="n"/>
+      <c r="AS220" s="3" t="n"/>
+      <c r="AT220" s="3" t="n"/>
+      <c r="AU220" s="3" t="n"/>
+      <c r="AV220" s="3" t="n"/>
+      <c r="AW220" s="3" t="n"/>
+      <c r="AX220" s="3" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="3" t="n"/>
@@ -10837,6 +12447,13 @@
       <c r="AO221" s="3" t="n"/>
       <c r="AP221" s="3" t="n"/>
       <c r="AQ221" s="3" t="n"/>
+      <c r="AR221" s="3" t="n"/>
+      <c r="AS221" s="3" t="n"/>
+      <c r="AT221" s="3" t="n"/>
+      <c r="AU221" s="3" t="n"/>
+      <c r="AV221" s="3" t="n"/>
+      <c r="AW221" s="3" t="n"/>
+      <c r="AX221" s="3" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="3" t="n"/>
@@ -10882,6 +12499,13 @@
       <c r="AO222" s="3" t="n"/>
       <c r="AP222" s="3" t="n"/>
       <c r="AQ222" s="3" t="n"/>
+      <c r="AR222" s="3" t="n"/>
+      <c r="AS222" s="3" t="n"/>
+      <c r="AT222" s="3" t="n"/>
+      <c r="AU222" s="3" t="n"/>
+      <c r="AV222" s="3" t="n"/>
+      <c r="AW222" s="3" t="n"/>
+      <c r="AX222" s="3" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="3" t="n"/>
@@ -10927,6 +12551,13 @@
       <c r="AO223" s="3" t="n"/>
       <c r="AP223" s="3" t="n"/>
       <c r="AQ223" s="3" t="n"/>
+      <c r="AR223" s="3" t="n"/>
+      <c r="AS223" s="3" t="n"/>
+      <c r="AT223" s="3" t="n"/>
+      <c r="AU223" s="3" t="n"/>
+      <c r="AV223" s="3" t="n"/>
+      <c r="AW223" s="3" t="n"/>
+      <c r="AX223" s="3" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="3" t="n"/>
@@ -10972,6 +12603,13 @@
       <c r="AO224" s="3" t="n"/>
       <c r="AP224" s="3" t="n"/>
       <c r="AQ224" s="3" t="n"/>
+      <c r="AR224" s="3" t="n"/>
+      <c r="AS224" s="3" t="n"/>
+      <c r="AT224" s="3" t="n"/>
+      <c r="AU224" s="3" t="n"/>
+      <c r="AV224" s="3" t="n"/>
+      <c r="AW224" s="3" t="n"/>
+      <c r="AX224" s="3" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="3" t="n"/>
@@ -11017,6 +12655,13 @@
       <c r="AO225" s="3" t="n"/>
       <c r="AP225" s="3" t="n"/>
       <c r="AQ225" s="3" t="n"/>
+      <c r="AR225" s="3" t="n"/>
+      <c r="AS225" s="3" t="n"/>
+      <c r="AT225" s="3" t="n"/>
+      <c r="AU225" s="3" t="n"/>
+      <c r="AV225" s="3" t="n"/>
+      <c r="AW225" s="3" t="n"/>
+      <c r="AX225" s="3" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="3" t="n"/>
@@ -11062,6 +12707,13 @@
       <c r="AO226" s="3" t="n"/>
       <c r="AP226" s="3" t="n"/>
       <c r="AQ226" s="3" t="n"/>
+      <c r="AR226" s="3" t="n"/>
+      <c r="AS226" s="3" t="n"/>
+      <c r="AT226" s="3" t="n"/>
+      <c r="AU226" s="3" t="n"/>
+      <c r="AV226" s="3" t="n"/>
+      <c r="AW226" s="3" t="n"/>
+      <c r="AX226" s="3" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="3" t="n"/>
@@ -11107,6 +12759,13 @@
       <c r="AO227" s="3" t="n"/>
       <c r="AP227" s="3" t="n"/>
       <c r="AQ227" s="3" t="n"/>
+      <c r="AR227" s="3" t="n"/>
+      <c r="AS227" s="3" t="n"/>
+      <c r="AT227" s="3" t="n"/>
+      <c r="AU227" s="3" t="n"/>
+      <c r="AV227" s="3" t="n"/>
+      <c r="AW227" s="3" t="n"/>
+      <c r="AX227" s="3" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="3" t="n"/>
@@ -11152,6 +12811,13 @@
       <c r="AO228" s="3" t="n"/>
       <c r="AP228" s="3" t="n"/>
       <c r="AQ228" s="3" t="n"/>
+      <c r="AR228" s="3" t="n"/>
+      <c r="AS228" s="3" t="n"/>
+      <c r="AT228" s="3" t="n"/>
+      <c r="AU228" s="3" t="n"/>
+      <c r="AV228" s="3" t="n"/>
+      <c r="AW228" s="3" t="n"/>
+      <c r="AX228" s="3" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="3" t="n"/>
@@ -11197,6 +12863,13 @@
       <c r="AO229" s="3" t="n"/>
       <c r="AP229" s="3" t="n"/>
       <c r="AQ229" s="3" t="n"/>
+      <c r="AR229" s="3" t="n"/>
+      <c r="AS229" s="3" t="n"/>
+      <c r="AT229" s="3" t="n"/>
+      <c r="AU229" s="3" t="n"/>
+      <c r="AV229" s="3" t="n"/>
+      <c r="AW229" s="3" t="n"/>
+      <c r="AX229" s="3" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="3" t="n"/>
@@ -11242,6 +12915,13 @@
       <c r="AO230" s="3" t="n"/>
       <c r="AP230" s="3" t="n"/>
       <c r="AQ230" s="3" t="n"/>
+      <c r="AR230" s="3" t="n"/>
+      <c r="AS230" s="3" t="n"/>
+      <c r="AT230" s="3" t="n"/>
+      <c r="AU230" s="3" t="n"/>
+      <c r="AV230" s="3" t="n"/>
+      <c r="AW230" s="3" t="n"/>
+      <c r="AX230" s="3" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="3" t="n"/>
@@ -11287,6 +12967,13 @@
       <c r="AO231" s="3" t="n"/>
       <c r="AP231" s="3" t="n"/>
       <c r="AQ231" s="3" t="n"/>
+      <c r="AR231" s="3" t="n"/>
+      <c r="AS231" s="3" t="n"/>
+      <c r="AT231" s="3" t="n"/>
+      <c r="AU231" s="3" t="n"/>
+      <c r="AV231" s="3" t="n"/>
+      <c r="AW231" s="3" t="n"/>
+      <c r="AX231" s="3" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="3" t="n"/>
@@ -11332,6 +13019,13 @@
       <c r="AO232" s="3" t="n"/>
       <c r="AP232" s="3" t="n"/>
       <c r="AQ232" s="3" t="n"/>
+      <c r="AR232" s="3" t="n"/>
+      <c r="AS232" s="3" t="n"/>
+      <c r="AT232" s="3" t="n"/>
+      <c r="AU232" s="3" t="n"/>
+      <c r="AV232" s="3" t="n"/>
+      <c r="AW232" s="3" t="n"/>
+      <c r="AX232" s="3" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="3" t="n"/>
@@ -11377,6 +13071,13 @@
       <c r="AO233" s="3" t="n"/>
       <c r="AP233" s="3" t="n"/>
       <c r="AQ233" s="3" t="n"/>
+      <c r="AR233" s="3" t="n"/>
+      <c r="AS233" s="3" t="n"/>
+      <c r="AT233" s="3" t="n"/>
+      <c r="AU233" s="3" t="n"/>
+      <c r="AV233" s="3" t="n"/>
+      <c r="AW233" s="3" t="n"/>
+      <c r="AX233" s="3" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="3" t="n"/>
@@ -11422,6 +13123,13 @@
       <c r="AO234" s="3" t="n"/>
       <c r="AP234" s="3" t="n"/>
       <c r="AQ234" s="3" t="n"/>
+      <c r="AR234" s="3" t="n"/>
+      <c r="AS234" s="3" t="n"/>
+      <c r="AT234" s="3" t="n"/>
+      <c r="AU234" s="3" t="n"/>
+      <c r="AV234" s="3" t="n"/>
+      <c r="AW234" s="3" t="n"/>
+      <c r="AX234" s="3" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="3" t="n"/>
@@ -11467,6 +13175,13 @@
       <c r="AO235" s="3" t="n"/>
       <c r="AP235" s="3" t="n"/>
       <c r="AQ235" s="3" t="n"/>
+      <c r="AR235" s="3" t="n"/>
+      <c r="AS235" s="3" t="n"/>
+      <c r="AT235" s="3" t="n"/>
+      <c r="AU235" s="3" t="n"/>
+      <c r="AV235" s="3" t="n"/>
+      <c r="AW235" s="3" t="n"/>
+      <c r="AX235" s="3" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="3" t="n"/>
@@ -11512,6 +13227,13 @@
       <c r="AO236" s="3" t="n"/>
       <c r="AP236" s="3" t="n"/>
       <c r="AQ236" s="3" t="n"/>
+      <c r="AR236" s="3" t="n"/>
+      <c r="AS236" s="3" t="n"/>
+      <c r="AT236" s="3" t="n"/>
+      <c r="AU236" s="3" t="n"/>
+      <c r="AV236" s="3" t="n"/>
+      <c r="AW236" s="3" t="n"/>
+      <c r="AX236" s="3" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="3" t="n"/>
@@ -11557,6 +13279,13 @@
       <c r="AO237" s="3" t="n"/>
       <c r="AP237" s="3" t="n"/>
       <c r="AQ237" s="3" t="n"/>
+      <c r="AR237" s="3" t="n"/>
+      <c r="AS237" s="3" t="n"/>
+      <c r="AT237" s="3" t="n"/>
+      <c r="AU237" s="3" t="n"/>
+      <c r="AV237" s="3" t="n"/>
+      <c r="AW237" s="3" t="n"/>
+      <c r="AX237" s="3" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="3" t="n"/>
@@ -11602,6 +13331,13 @@
       <c r="AO238" s="3" t="n"/>
       <c r="AP238" s="3" t="n"/>
       <c r="AQ238" s="3" t="n"/>
+      <c r="AR238" s="3" t="n"/>
+      <c r="AS238" s="3" t="n"/>
+      <c r="AT238" s="3" t="n"/>
+      <c r="AU238" s="3" t="n"/>
+      <c r="AV238" s="3" t="n"/>
+      <c r="AW238" s="3" t="n"/>
+      <c r="AX238" s="3" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="3" t="n"/>
@@ -11647,6 +13383,13 @@
       <c r="AO239" s="3" t="n"/>
       <c r="AP239" s="3" t="n"/>
       <c r="AQ239" s="3" t="n"/>
+      <c r="AR239" s="3" t="n"/>
+      <c r="AS239" s="3" t="n"/>
+      <c r="AT239" s="3" t="n"/>
+      <c r="AU239" s="3" t="n"/>
+      <c r="AV239" s="3" t="n"/>
+      <c r="AW239" s="3" t="n"/>
+      <c r="AX239" s="3" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="3" t="n"/>
@@ -11692,6 +13435,13 @@
       <c r="AO240" s="3" t="n"/>
       <c r="AP240" s="3" t="n"/>
       <c r="AQ240" s="3" t="n"/>
+      <c r="AR240" s="3" t="n"/>
+      <c r="AS240" s="3" t="n"/>
+      <c r="AT240" s="3" t="n"/>
+      <c r="AU240" s="3" t="n"/>
+      <c r="AV240" s="3" t="n"/>
+      <c r="AW240" s="3" t="n"/>
+      <c r="AX240" s="3" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="3" t="n"/>
@@ -11737,6 +13487,13 @@
       <c r="AO241" s="3" t="n"/>
       <c r="AP241" s="3" t="n"/>
       <c r="AQ241" s="3" t="n"/>
+      <c r="AR241" s="3" t="n"/>
+      <c r="AS241" s="3" t="n"/>
+      <c r="AT241" s="3" t="n"/>
+      <c r="AU241" s="3" t="n"/>
+      <c r="AV241" s="3" t="n"/>
+      <c r="AW241" s="3" t="n"/>
+      <c r="AX241" s="3" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="3" t="n"/>
@@ -11782,6 +13539,13 @@
       <c r="AO242" s="3" t="n"/>
       <c r="AP242" s="3" t="n"/>
       <c r="AQ242" s="3" t="n"/>
+      <c r="AR242" s="3" t="n"/>
+      <c r="AS242" s="3" t="n"/>
+      <c r="AT242" s="3" t="n"/>
+      <c r="AU242" s="3" t="n"/>
+      <c r="AV242" s="3" t="n"/>
+      <c r="AW242" s="3" t="n"/>
+      <c r="AX242" s="3" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="3" t="n"/>
@@ -11827,6 +13591,13 @@
       <c r="AO243" s="3" t="n"/>
       <c r="AP243" s="3" t="n"/>
       <c r="AQ243" s="3" t="n"/>
+      <c r="AR243" s="3" t="n"/>
+      <c r="AS243" s="3" t="n"/>
+      <c r="AT243" s="3" t="n"/>
+      <c r="AU243" s="3" t="n"/>
+      <c r="AV243" s="3" t="n"/>
+      <c r="AW243" s="3" t="n"/>
+      <c r="AX243" s="3" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="3" t="n"/>
@@ -11872,6 +13643,13 @@
       <c r="AO244" s="3" t="n"/>
       <c r="AP244" s="3" t="n"/>
       <c r="AQ244" s="3" t="n"/>
+      <c r="AR244" s="3" t="n"/>
+      <c r="AS244" s="3" t="n"/>
+      <c r="AT244" s="3" t="n"/>
+      <c r="AU244" s="3" t="n"/>
+      <c r="AV244" s="3" t="n"/>
+      <c r="AW244" s="3" t="n"/>
+      <c r="AX244" s="3" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="3" t="n"/>
@@ -11917,6 +13695,13 @@
       <c r="AO245" s="3" t="n"/>
       <c r="AP245" s="3" t="n"/>
       <c r="AQ245" s="3" t="n"/>
+      <c r="AR245" s="3" t="n"/>
+      <c r="AS245" s="3" t="n"/>
+      <c r="AT245" s="3" t="n"/>
+      <c r="AU245" s="3" t="n"/>
+      <c r="AV245" s="3" t="n"/>
+      <c r="AW245" s="3" t="n"/>
+      <c r="AX245" s="3" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="3" t="n"/>
@@ -11962,6 +13747,13 @@
       <c r="AO246" s="3" t="n"/>
       <c r="AP246" s="3" t="n"/>
       <c r="AQ246" s="3" t="n"/>
+      <c r="AR246" s="3" t="n"/>
+      <c r="AS246" s="3" t="n"/>
+      <c r="AT246" s="3" t="n"/>
+      <c r="AU246" s="3" t="n"/>
+      <c r="AV246" s="3" t="n"/>
+      <c r="AW246" s="3" t="n"/>
+      <c r="AX246" s="3" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="3" t="n"/>
@@ -12007,6 +13799,13 @@
       <c r="AO247" s="3" t="n"/>
       <c r="AP247" s="3" t="n"/>
       <c r="AQ247" s="3" t="n"/>
+      <c r="AR247" s="3" t="n"/>
+      <c r="AS247" s="3" t="n"/>
+      <c r="AT247" s="3" t="n"/>
+      <c r="AU247" s="3" t="n"/>
+      <c r="AV247" s="3" t="n"/>
+      <c r="AW247" s="3" t="n"/>
+      <c r="AX247" s="3" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="3" t="n"/>
@@ -12052,6 +13851,13 @@
       <c r="AO248" s="3" t="n"/>
       <c r="AP248" s="3" t="n"/>
       <c r="AQ248" s="3" t="n"/>
+      <c r="AR248" s="3" t="n"/>
+      <c r="AS248" s="3" t="n"/>
+      <c r="AT248" s="3" t="n"/>
+      <c r="AU248" s="3" t="n"/>
+      <c r="AV248" s="3" t="n"/>
+      <c r="AW248" s="3" t="n"/>
+      <c r="AX248" s="3" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="3" t="n"/>
@@ -12097,6 +13903,13 @@
       <c r="AO249" s="3" t="n"/>
       <c r="AP249" s="3" t="n"/>
       <c r="AQ249" s="3" t="n"/>
+      <c r="AR249" s="3" t="n"/>
+      <c r="AS249" s="3" t="n"/>
+      <c r="AT249" s="3" t="n"/>
+      <c r="AU249" s="3" t="n"/>
+      <c r="AV249" s="3" t="n"/>
+      <c r="AW249" s="3" t="n"/>
+      <c r="AX249" s="3" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="3" t="n"/>
@@ -12142,6 +13955,13 @@
       <c r="AO250" s="3" t="n"/>
       <c r="AP250" s="3" t="n"/>
       <c r="AQ250" s="3" t="n"/>
+      <c r="AR250" s="3" t="n"/>
+      <c r="AS250" s="3" t="n"/>
+      <c r="AT250" s="3" t="n"/>
+      <c r="AU250" s="3" t="n"/>
+      <c r="AV250" s="3" t="n"/>
+      <c r="AW250" s="3" t="n"/>
+      <c r="AX250" s="3" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="3" t="n"/>
@@ -12187,6 +14007,13 @@
       <c r="AO251" s="3" t="n"/>
       <c r="AP251" s="3" t="n"/>
       <c r="AQ251" s="3" t="n"/>
+      <c r="AR251" s="3" t="n"/>
+      <c r="AS251" s="3" t="n"/>
+      <c r="AT251" s="3" t="n"/>
+      <c r="AU251" s="3" t="n"/>
+      <c r="AV251" s="3" t="n"/>
+      <c r="AW251" s="3" t="n"/>
+      <c r="AX251" s="3" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="3" t="n"/>
@@ -12232,6 +14059,13 @@
       <c r="AO252" s="3" t="n"/>
       <c r="AP252" s="3" t="n"/>
       <c r="AQ252" s="3" t="n"/>
+      <c r="AR252" s="3" t="n"/>
+      <c r="AS252" s="3" t="n"/>
+      <c r="AT252" s="3" t="n"/>
+      <c r="AU252" s="3" t="n"/>
+      <c r="AV252" s="3" t="n"/>
+      <c r="AW252" s="3" t="n"/>
+      <c r="AX252" s="3" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="3" t="n"/>
@@ -12277,6 +14111,13 @@
       <c r="AO253" s="3" t="n"/>
       <c r="AP253" s="3" t="n"/>
       <c r="AQ253" s="3" t="n"/>
+      <c r="AR253" s="3" t="n"/>
+      <c r="AS253" s="3" t="n"/>
+      <c r="AT253" s="3" t="n"/>
+      <c r="AU253" s="3" t="n"/>
+      <c r="AV253" s="3" t="n"/>
+      <c r="AW253" s="3" t="n"/>
+      <c r="AX253" s="3" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="3" t="n"/>
@@ -12322,6 +14163,13 @@
       <c r="AO254" s="3" t="n"/>
       <c r="AP254" s="3" t="n"/>
       <c r="AQ254" s="3" t="n"/>
+      <c r="AR254" s="3" t="n"/>
+      <c r="AS254" s="3" t="n"/>
+      <c r="AT254" s="3" t="n"/>
+      <c r="AU254" s="3" t="n"/>
+      <c r="AV254" s="3" t="n"/>
+      <c r="AW254" s="3" t="n"/>
+      <c r="AX254" s="3" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="3" t="n"/>
@@ -12367,6 +14215,13 @@
       <c r="AO255" s="3" t="n"/>
       <c r="AP255" s="3" t="n"/>
       <c r="AQ255" s="3" t="n"/>
+      <c r="AR255" s="3" t="n"/>
+      <c r="AS255" s="3" t="n"/>
+      <c r="AT255" s="3" t="n"/>
+      <c r="AU255" s="3" t="n"/>
+      <c r="AV255" s="3" t="n"/>
+      <c r="AW255" s="3" t="n"/>
+      <c r="AX255" s="3" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="3" t="n"/>
@@ -12412,6 +14267,13 @@
       <c r="AO256" s="3" t="n"/>
       <c r="AP256" s="3" t="n"/>
       <c r="AQ256" s="3" t="n"/>
+      <c r="AR256" s="3" t="n"/>
+      <c r="AS256" s="3" t="n"/>
+      <c r="AT256" s="3" t="n"/>
+      <c r="AU256" s="3" t="n"/>
+      <c r="AV256" s="3" t="n"/>
+      <c r="AW256" s="3" t="n"/>
+      <c r="AX256" s="3" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="3" t="n"/>
@@ -12457,6 +14319,13 @@
       <c r="AO257" s="3" t="n"/>
       <c r="AP257" s="3" t="n"/>
       <c r="AQ257" s="3" t="n"/>
+      <c r="AR257" s="3" t="n"/>
+      <c r="AS257" s="3" t="n"/>
+      <c r="AT257" s="3" t="n"/>
+      <c r="AU257" s="3" t="n"/>
+      <c r="AV257" s="3" t="n"/>
+      <c r="AW257" s="3" t="n"/>
+      <c r="AX257" s="3" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="3" t="n"/>
@@ -12502,6 +14371,13 @@
       <c r="AO258" s="3" t="n"/>
       <c r="AP258" s="3" t="n"/>
       <c r="AQ258" s="3" t="n"/>
+      <c r="AR258" s="3" t="n"/>
+      <c r="AS258" s="3" t="n"/>
+      <c r="AT258" s="3" t="n"/>
+      <c r="AU258" s="3" t="n"/>
+      <c r="AV258" s="3" t="n"/>
+      <c r="AW258" s="3" t="n"/>
+      <c r="AX258" s="3" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="3" t="n"/>
@@ -12547,6 +14423,13 @@
       <c r="AO259" s="3" t="n"/>
       <c r="AP259" s="3" t="n"/>
       <c r="AQ259" s="3" t="n"/>
+      <c r="AR259" s="3" t="n"/>
+      <c r="AS259" s="3" t="n"/>
+      <c r="AT259" s="3" t="n"/>
+      <c r="AU259" s="3" t="n"/>
+      <c r="AV259" s="3" t="n"/>
+      <c r="AW259" s="3" t="n"/>
+      <c r="AX259" s="3" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="3" t="n"/>
@@ -12592,6 +14475,13 @@
       <c r="AO260" s="3" t="n"/>
       <c r="AP260" s="3" t="n"/>
       <c r="AQ260" s="3" t="n"/>
+      <c r="AR260" s="3" t="n"/>
+      <c r="AS260" s="3" t="n"/>
+      <c r="AT260" s="3" t="n"/>
+      <c r="AU260" s="3" t="n"/>
+      <c r="AV260" s="3" t="n"/>
+      <c r="AW260" s="3" t="n"/>
+      <c r="AX260" s="3" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="3" t="n"/>
@@ -12637,6 +14527,13 @@
       <c r="AO261" s="3" t="n"/>
       <c r="AP261" s="3" t="n"/>
       <c r="AQ261" s="3" t="n"/>
+      <c r="AR261" s="3" t="n"/>
+      <c r="AS261" s="3" t="n"/>
+      <c r="AT261" s="3" t="n"/>
+      <c r="AU261" s="3" t="n"/>
+      <c r="AV261" s="3" t="n"/>
+      <c r="AW261" s="3" t="n"/>
+      <c r="AX261" s="3" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="3" t="n"/>
@@ -12682,6 +14579,13 @@
       <c r="AO262" s="3" t="n"/>
       <c r="AP262" s="3" t="n"/>
       <c r="AQ262" s="3" t="n"/>
+      <c r="AR262" s="3" t="n"/>
+      <c r="AS262" s="3" t="n"/>
+      <c r="AT262" s="3" t="n"/>
+      <c r="AU262" s="3" t="n"/>
+      <c r="AV262" s="3" t="n"/>
+      <c r="AW262" s="3" t="n"/>
+      <c r="AX262" s="3" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="3" t="n"/>
@@ -12727,6 +14631,13 @@
       <c r="AO263" s="3" t="n"/>
       <c r="AP263" s="3" t="n"/>
       <c r="AQ263" s="3" t="n"/>
+      <c r="AR263" s="3" t="n"/>
+      <c r="AS263" s="3" t="n"/>
+      <c r="AT263" s="3" t="n"/>
+      <c r="AU263" s="3" t="n"/>
+      <c r="AV263" s="3" t="n"/>
+      <c r="AW263" s="3" t="n"/>
+      <c r="AX263" s="3" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="3" t="n"/>
@@ -12772,6 +14683,13 @@
       <c r="AO264" s="3" t="n"/>
       <c r="AP264" s="3" t="n"/>
       <c r="AQ264" s="3" t="n"/>
+      <c r="AR264" s="3" t="n"/>
+      <c r="AS264" s="3" t="n"/>
+      <c r="AT264" s="3" t="n"/>
+      <c r="AU264" s="3" t="n"/>
+      <c r="AV264" s="3" t="n"/>
+      <c r="AW264" s="3" t="n"/>
+      <c r="AX264" s="3" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="3" t="n"/>
@@ -12817,6 +14735,13 @@
       <c r="AO265" s="3" t="n"/>
       <c r="AP265" s="3" t="n"/>
       <c r="AQ265" s="3" t="n"/>
+      <c r="AR265" s="3" t="n"/>
+      <c r="AS265" s="3" t="n"/>
+      <c r="AT265" s="3" t="n"/>
+      <c r="AU265" s="3" t="n"/>
+      <c r="AV265" s="3" t="n"/>
+      <c r="AW265" s="3" t="n"/>
+      <c r="AX265" s="3" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="3" t="n"/>
@@ -12862,6 +14787,13 @@
       <c r="AO266" s="3" t="n"/>
       <c r="AP266" s="3" t="n"/>
       <c r="AQ266" s="3" t="n"/>
+      <c r="AR266" s="3" t="n"/>
+      <c r="AS266" s="3" t="n"/>
+      <c r="AT266" s="3" t="n"/>
+      <c r="AU266" s="3" t="n"/>
+      <c r="AV266" s="3" t="n"/>
+      <c r="AW266" s="3" t="n"/>
+      <c r="AX266" s="3" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="3" t="n"/>
@@ -12907,6 +14839,13 @@
       <c r="AO267" s="3" t="n"/>
       <c r="AP267" s="3" t="n"/>
       <c r="AQ267" s="3" t="n"/>
+      <c r="AR267" s="3" t="n"/>
+      <c r="AS267" s="3" t="n"/>
+      <c r="AT267" s="3" t="n"/>
+      <c r="AU267" s="3" t="n"/>
+      <c r="AV267" s="3" t="n"/>
+      <c r="AW267" s="3" t="n"/>
+      <c r="AX267" s="3" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="3" t="n"/>
@@ -12952,6 +14891,13 @@
       <c r="AO268" s="3" t="n"/>
       <c r="AP268" s="3" t="n"/>
       <c r="AQ268" s="3" t="n"/>
+      <c r="AR268" s="3" t="n"/>
+      <c r="AS268" s="3" t="n"/>
+      <c r="AT268" s="3" t="n"/>
+      <c r="AU268" s="3" t="n"/>
+      <c r="AV268" s="3" t="n"/>
+      <c r="AW268" s="3" t="n"/>
+      <c r="AX268" s="3" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="3" t="n"/>
@@ -12997,6 +14943,13 @@
       <c r="AO269" s="3" t="n"/>
       <c r="AP269" s="3" t="n"/>
       <c r="AQ269" s="3" t="n"/>
+      <c r="AR269" s="3" t="n"/>
+      <c r="AS269" s="3" t="n"/>
+      <c r="AT269" s="3" t="n"/>
+      <c r="AU269" s="3" t="n"/>
+      <c r="AV269" s="3" t="n"/>
+      <c r="AW269" s="3" t="n"/>
+      <c r="AX269" s="3" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="3" t="n"/>
@@ -13042,6 +14995,13 @@
       <c r="AO270" s="3" t="n"/>
       <c r="AP270" s="3" t="n"/>
       <c r="AQ270" s="3" t="n"/>
+      <c r="AR270" s="3" t="n"/>
+      <c r="AS270" s="3" t="n"/>
+      <c r="AT270" s="3" t="n"/>
+      <c r="AU270" s="3" t="n"/>
+      <c r="AV270" s="3" t="n"/>
+      <c r="AW270" s="3" t="n"/>
+      <c r="AX270" s="3" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="3" t="n"/>
@@ -13087,6 +15047,13 @@
       <c r="AO271" s="3" t="n"/>
       <c r="AP271" s="3" t="n"/>
       <c r="AQ271" s="3" t="n"/>
+      <c r="AR271" s="3" t="n"/>
+      <c r="AS271" s="3" t="n"/>
+      <c r="AT271" s="3" t="n"/>
+      <c r="AU271" s="3" t="n"/>
+      <c r="AV271" s="3" t="n"/>
+      <c r="AW271" s="3" t="n"/>
+      <c r="AX271" s="3" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="3" t="n"/>
@@ -13132,6 +15099,13 @@
       <c r="AO272" s="3" t="n"/>
       <c r="AP272" s="3" t="n"/>
       <c r="AQ272" s="3" t="n"/>
+      <c r="AR272" s="3" t="n"/>
+      <c r="AS272" s="3" t="n"/>
+      <c r="AT272" s="3" t="n"/>
+      <c r="AU272" s="3" t="n"/>
+      <c r="AV272" s="3" t="n"/>
+      <c r="AW272" s="3" t="n"/>
+      <c r="AX272" s="3" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="3" t="n"/>
@@ -13177,6 +15151,13 @@
       <c r="AO273" s="3" t="n"/>
       <c r="AP273" s="3" t="n"/>
       <c r="AQ273" s="3" t="n"/>
+      <c r="AR273" s="3" t="n"/>
+      <c r="AS273" s="3" t="n"/>
+      <c r="AT273" s="3" t="n"/>
+      <c r="AU273" s="3" t="n"/>
+      <c r="AV273" s="3" t="n"/>
+      <c r="AW273" s="3" t="n"/>
+      <c r="AX273" s="3" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="3" t="n"/>
@@ -13222,6 +15203,13 @@
       <c r="AO274" s="3" t="n"/>
       <c r="AP274" s="3" t="n"/>
       <c r="AQ274" s="3" t="n"/>
+      <c r="AR274" s="3" t="n"/>
+      <c r="AS274" s="3" t="n"/>
+      <c r="AT274" s="3" t="n"/>
+      <c r="AU274" s="3" t="n"/>
+      <c r="AV274" s="3" t="n"/>
+      <c r="AW274" s="3" t="n"/>
+      <c r="AX274" s="3" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="3" t="n"/>
@@ -13267,6 +15255,13 @@
       <c r="AO275" s="3" t="n"/>
       <c r="AP275" s="3" t="n"/>
       <c r="AQ275" s="3" t="n"/>
+      <c r="AR275" s="3" t="n"/>
+      <c r="AS275" s="3" t="n"/>
+      <c r="AT275" s="3" t="n"/>
+      <c r="AU275" s="3" t="n"/>
+      <c r="AV275" s="3" t="n"/>
+      <c r="AW275" s="3" t="n"/>
+      <c r="AX275" s="3" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="3" t="n"/>
@@ -13312,6 +15307,13 @@
       <c r="AO276" s="3" t="n"/>
       <c r="AP276" s="3" t="n"/>
       <c r="AQ276" s="3" t="n"/>
+      <c r="AR276" s="3" t="n"/>
+      <c r="AS276" s="3" t="n"/>
+      <c r="AT276" s="3" t="n"/>
+      <c r="AU276" s="3" t="n"/>
+      <c r="AV276" s="3" t="n"/>
+      <c r="AW276" s="3" t="n"/>
+      <c r="AX276" s="3" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="3" t="n"/>
@@ -13357,6 +15359,13 @@
       <c r="AO277" s="3" t="n"/>
       <c r="AP277" s="3" t="n"/>
       <c r="AQ277" s="3" t="n"/>
+      <c r="AR277" s="3" t="n"/>
+      <c r="AS277" s="3" t="n"/>
+      <c r="AT277" s="3" t="n"/>
+      <c r="AU277" s="3" t="n"/>
+      <c r="AV277" s="3" t="n"/>
+      <c r="AW277" s="3" t="n"/>
+      <c r="AX277" s="3" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="3" t="n"/>
@@ -13402,6 +15411,13 @@
       <c r="AO278" s="3" t="n"/>
       <c r="AP278" s="3" t="n"/>
       <c r="AQ278" s="3" t="n"/>
+      <c r="AR278" s="3" t="n"/>
+      <c r="AS278" s="3" t="n"/>
+      <c r="AT278" s="3" t="n"/>
+      <c r="AU278" s="3" t="n"/>
+      <c r="AV278" s="3" t="n"/>
+      <c r="AW278" s="3" t="n"/>
+      <c r="AX278" s="3" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="3" t="n"/>
@@ -13447,6 +15463,13 @@
       <c r="AO279" s="3" t="n"/>
       <c r="AP279" s="3" t="n"/>
       <c r="AQ279" s="3" t="n"/>
+      <c r="AR279" s="3" t="n"/>
+      <c r="AS279" s="3" t="n"/>
+      <c r="AT279" s="3" t="n"/>
+      <c r="AU279" s="3" t="n"/>
+      <c r="AV279" s="3" t="n"/>
+      <c r="AW279" s="3" t="n"/>
+      <c r="AX279" s="3" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="3" t="n"/>
@@ -13492,6 +15515,13 @@
       <c r="AO280" s="3" t="n"/>
       <c r="AP280" s="3" t="n"/>
       <c r="AQ280" s="3" t="n"/>
+      <c r="AR280" s="3" t="n"/>
+      <c r="AS280" s="3" t="n"/>
+      <c r="AT280" s="3" t="n"/>
+      <c r="AU280" s="3" t="n"/>
+      <c r="AV280" s="3" t="n"/>
+      <c r="AW280" s="3" t="n"/>
+      <c r="AX280" s="3" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="3" t="n"/>
@@ -13537,6 +15567,13 @@
       <c r="AO281" s="3" t="n"/>
       <c r="AP281" s="3" t="n"/>
       <c r="AQ281" s="3" t="n"/>
+      <c r="AR281" s="3" t="n"/>
+      <c r="AS281" s="3" t="n"/>
+      <c r="AT281" s="3" t="n"/>
+      <c r="AU281" s="3" t="n"/>
+      <c r="AV281" s="3" t="n"/>
+      <c r="AW281" s="3" t="n"/>
+      <c r="AX281" s="3" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="3" t="n"/>
@@ -13582,6 +15619,13 @@
       <c r="AO282" s="3" t="n"/>
       <c r="AP282" s="3" t="n"/>
       <c r="AQ282" s="3" t="n"/>
+      <c r="AR282" s="3" t="n"/>
+      <c r="AS282" s="3" t="n"/>
+      <c r="AT282" s="3" t="n"/>
+      <c r="AU282" s="3" t="n"/>
+      <c r="AV282" s="3" t="n"/>
+      <c r="AW282" s="3" t="n"/>
+      <c r="AX282" s="3" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="3" t="n"/>
@@ -13627,6 +15671,13 @@
       <c r="AO283" s="3" t="n"/>
       <c r="AP283" s="3" t="n"/>
       <c r="AQ283" s="3" t="n"/>
+      <c r="AR283" s="3" t="n"/>
+      <c r="AS283" s="3" t="n"/>
+      <c r="AT283" s="3" t="n"/>
+      <c r="AU283" s="3" t="n"/>
+      <c r="AV283" s="3" t="n"/>
+      <c r="AW283" s="3" t="n"/>
+      <c r="AX283" s="3" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="3" t="n"/>
@@ -13672,6 +15723,13 @@
       <c r="AO284" s="3" t="n"/>
       <c r="AP284" s="3" t="n"/>
       <c r="AQ284" s="3" t="n"/>
+      <c r="AR284" s="3" t="n"/>
+      <c r="AS284" s="3" t="n"/>
+      <c r="AT284" s="3" t="n"/>
+      <c r="AU284" s="3" t="n"/>
+      <c r="AV284" s="3" t="n"/>
+      <c r="AW284" s="3" t="n"/>
+      <c r="AX284" s="3" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="3" t="n"/>
@@ -13717,6 +15775,13 @@
       <c r="AO285" s="3" t="n"/>
       <c r="AP285" s="3" t="n"/>
       <c r="AQ285" s="3" t="n"/>
+      <c r="AR285" s="3" t="n"/>
+      <c r="AS285" s="3" t="n"/>
+      <c r="AT285" s="3" t="n"/>
+      <c r="AU285" s="3" t="n"/>
+      <c r="AV285" s="3" t="n"/>
+      <c r="AW285" s="3" t="n"/>
+      <c r="AX285" s="3" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="3" t="n"/>
@@ -13762,6 +15827,13 @@
       <c r="AO286" s="3" t="n"/>
       <c r="AP286" s="3" t="n"/>
       <c r="AQ286" s="3" t="n"/>
+      <c r="AR286" s="3" t="n"/>
+      <c r="AS286" s="3" t="n"/>
+      <c r="AT286" s="3" t="n"/>
+      <c r="AU286" s="3" t="n"/>
+      <c r="AV286" s="3" t="n"/>
+      <c r="AW286" s="3" t="n"/>
+      <c r="AX286" s="3" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="3" t="n"/>
@@ -13807,6 +15879,13 @@
       <c r="AO287" s="3" t="n"/>
       <c r="AP287" s="3" t="n"/>
       <c r="AQ287" s="3" t="n"/>
+      <c r="AR287" s="3" t="n"/>
+      <c r="AS287" s="3" t="n"/>
+      <c r="AT287" s="3" t="n"/>
+      <c r="AU287" s="3" t="n"/>
+      <c r="AV287" s="3" t="n"/>
+      <c r="AW287" s="3" t="n"/>
+      <c r="AX287" s="3" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="3" t="n"/>
@@ -13852,6 +15931,13 @@
       <c r="AO288" s="3" t="n"/>
       <c r="AP288" s="3" t="n"/>
       <c r="AQ288" s="3" t="n"/>
+      <c r="AR288" s="3" t="n"/>
+      <c r="AS288" s="3" t="n"/>
+      <c r="AT288" s="3" t="n"/>
+      <c r="AU288" s="3" t="n"/>
+      <c r="AV288" s="3" t="n"/>
+      <c r="AW288" s="3" t="n"/>
+      <c r="AX288" s="3" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="3" t="n"/>
@@ -13897,6 +15983,13 @@
       <c r="AO289" s="3" t="n"/>
       <c r="AP289" s="3" t="n"/>
       <c r="AQ289" s="3" t="n"/>
+      <c r="AR289" s="3" t="n"/>
+      <c r="AS289" s="3" t="n"/>
+      <c r="AT289" s="3" t="n"/>
+      <c r="AU289" s="3" t="n"/>
+      <c r="AV289" s="3" t="n"/>
+      <c r="AW289" s="3" t="n"/>
+      <c r="AX289" s="3" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="3" t="n"/>
@@ -13942,6 +16035,13 @@
       <c r="AO290" s="3" t="n"/>
       <c r="AP290" s="3" t="n"/>
       <c r="AQ290" s="3" t="n"/>
+      <c r="AR290" s="3" t="n"/>
+      <c r="AS290" s="3" t="n"/>
+      <c r="AT290" s="3" t="n"/>
+      <c r="AU290" s="3" t="n"/>
+      <c r="AV290" s="3" t="n"/>
+      <c r="AW290" s="3" t="n"/>
+      <c r="AX290" s="3" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="3" t="n"/>
@@ -13987,6 +16087,13 @@
       <c r="AO291" s="3" t="n"/>
       <c r="AP291" s="3" t="n"/>
       <c r="AQ291" s="3" t="n"/>
+      <c r="AR291" s="3" t="n"/>
+      <c r="AS291" s="3" t="n"/>
+      <c r="AT291" s="3" t="n"/>
+      <c r="AU291" s="3" t="n"/>
+      <c r="AV291" s="3" t="n"/>
+      <c r="AW291" s="3" t="n"/>
+      <c r="AX291" s="3" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="3" t="n"/>
@@ -14032,6 +16139,13 @@
       <c r="AO292" s="3" t="n"/>
       <c r="AP292" s="3" t="n"/>
       <c r="AQ292" s="3" t="n"/>
+      <c r="AR292" s="3" t="n"/>
+      <c r="AS292" s="3" t="n"/>
+      <c r="AT292" s="3" t="n"/>
+      <c r="AU292" s="3" t="n"/>
+      <c r="AV292" s="3" t="n"/>
+      <c r="AW292" s="3" t="n"/>
+      <c r="AX292" s="3" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="3" t="n"/>
@@ -14077,6 +16191,13 @@
       <c r="AO293" s="3" t="n"/>
       <c r="AP293" s="3" t="n"/>
       <c r="AQ293" s="3" t="n"/>
+      <c r="AR293" s="3" t="n"/>
+      <c r="AS293" s="3" t="n"/>
+      <c r="AT293" s="3" t="n"/>
+      <c r="AU293" s="3" t="n"/>
+      <c r="AV293" s="3" t="n"/>
+      <c r="AW293" s="3" t="n"/>
+      <c r="AX293" s="3" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="3" t="n"/>
@@ -14122,6 +16243,13 @@
       <c r="AO294" s="3" t="n"/>
       <c r="AP294" s="3" t="n"/>
       <c r="AQ294" s="3" t="n"/>
+      <c r="AR294" s="3" t="n"/>
+      <c r="AS294" s="3" t="n"/>
+      <c r="AT294" s="3" t="n"/>
+      <c r="AU294" s="3" t="n"/>
+      <c r="AV294" s="3" t="n"/>
+      <c r="AW294" s="3" t="n"/>
+      <c r="AX294" s="3" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="3" t="n"/>
@@ -14167,6 +16295,13 @@
       <c r="AO295" s="3" t="n"/>
       <c r="AP295" s="3" t="n"/>
       <c r="AQ295" s="3" t="n"/>
+      <c r="AR295" s="3" t="n"/>
+      <c r="AS295" s="3" t="n"/>
+      <c r="AT295" s="3" t="n"/>
+      <c r="AU295" s="3" t="n"/>
+      <c r="AV295" s="3" t="n"/>
+      <c r="AW295" s="3" t="n"/>
+      <c r="AX295" s="3" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="3" t="n"/>
@@ -14212,6 +16347,13 @@
       <c r="AO296" s="3" t="n"/>
       <c r="AP296" s="3" t="n"/>
       <c r="AQ296" s="3" t="n"/>
+      <c r="AR296" s="3" t="n"/>
+      <c r="AS296" s="3" t="n"/>
+      <c r="AT296" s="3" t="n"/>
+      <c r="AU296" s="3" t="n"/>
+      <c r="AV296" s="3" t="n"/>
+      <c r="AW296" s="3" t="n"/>
+      <c r="AX296" s="3" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="3" t="n"/>
@@ -14257,6 +16399,13 @@
       <c r="AO297" s="3" t="n"/>
       <c r="AP297" s="3" t="n"/>
       <c r="AQ297" s="3" t="n"/>
+      <c r="AR297" s="3" t="n"/>
+      <c r="AS297" s="3" t="n"/>
+      <c r="AT297" s="3" t="n"/>
+      <c r="AU297" s="3" t="n"/>
+      <c r="AV297" s="3" t="n"/>
+      <c r="AW297" s="3" t="n"/>
+      <c r="AX297" s="3" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="3" t="n"/>
@@ -14302,6 +16451,13 @@
       <c r="AO298" s="3" t="n"/>
       <c r="AP298" s="3" t="n"/>
       <c r="AQ298" s="3" t="n"/>
+      <c r="AR298" s="3" t="n"/>
+      <c r="AS298" s="3" t="n"/>
+      <c r="AT298" s="3" t="n"/>
+      <c r="AU298" s="3" t="n"/>
+      <c r="AV298" s="3" t="n"/>
+      <c r="AW298" s="3" t="n"/>
+      <c r="AX298" s="3" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="3" t="n"/>
@@ -14347,6 +16503,13 @@
       <c r="AO299" s="3" t="n"/>
       <c r="AP299" s="3" t="n"/>
       <c r="AQ299" s="3" t="n"/>
+      <c r="AR299" s="3" t="n"/>
+      <c r="AS299" s="3" t="n"/>
+      <c r="AT299" s="3" t="n"/>
+      <c r="AU299" s="3" t="n"/>
+      <c r="AV299" s="3" t="n"/>
+      <c r="AW299" s="3" t="n"/>
+      <c r="AX299" s="3" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="3" t="n"/>
@@ -14392,6 +16555,13 @@
       <c r="AO300" s="3" t="n"/>
       <c r="AP300" s="3" t="n"/>
       <c r="AQ300" s="3" t="n"/>
+      <c r="AR300" s="3" t="n"/>
+      <c r="AS300" s="3" t="n"/>
+      <c r="AT300" s="3" t="n"/>
+      <c r="AU300" s="3" t="n"/>
+      <c r="AV300" s="3" t="n"/>
+      <c r="AW300" s="3" t="n"/>
+      <c r="AX300" s="3" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="3" t="n"/>
@@ -14437,6 +16607,13 @@
       <c r="AO301" s="3" t="n"/>
       <c r="AP301" s="3" t="n"/>
       <c r="AQ301" s="3" t="n"/>
+      <c r="AR301" s="3" t="n"/>
+      <c r="AS301" s="3" t="n"/>
+      <c r="AT301" s="3" t="n"/>
+      <c r="AU301" s="3" t="n"/>
+      <c r="AV301" s="3" t="n"/>
+      <c r="AW301" s="3" t="n"/>
+      <c r="AX301" s="3" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="3" t="n"/>
@@ -14482,6 +16659,13 @@
       <c r="AO302" s="3" t="n"/>
       <c r="AP302" s="3" t="n"/>
       <c r="AQ302" s="3" t="n"/>
+      <c r="AR302" s="3" t="n"/>
+      <c r="AS302" s="3" t="n"/>
+      <c r="AT302" s="3" t="n"/>
+      <c r="AU302" s="3" t="n"/>
+      <c r="AV302" s="3" t="n"/>
+      <c r="AW302" s="3" t="n"/>
+      <c r="AX302" s="3" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="3" t="n"/>
@@ -14527,6 +16711,13 @@
       <c r="AO303" s="3" t="n"/>
       <c r="AP303" s="3" t="n"/>
       <c r="AQ303" s="3" t="n"/>
+      <c r="AR303" s="3" t="n"/>
+      <c r="AS303" s="3" t="n"/>
+      <c r="AT303" s="3" t="n"/>
+      <c r="AU303" s="3" t="n"/>
+      <c r="AV303" s="3" t="n"/>
+      <c r="AW303" s="3" t="n"/>
+      <c r="AX303" s="3" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="3" t="n"/>
@@ -14572,6 +16763,13 @@
       <c r="AO304" s="3" t="n"/>
       <c r="AP304" s="3" t="n"/>
       <c r="AQ304" s="3" t="n"/>
+      <c r="AR304" s="3" t="n"/>
+      <c r="AS304" s="3" t="n"/>
+      <c r="AT304" s="3" t="n"/>
+      <c r="AU304" s="3" t="n"/>
+      <c r="AV304" s="3" t="n"/>
+      <c r="AW304" s="3" t="n"/>
+      <c r="AX304" s="3" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="3" t="n"/>
@@ -14617,6 +16815,13 @@
       <c r="AO305" s="3" t="n"/>
       <c r="AP305" s="3" t="n"/>
       <c r="AQ305" s="3" t="n"/>
+      <c r="AR305" s="3" t="n"/>
+      <c r="AS305" s="3" t="n"/>
+      <c r="AT305" s="3" t="n"/>
+      <c r="AU305" s="3" t="n"/>
+      <c r="AV305" s="3" t="n"/>
+      <c r="AW305" s="3" t="n"/>
+      <c r="AX305" s="3" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="3" t="n"/>
@@ -14662,6 +16867,13 @@
       <c r="AO306" s="3" t="n"/>
       <c r="AP306" s="3" t="n"/>
       <c r="AQ306" s="3" t="n"/>
+      <c r="AR306" s="3" t="n"/>
+      <c r="AS306" s="3" t="n"/>
+      <c r="AT306" s="3" t="n"/>
+      <c r="AU306" s="3" t="n"/>
+      <c r="AV306" s="3" t="n"/>
+      <c r="AW306" s="3" t="n"/>
+      <c r="AX306" s="3" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="3" t="n"/>
@@ -14707,6 +16919,13 @@
       <c r="AO307" s="3" t="n"/>
       <c r="AP307" s="3" t="n"/>
       <c r="AQ307" s="3" t="n"/>
+      <c r="AR307" s="3" t="n"/>
+      <c r="AS307" s="3" t="n"/>
+      <c r="AT307" s="3" t="n"/>
+      <c r="AU307" s="3" t="n"/>
+      <c r="AV307" s="3" t="n"/>
+      <c r="AW307" s="3" t="n"/>
+      <c r="AX307" s="3" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="3" t="n"/>
@@ -14752,6 +16971,13 @@
       <c r="AO308" s="3" t="n"/>
       <c r="AP308" s="3" t="n"/>
       <c r="AQ308" s="3" t="n"/>
+      <c r="AR308" s="3" t="n"/>
+      <c r="AS308" s="3" t="n"/>
+      <c r="AT308" s="3" t="n"/>
+      <c r="AU308" s="3" t="n"/>
+      <c r="AV308" s="3" t="n"/>
+      <c r="AW308" s="3" t="n"/>
+      <c r="AX308" s="3" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="3" t="n"/>
@@ -14797,6 +17023,13 @@
       <c r="AO309" s="3" t="n"/>
       <c r="AP309" s="3" t="n"/>
       <c r="AQ309" s="3" t="n"/>
+      <c r="AR309" s="3" t="n"/>
+      <c r="AS309" s="3" t="n"/>
+      <c r="AT309" s="3" t="n"/>
+      <c r="AU309" s="3" t="n"/>
+      <c r="AV309" s="3" t="n"/>
+      <c r="AW309" s="3" t="n"/>
+      <c r="AX309" s="3" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="3" t="n"/>
@@ -14842,6 +17075,13 @@
       <c r="AO310" s="3" t="n"/>
       <c r="AP310" s="3" t="n"/>
       <c r="AQ310" s="3" t="n"/>
+      <c r="AR310" s="3" t="n"/>
+      <c r="AS310" s="3" t="n"/>
+      <c r="AT310" s="3" t="n"/>
+      <c r="AU310" s="3" t="n"/>
+      <c r="AV310" s="3" t="n"/>
+      <c r="AW310" s="3" t="n"/>
+      <c r="AX310" s="3" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="3" t="n"/>
@@ -14887,6 +17127,13 @@
       <c r="AO311" s="3" t="n"/>
       <c r="AP311" s="3" t="n"/>
       <c r="AQ311" s="3" t="n"/>
+      <c r="AR311" s="3" t="n"/>
+      <c r="AS311" s="3" t="n"/>
+      <c r="AT311" s="3" t="n"/>
+      <c r="AU311" s="3" t="n"/>
+      <c r="AV311" s="3" t="n"/>
+      <c r="AW311" s="3" t="n"/>
+      <c r="AX311" s="3" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="3" t="n"/>
@@ -14932,6 +17179,13 @@
       <c r="AO312" s="3" t="n"/>
       <c r="AP312" s="3" t="n"/>
       <c r="AQ312" s="3" t="n"/>
+      <c r="AR312" s="3" t="n"/>
+      <c r="AS312" s="3" t="n"/>
+      <c r="AT312" s="3" t="n"/>
+      <c r="AU312" s="3" t="n"/>
+      <c r="AV312" s="3" t="n"/>
+      <c r="AW312" s="3" t="n"/>
+      <c r="AX312" s="3" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="3" t="n"/>
@@ -14977,6 +17231,13 @@
       <c r="AO313" s="3" t="n"/>
       <c r="AP313" s="3" t="n"/>
       <c r="AQ313" s="3" t="n"/>
+      <c r="AR313" s="3" t="n"/>
+      <c r="AS313" s="3" t="n"/>
+      <c r="AT313" s="3" t="n"/>
+      <c r="AU313" s="3" t="n"/>
+      <c r="AV313" s="3" t="n"/>
+      <c r="AW313" s="3" t="n"/>
+      <c r="AX313" s="3" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="3" t="n"/>
@@ -15022,6 +17283,13 @@
       <c r="AO314" s="3" t="n"/>
       <c r="AP314" s="3" t="n"/>
       <c r="AQ314" s="3" t="n"/>
+      <c r="AR314" s="3" t="n"/>
+      <c r="AS314" s="3" t="n"/>
+      <c r="AT314" s="3" t="n"/>
+      <c r="AU314" s="3" t="n"/>
+      <c r="AV314" s="3" t="n"/>
+      <c r="AW314" s="3" t="n"/>
+      <c r="AX314" s="3" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="3" t="n"/>
@@ -15067,6 +17335,13 @@
       <c r="AO315" s="3" t="n"/>
       <c r="AP315" s="3" t="n"/>
       <c r="AQ315" s="3" t="n"/>
+      <c r="AR315" s="3" t="n"/>
+      <c r="AS315" s="3" t="n"/>
+      <c r="AT315" s="3" t="n"/>
+      <c r="AU315" s="3" t="n"/>
+      <c r="AV315" s="3" t="n"/>
+      <c r="AW315" s="3" t="n"/>
+      <c r="AX315" s="3" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="3" t="n"/>
@@ -15112,6 +17387,13 @@
       <c r="AO316" s="3" t="n"/>
       <c r="AP316" s="3" t="n"/>
       <c r="AQ316" s="3" t="n"/>
+      <c r="AR316" s="3" t="n"/>
+      <c r="AS316" s="3" t="n"/>
+      <c r="AT316" s="3" t="n"/>
+      <c r="AU316" s="3" t="n"/>
+      <c r="AV316" s="3" t="n"/>
+      <c r="AW316" s="3" t="n"/>
+      <c r="AX316" s="3" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="3" t="n"/>
@@ -15157,6 +17439,13 @@
       <c r="AO317" s="3" t="n"/>
       <c r="AP317" s="3" t="n"/>
       <c r="AQ317" s="3" t="n"/>
+      <c r="AR317" s="3" t="n"/>
+      <c r="AS317" s="3" t="n"/>
+      <c r="AT317" s="3" t="n"/>
+      <c r="AU317" s="3" t="n"/>
+      <c r="AV317" s="3" t="n"/>
+      <c r="AW317" s="3" t="n"/>
+      <c r="AX317" s="3" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="3" t="n"/>
@@ -15202,6 +17491,13 @@
       <c r="AO318" s="3" t="n"/>
       <c r="AP318" s="3" t="n"/>
       <c r="AQ318" s="3" t="n"/>
+      <c r="AR318" s="3" t="n"/>
+      <c r="AS318" s="3" t="n"/>
+      <c r="AT318" s="3" t="n"/>
+      <c r="AU318" s="3" t="n"/>
+      <c r="AV318" s="3" t="n"/>
+      <c r="AW318" s="3" t="n"/>
+      <c r="AX318" s="3" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="3" t="n"/>
@@ -15247,6 +17543,13 @@
       <c r="AO319" s="3" t="n"/>
       <c r="AP319" s="3" t="n"/>
       <c r="AQ319" s="3" t="n"/>
+      <c r="AR319" s="3" t="n"/>
+      <c r="AS319" s="3" t="n"/>
+      <c r="AT319" s="3" t="n"/>
+      <c r="AU319" s="3" t="n"/>
+      <c r="AV319" s="3" t="n"/>
+      <c r="AW319" s="3" t="n"/>
+      <c r="AX319" s="3" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="3" t="n"/>
@@ -15292,6 +17595,13 @@
       <c r="AO320" s="3" t="n"/>
       <c r="AP320" s="3" t="n"/>
       <c r="AQ320" s="3" t="n"/>
+      <c r="AR320" s="3" t="n"/>
+      <c r="AS320" s="3" t="n"/>
+      <c r="AT320" s="3" t="n"/>
+      <c r="AU320" s="3" t="n"/>
+      <c r="AV320" s="3" t="n"/>
+      <c r="AW320" s="3" t="n"/>
+      <c r="AX320" s="3" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="3" t="n"/>
@@ -15337,6 +17647,13 @@
       <c r="AO321" s="3" t="n"/>
       <c r="AP321" s="3" t="n"/>
       <c r="AQ321" s="3" t="n"/>
+      <c r="AR321" s="3" t="n"/>
+      <c r="AS321" s="3" t="n"/>
+      <c r="AT321" s="3" t="n"/>
+      <c r="AU321" s="3" t="n"/>
+      <c r="AV321" s="3" t="n"/>
+      <c r="AW321" s="3" t="n"/>
+      <c r="AX321" s="3" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="3" t="n"/>
@@ -15382,6 +17699,13 @@
       <c r="AO322" s="3" t="n"/>
       <c r="AP322" s="3" t="n"/>
       <c r="AQ322" s="3" t="n"/>
+      <c r="AR322" s="3" t="n"/>
+      <c r="AS322" s="3" t="n"/>
+      <c r="AT322" s="3" t="n"/>
+      <c r="AU322" s="3" t="n"/>
+      <c r="AV322" s="3" t="n"/>
+      <c r="AW322" s="3" t="n"/>
+      <c r="AX322" s="3" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="3" t="n"/>
@@ -15427,6 +17751,13 @@
       <c r="AO323" s="3" t="n"/>
       <c r="AP323" s="3" t="n"/>
       <c r="AQ323" s="3" t="n"/>
+      <c r="AR323" s="3" t="n"/>
+      <c r="AS323" s="3" t="n"/>
+      <c r="AT323" s="3" t="n"/>
+      <c r="AU323" s="3" t="n"/>
+      <c r="AV323" s="3" t="n"/>
+      <c r="AW323" s="3" t="n"/>
+      <c r="AX323" s="3" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="3" t="n"/>
@@ -15472,6 +17803,13 @@
       <c r="AO324" s="3" t="n"/>
       <c r="AP324" s="3" t="n"/>
       <c r="AQ324" s="3" t="n"/>
+      <c r="AR324" s="3" t="n"/>
+      <c r="AS324" s="3" t="n"/>
+      <c r="AT324" s="3" t="n"/>
+      <c r="AU324" s="3" t="n"/>
+      <c r="AV324" s="3" t="n"/>
+      <c r="AW324" s="3" t="n"/>
+      <c r="AX324" s="3" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="3" t="n"/>
@@ -15517,6 +17855,13 @@
       <c r="AO325" s="3" t="n"/>
       <c r="AP325" s="3" t="n"/>
       <c r="AQ325" s="3" t="n"/>
+      <c r="AR325" s="3" t="n"/>
+      <c r="AS325" s="3" t="n"/>
+      <c r="AT325" s="3" t="n"/>
+      <c r="AU325" s="3" t="n"/>
+      <c r="AV325" s="3" t="n"/>
+      <c r="AW325" s="3" t="n"/>
+      <c r="AX325" s="3" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="3" t="n"/>
@@ -15562,6 +17907,13 @@
       <c r="AO326" s="3" t="n"/>
       <c r="AP326" s="3" t="n"/>
       <c r="AQ326" s="3" t="n"/>
+      <c r="AR326" s="3" t="n"/>
+      <c r="AS326" s="3" t="n"/>
+      <c r="AT326" s="3" t="n"/>
+      <c r="AU326" s="3" t="n"/>
+      <c r="AV326" s="3" t="n"/>
+      <c r="AW326" s="3" t="n"/>
+      <c r="AX326" s="3" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="3" t="n"/>
@@ -15607,6 +17959,13 @@
       <c r="AO327" s="3" t="n"/>
       <c r="AP327" s="3" t="n"/>
       <c r="AQ327" s="3" t="n"/>
+      <c r="AR327" s="3" t="n"/>
+      <c r="AS327" s="3" t="n"/>
+      <c r="AT327" s="3" t="n"/>
+      <c r="AU327" s="3" t="n"/>
+      <c r="AV327" s="3" t="n"/>
+      <c r="AW327" s="3" t="n"/>
+      <c r="AX327" s="3" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="3" t="n"/>
@@ -15652,6 +18011,13 @@
       <c r="AO328" s="3" t="n"/>
       <c r="AP328" s="3" t="n"/>
       <c r="AQ328" s="3" t="n"/>
+      <c r="AR328" s="3" t="n"/>
+      <c r="AS328" s="3" t="n"/>
+      <c r="AT328" s="3" t="n"/>
+      <c r="AU328" s="3" t="n"/>
+      <c r="AV328" s="3" t="n"/>
+      <c r="AW328" s="3" t="n"/>
+      <c r="AX328" s="3" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="3" t="n"/>
@@ -15697,6 +18063,13 @@
       <c r="AO329" s="3" t="n"/>
       <c r="AP329" s="3" t="n"/>
       <c r="AQ329" s="3" t="n"/>
+      <c r="AR329" s="3" t="n"/>
+      <c r="AS329" s="3" t="n"/>
+      <c r="AT329" s="3" t="n"/>
+      <c r="AU329" s="3" t="n"/>
+      <c r="AV329" s="3" t="n"/>
+      <c r="AW329" s="3" t="n"/>
+      <c r="AX329" s="3" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="3" t="n"/>
@@ -15742,6 +18115,13 @@
       <c r="AO330" s="3" t="n"/>
       <c r="AP330" s="3" t="n"/>
       <c r="AQ330" s="3" t="n"/>
+      <c r="AR330" s="3" t="n"/>
+      <c r="AS330" s="3" t="n"/>
+      <c r="AT330" s="3" t="n"/>
+      <c r="AU330" s="3" t="n"/>
+      <c r="AV330" s="3" t="n"/>
+      <c r="AW330" s="3" t="n"/>
+      <c r="AX330" s="3" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="3" t="n"/>
@@ -15787,6 +18167,13 @@
       <c r="AO331" s="3" t="n"/>
       <c r="AP331" s="3" t="n"/>
       <c r="AQ331" s="3" t="n"/>
+      <c r="AR331" s="3" t="n"/>
+      <c r="AS331" s="3" t="n"/>
+      <c r="AT331" s="3" t="n"/>
+      <c r="AU331" s="3" t="n"/>
+      <c r="AV331" s="3" t="n"/>
+      <c r="AW331" s="3" t="n"/>
+      <c r="AX331" s="3" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="3" t="n"/>
@@ -15832,6 +18219,13 @@
       <c r="AO332" s="3" t="n"/>
       <c r="AP332" s="3" t="n"/>
       <c r="AQ332" s="3" t="n"/>
+      <c r="AR332" s="3" t="n"/>
+      <c r="AS332" s="3" t="n"/>
+      <c r="AT332" s="3" t="n"/>
+      <c r="AU332" s="3" t="n"/>
+      <c r="AV332" s="3" t="n"/>
+      <c r="AW332" s="3" t="n"/>
+      <c r="AX332" s="3" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="3" t="n"/>
@@ -15877,6 +18271,13 @@
       <c r="AO333" s="3" t="n"/>
       <c r="AP333" s="3" t="n"/>
       <c r="AQ333" s="3" t="n"/>
+      <c r="AR333" s="3" t="n"/>
+      <c r="AS333" s="3" t="n"/>
+      <c r="AT333" s="3" t="n"/>
+      <c r="AU333" s="3" t="n"/>
+      <c r="AV333" s="3" t="n"/>
+      <c r="AW333" s="3" t="n"/>
+      <c r="AX333" s="3" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="3" t="n"/>
@@ -15922,6 +18323,13 @@
       <c r="AO334" s="3" t="n"/>
       <c r="AP334" s="3" t="n"/>
       <c r="AQ334" s="3" t="n"/>
+      <c r="AR334" s="3" t="n"/>
+      <c r="AS334" s="3" t="n"/>
+      <c r="AT334" s="3" t="n"/>
+      <c r="AU334" s="3" t="n"/>
+      <c r="AV334" s="3" t="n"/>
+      <c r="AW334" s="3" t="n"/>
+      <c r="AX334" s="3" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="3" t="n"/>
@@ -15967,6 +18375,13 @@
       <c r="AO335" s="3" t="n"/>
       <c r="AP335" s="3" t="n"/>
       <c r="AQ335" s="3" t="n"/>
+      <c r="AR335" s="3" t="n"/>
+      <c r="AS335" s="3" t="n"/>
+      <c r="AT335" s="3" t="n"/>
+      <c r="AU335" s="3" t="n"/>
+      <c r="AV335" s="3" t="n"/>
+      <c r="AW335" s="3" t="n"/>
+      <c r="AX335" s="3" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="3" t="n"/>
@@ -16012,6 +18427,13 @@
       <c r="AO336" s="3" t="n"/>
       <c r="AP336" s="3" t="n"/>
       <c r="AQ336" s="3" t="n"/>
+      <c r="AR336" s="3" t="n"/>
+      <c r="AS336" s="3" t="n"/>
+      <c r="AT336" s="3" t="n"/>
+      <c r="AU336" s="3" t="n"/>
+      <c r="AV336" s="3" t="n"/>
+      <c r="AW336" s="3" t="n"/>
+      <c r="AX336" s="3" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="3" t="n"/>
@@ -16057,6 +18479,13 @@
       <c r="AO337" s="3" t="n"/>
       <c r="AP337" s="3" t="n"/>
       <c r="AQ337" s="3" t="n"/>
+      <c r="AR337" s="3" t="n"/>
+      <c r="AS337" s="3" t="n"/>
+      <c r="AT337" s="3" t="n"/>
+      <c r="AU337" s="3" t="n"/>
+      <c r="AV337" s="3" t="n"/>
+      <c r="AW337" s="3" t="n"/>
+      <c r="AX337" s="3" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="3" t="n"/>
@@ -16102,6 +18531,13 @@
       <c r="AO338" s="3" t="n"/>
       <c r="AP338" s="3" t="n"/>
       <c r="AQ338" s="3" t="n"/>
+      <c r="AR338" s="3" t="n"/>
+      <c r="AS338" s="3" t="n"/>
+      <c r="AT338" s="3" t="n"/>
+      <c r="AU338" s="3" t="n"/>
+      <c r="AV338" s="3" t="n"/>
+      <c r="AW338" s="3" t="n"/>
+      <c r="AX338" s="3" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="3" t="n"/>
@@ -16147,6 +18583,13 @@
       <c r="AO339" s="3" t="n"/>
       <c r="AP339" s="3" t="n"/>
       <c r="AQ339" s="3" t="n"/>
+      <c r="AR339" s="3" t="n"/>
+      <c r="AS339" s="3" t="n"/>
+      <c r="AT339" s="3" t="n"/>
+      <c r="AU339" s="3" t="n"/>
+      <c r="AV339" s="3" t="n"/>
+      <c r="AW339" s="3" t="n"/>
+      <c r="AX339" s="3" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="3" t="n"/>
@@ -16192,6 +18635,13 @@
       <c r="AO340" s="3" t="n"/>
       <c r="AP340" s="3" t="n"/>
       <c r="AQ340" s="3" t="n"/>
+      <c r="AR340" s="3" t="n"/>
+      <c r="AS340" s="3" t="n"/>
+      <c r="AT340" s="3" t="n"/>
+      <c r="AU340" s="3" t="n"/>
+      <c r="AV340" s="3" t="n"/>
+      <c r="AW340" s="3" t="n"/>
+      <c r="AX340" s="3" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="3" t="n"/>
@@ -16237,6 +18687,13 @@
       <c r="AO341" s="3" t="n"/>
       <c r="AP341" s="3" t="n"/>
       <c r="AQ341" s="3" t="n"/>
+      <c r="AR341" s="3" t="n"/>
+      <c r="AS341" s="3" t="n"/>
+      <c r="AT341" s="3" t="n"/>
+      <c r="AU341" s="3" t="n"/>
+      <c r="AV341" s="3" t="n"/>
+      <c r="AW341" s="3" t="n"/>
+      <c r="AX341" s="3" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="3" t="n"/>
@@ -16282,6 +18739,13 @@
       <c r="AO342" s="3" t="n"/>
       <c r="AP342" s="3" t="n"/>
       <c r="AQ342" s="3" t="n"/>
+      <c r="AR342" s="3" t="n"/>
+      <c r="AS342" s="3" t="n"/>
+      <c r="AT342" s="3" t="n"/>
+      <c r="AU342" s="3" t="n"/>
+      <c r="AV342" s="3" t="n"/>
+      <c r="AW342" s="3" t="n"/>
+      <c r="AX342" s="3" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="3" t="n"/>
@@ -16327,6 +18791,13 @@
       <c r="AO343" s="3" t="n"/>
       <c r="AP343" s="3" t="n"/>
       <c r="AQ343" s="3" t="n"/>
+      <c r="AR343" s="3" t="n"/>
+      <c r="AS343" s="3" t="n"/>
+      <c r="AT343" s="3" t="n"/>
+      <c r="AU343" s="3" t="n"/>
+      <c r="AV343" s="3" t="n"/>
+      <c r="AW343" s="3" t="n"/>
+      <c r="AX343" s="3" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="3" t="n"/>
@@ -16372,6 +18843,13 @@
       <c r="AO344" s="3" t="n"/>
       <c r="AP344" s="3" t="n"/>
       <c r="AQ344" s="3" t="n"/>
+      <c r="AR344" s="3" t="n"/>
+      <c r="AS344" s="3" t="n"/>
+      <c r="AT344" s="3" t="n"/>
+      <c r="AU344" s="3" t="n"/>
+      <c r="AV344" s="3" t="n"/>
+      <c r="AW344" s="3" t="n"/>
+      <c r="AX344" s="3" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="3" t="n"/>
@@ -16417,6 +18895,13 @@
       <c r="AO345" s="3" t="n"/>
       <c r="AP345" s="3" t="n"/>
       <c r="AQ345" s="3" t="n"/>
+      <c r="AR345" s="3" t="n"/>
+      <c r="AS345" s="3" t="n"/>
+      <c r="AT345" s="3" t="n"/>
+      <c r="AU345" s="3" t="n"/>
+      <c r="AV345" s="3" t="n"/>
+      <c r="AW345" s="3" t="n"/>
+      <c r="AX345" s="3" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="3" t="n"/>
@@ -16462,6 +18947,13 @@
       <c r="AO346" s="3" t="n"/>
       <c r="AP346" s="3" t="n"/>
       <c r="AQ346" s="3" t="n"/>
+      <c r="AR346" s="3" t="n"/>
+      <c r="AS346" s="3" t="n"/>
+      <c r="AT346" s="3" t="n"/>
+      <c r="AU346" s="3" t="n"/>
+      <c r="AV346" s="3" t="n"/>
+      <c r="AW346" s="3" t="n"/>
+      <c r="AX346" s="3" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="3" t="n"/>
@@ -16507,6 +18999,13 @@
       <c r="AO347" s="3" t="n"/>
       <c r="AP347" s="3" t="n"/>
       <c r="AQ347" s="3" t="n"/>
+      <c r="AR347" s="3" t="n"/>
+      <c r="AS347" s="3" t="n"/>
+      <c r="AT347" s="3" t="n"/>
+      <c r="AU347" s="3" t="n"/>
+      <c r="AV347" s="3" t="n"/>
+      <c r="AW347" s="3" t="n"/>
+      <c r="AX347" s="3" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="3" t="n"/>
@@ -16552,6 +19051,13 @@
       <c r="AO348" s="3" t="n"/>
       <c r="AP348" s="3" t="n"/>
       <c r="AQ348" s="3" t="n"/>
+      <c r="AR348" s="3" t="n"/>
+      <c r="AS348" s="3" t="n"/>
+      <c r="AT348" s="3" t="n"/>
+      <c r="AU348" s="3" t="n"/>
+      <c r="AV348" s="3" t="n"/>
+      <c r="AW348" s="3" t="n"/>
+      <c r="AX348" s="3" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="3" t="n"/>
@@ -16597,6 +19103,13 @@
       <c r="AO349" s="3" t="n"/>
       <c r="AP349" s="3" t="n"/>
       <c r="AQ349" s="3" t="n"/>
+      <c r="AR349" s="3" t="n"/>
+      <c r="AS349" s="3" t="n"/>
+      <c r="AT349" s="3" t="n"/>
+      <c r="AU349" s="3" t="n"/>
+      <c r="AV349" s="3" t="n"/>
+      <c r="AW349" s="3" t="n"/>
+      <c r="AX349" s="3" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="3" t="n"/>
@@ -16642,6 +19155,13 @@
       <c r="AO350" s="3" t="n"/>
       <c r="AP350" s="3" t="n"/>
       <c r="AQ350" s="3" t="n"/>
+      <c r="AR350" s="3" t="n"/>
+      <c r="AS350" s="3" t="n"/>
+      <c r="AT350" s="3" t="n"/>
+      <c r="AU350" s="3" t="n"/>
+      <c r="AV350" s="3" t="n"/>
+      <c r="AW350" s="3" t="n"/>
+      <c r="AX350" s="3" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="3" t="n"/>
@@ -16687,6 +19207,13 @@
       <c r="AO351" s="3" t="n"/>
       <c r="AP351" s="3" t="n"/>
       <c r="AQ351" s="3" t="n"/>
+      <c r="AR351" s="3" t="n"/>
+      <c r="AS351" s="3" t="n"/>
+      <c r="AT351" s="3" t="n"/>
+      <c r="AU351" s="3" t="n"/>
+      <c r="AV351" s="3" t="n"/>
+      <c r="AW351" s="3" t="n"/>
+      <c r="AX351" s="3" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="3" t="n"/>
@@ -16732,6 +19259,13 @@
       <c r="AO352" s="3" t="n"/>
       <c r="AP352" s="3" t="n"/>
       <c r="AQ352" s="3" t="n"/>
+      <c r="AR352" s="3" t="n"/>
+      <c r="AS352" s="3" t="n"/>
+      <c r="AT352" s="3" t="n"/>
+      <c r="AU352" s="3" t="n"/>
+      <c r="AV352" s="3" t="n"/>
+      <c r="AW352" s="3" t="n"/>
+      <c r="AX352" s="3" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="3" t="n"/>
@@ -16777,6 +19311,13 @@
       <c r="AO353" s="3" t="n"/>
       <c r="AP353" s="3" t="n"/>
       <c r="AQ353" s="3" t="n"/>
+      <c r="AR353" s="3" t="n"/>
+      <c r="AS353" s="3" t="n"/>
+      <c r="AT353" s="3" t="n"/>
+      <c r="AU353" s="3" t="n"/>
+      <c r="AV353" s="3" t="n"/>
+      <c r="AW353" s="3" t="n"/>
+      <c r="AX353" s="3" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="3" t="n"/>
@@ -16822,6 +19363,13 @@
       <c r="AO354" s="3" t="n"/>
       <c r="AP354" s="3" t="n"/>
       <c r="AQ354" s="3" t="n"/>
+      <c r="AR354" s="3" t="n"/>
+      <c r="AS354" s="3" t="n"/>
+      <c r="AT354" s="3" t="n"/>
+      <c r="AU354" s="3" t="n"/>
+      <c r="AV354" s="3" t="n"/>
+      <c r="AW354" s="3" t="n"/>
+      <c r="AX354" s="3" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="3" t="n"/>
@@ -16867,6 +19415,13 @@
       <c r="AO355" s="3" t="n"/>
       <c r="AP355" s="3" t="n"/>
       <c r="AQ355" s="3" t="n"/>
+      <c r="AR355" s="3" t="n"/>
+      <c r="AS355" s="3" t="n"/>
+      <c r="AT355" s="3" t="n"/>
+      <c r="AU355" s="3" t="n"/>
+      <c r="AV355" s="3" t="n"/>
+      <c r="AW355" s="3" t="n"/>
+      <c r="AX355" s="3" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="3" t="n"/>
@@ -16912,6 +19467,13 @@
       <c r="AO356" s="3" t="n"/>
       <c r="AP356" s="3" t="n"/>
       <c r="AQ356" s="3" t="n"/>
+      <c r="AR356" s="3" t="n"/>
+      <c r="AS356" s="3" t="n"/>
+      <c r="AT356" s="3" t="n"/>
+      <c r="AU356" s="3" t="n"/>
+      <c r="AV356" s="3" t="n"/>
+      <c r="AW356" s="3" t="n"/>
+      <c r="AX356" s="3" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="3" t="n"/>
@@ -16957,6 +19519,13 @@
       <c r="AO357" s="3" t="n"/>
       <c r="AP357" s="3" t="n"/>
       <c r="AQ357" s="3" t="n"/>
+      <c r="AR357" s="3" t="n"/>
+      <c r="AS357" s="3" t="n"/>
+      <c r="AT357" s="3" t="n"/>
+      <c r="AU357" s="3" t="n"/>
+      <c r="AV357" s="3" t="n"/>
+      <c r="AW357" s="3" t="n"/>
+      <c r="AX357" s="3" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="3" t="n"/>
@@ -17002,6 +19571,13 @@
       <c r="AO358" s="3" t="n"/>
       <c r="AP358" s="3" t="n"/>
       <c r="AQ358" s="3" t="n"/>
+      <c r="AR358" s="3" t="n"/>
+      <c r="AS358" s="3" t="n"/>
+      <c r="AT358" s="3" t="n"/>
+      <c r="AU358" s="3" t="n"/>
+      <c r="AV358" s="3" t="n"/>
+      <c r="AW358" s="3" t="n"/>
+      <c r="AX358" s="3" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="3" t="n"/>
@@ -17047,6 +19623,13 @@
       <c r="AO359" s="3" t="n"/>
       <c r="AP359" s="3" t="n"/>
       <c r="AQ359" s="3" t="n"/>
+      <c r="AR359" s="3" t="n"/>
+      <c r="AS359" s="3" t="n"/>
+      <c r="AT359" s="3" t="n"/>
+      <c r="AU359" s="3" t="n"/>
+      <c r="AV359" s="3" t="n"/>
+      <c r="AW359" s="3" t="n"/>
+      <c r="AX359" s="3" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="3" t="n"/>
@@ -17092,6 +19675,13 @@
       <c r="AO360" s="3" t="n"/>
       <c r="AP360" s="3" t="n"/>
       <c r="AQ360" s="3" t="n"/>
+      <c r="AR360" s="3" t="n"/>
+      <c r="AS360" s="3" t="n"/>
+      <c r="AT360" s="3" t="n"/>
+      <c r="AU360" s="3" t="n"/>
+      <c r="AV360" s="3" t="n"/>
+      <c r="AW360" s="3" t="n"/>
+      <c r="AX360" s="3" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="3" t="n"/>
@@ -17137,6 +19727,13 @@
       <c r="AO361" s="3" t="n"/>
       <c r="AP361" s="3" t="n"/>
       <c r="AQ361" s="3" t="n"/>
+      <c r="AR361" s="3" t="n"/>
+      <c r="AS361" s="3" t="n"/>
+      <c r="AT361" s="3" t="n"/>
+      <c r="AU361" s="3" t="n"/>
+      <c r="AV361" s="3" t="n"/>
+      <c r="AW361" s="3" t="n"/>
+      <c r="AX361" s="3" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="3" t="n"/>
@@ -17182,6 +19779,13 @@
       <c r="AO362" s="3" t="n"/>
       <c r="AP362" s="3" t="n"/>
       <c r="AQ362" s="3" t="n"/>
+      <c r="AR362" s="3" t="n"/>
+      <c r="AS362" s="3" t="n"/>
+      <c r="AT362" s="3" t="n"/>
+      <c r="AU362" s="3" t="n"/>
+      <c r="AV362" s="3" t="n"/>
+      <c r="AW362" s="3" t="n"/>
+      <c r="AX362" s="3" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="3" t="n"/>
@@ -17227,6 +19831,13 @@
       <c r="AO363" s="3" t="n"/>
       <c r="AP363" s="3" t="n"/>
       <c r="AQ363" s="3" t="n"/>
+      <c r="AR363" s="3" t="n"/>
+      <c r="AS363" s="3" t="n"/>
+      <c r="AT363" s="3" t="n"/>
+      <c r="AU363" s="3" t="n"/>
+      <c r="AV363" s="3" t="n"/>
+      <c r="AW363" s="3" t="n"/>
+      <c r="AX363" s="3" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="3" t="n"/>
@@ -17272,6 +19883,13 @@
       <c r="AO364" s="3" t="n"/>
       <c r="AP364" s="3" t="n"/>
       <c r="AQ364" s="3" t="n"/>
+      <c r="AR364" s="3" t="n"/>
+      <c r="AS364" s="3" t="n"/>
+      <c r="AT364" s="3" t="n"/>
+      <c r="AU364" s="3" t="n"/>
+      <c r="AV364" s="3" t="n"/>
+      <c r="AW364" s="3" t="n"/>
+      <c r="AX364" s="3" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="3" t="n"/>
@@ -17317,6 +19935,13 @@
       <c r="AO365" s="3" t="n"/>
       <c r="AP365" s="3" t="n"/>
       <c r="AQ365" s="3" t="n"/>
+      <c r="AR365" s="3" t="n"/>
+      <c r="AS365" s="3" t="n"/>
+      <c r="AT365" s="3" t="n"/>
+      <c r="AU365" s="3" t="n"/>
+      <c r="AV365" s="3" t="n"/>
+      <c r="AW365" s="3" t="n"/>
+      <c r="AX365" s="3" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="3" t="n"/>
@@ -17362,6 +19987,13 @@
       <c r="AO366" s="3" t="n"/>
       <c r="AP366" s="3" t="n"/>
       <c r="AQ366" s="3" t="n"/>
+      <c r="AR366" s="3" t="n"/>
+      <c r="AS366" s="3" t="n"/>
+      <c r="AT366" s="3" t="n"/>
+      <c r="AU366" s="3" t="n"/>
+      <c r="AV366" s="3" t="n"/>
+      <c r="AW366" s="3" t="n"/>
+      <c r="AX366" s="3" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="3" t="n"/>
@@ -17407,6 +20039,13 @@
       <c r="AO367" s="3" t="n"/>
       <c r="AP367" s="3" t="n"/>
       <c r="AQ367" s="3" t="n"/>
+      <c r="AR367" s="3" t="n"/>
+      <c r="AS367" s="3" t="n"/>
+      <c r="AT367" s="3" t="n"/>
+      <c r="AU367" s="3" t="n"/>
+      <c r="AV367" s="3" t="n"/>
+      <c r="AW367" s="3" t="n"/>
+      <c r="AX367" s="3" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="3" t="n"/>
@@ -17452,6 +20091,13 @@
       <c r="AO368" s="3" t="n"/>
       <c r="AP368" s="3" t="n"/>
       <c r="AQ368" s="3" t="n"/>
+      <c r="AR368" s="3" t="n"/>
+      <c r="AS368" s="3" t="n"/>
+      <c r="AT368" s="3" t="n"/>
+      <c r="AU368" s="3" t="n"/>
+      <c r="AV368" s="3" t="n"/>
+      <c r="AW368" s="3" t="n"/>
+      <c r="AX368" s="3" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="3" t="n"/>
@@ -17497,6 +20143,13 @@
       <c r="AO369" s="3" t="n"/>
       <c r="AP369" s="3" t="n"/>
       <c r="AQ369" s="3" t="n"/>
+      <c r="AR369" s="3" t="n"/>
+      <c r="AS369" s="3" t="n"/>
+      <c r="AT369" s="3" t="n"/>
+      <c r="AU369" s="3" t="n"/>
+      <c r="AV369" s="3" t="n"/>
+      <c r="AW369" s="3" t="n"/>
+      <c r="AX369" s="3" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="3" t="n"/>
@@ -17542,6 +20195,13 @@
       <c r="AO370" s="3" t="n"/>
       <c r="AP370" s="3" t="n"/>
       <c r="AQ370" s="3" t="n"/>
+      <c r="AR370" s="3" t="n"/>
+      <c r="AS370" s="3" t="n"/>
+      <c r="AT370" s="3" t="n"/>
+      <c r="AU370" s="3" t="n"/>
+      <c r="AV370" s="3" t="n"/>
+      <c r="AW370" s="3" t="n"/>
+      <c r="AX370" s="3" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="3" t="n"/>
@@ -17587,6 +20247,13 @@
       <c r="AO371" s="3" t="n"/>
       <c r="AP371" s="3" t="n"/>
       <c r="AQ371" s="3" t="n"/>
+      <c r="AR371" s="3" t="n"/>
+      <c r="AS371" s="3" t="n"/>
+      <c r="AT371" s="3" t="n"/>
+      <c r="AU371" s="3" t="n"/>
+      <c r="AV371" s="3" t="n"/>
+      <c r="AW371" s="3" t="n"/>
+      <c r="AX371" s="3" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="3" t="n"/>
@@ -17632,6 +20299,13 @@
       <c r="AO372" s="3" t="n"/>
       <c r="AP372" s="3" t="n"/>
       <c r="AQ372" s="3" t="n"/>
+      <c r="AR372" s="3" t="n"/>
+      <c r="AS372" s="3" t="n"/>
+      <c r="AT372" s="3" t="n"/>
+      <c r="AU372" s="3" t="n"/>
+      <c r="AV372" s="3" t="n"/>
+      <c r="AW372" s="3" t="n"/>
+      <c r="AX372" s="3" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="3" t="n"/>
@@ -17677,6 +20351,13 @@
       <c r="AO373" s="3" t="n"/>
       <c r="AP373" s="3" t="n"/>
       <c r="AQ373" s="3" t="n"/>
+      <c r="AR373" s="3" t="n"/>
+      <c r="AS373" s="3" t="n"/>
+      <c r="AT373" s="3" t="n"/>
+      <c r="AU373" s="3" t="n"/>
+      <c r="AV373" s="3" t="n"/>
+      <c r="AW373" s="3" t="n"/>
+      <c r="AX373" s="3" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="3" t="n"/>
@@ -17722,6 +20403,13 @@
       <c r="AO374" s="3" t="n"/>
       <c r="AP374" s="3" t="n"/>
       <c r="AQ374" s="3" t="n"/>
+      <c r="AR374" s="3" t="n"/>
+      <c r="AS374" s="3" t="n"/>
+      <c r="AT374" s="3" t="n"/>
+      <c r="AU374" s="3" t="n"/>
+      <c r="AV374" s="3" t="n"/>
+      <c r="AW374" s="3" t="n"/>
+      <c r="AX374" s="3" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="3" t="n"/>
@@ -17767,6 +20455,13 @@
       <c r="AO375" s="3" t="n"/>
       <c r="AP375" s="3" t="n"/>
       <c r="AQ375" s="3" t="n"/>
+      <c r="AR375" s="3" t="n"/>
+      <c r="AS375" s="3" t="n"/>
+      <c r="AT375" s="3" t="n"/>
+      <c r="AU375" s="3" t="n"/>
+      <c r="AV375" s="3" t="n"/>
+      <c r="AW375" s="3" t="n"/>
+      <c r="AX375" s="3" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="3" t="n"/>
@@ -17812,6 +20507,13 @@
       <c r="AO376" s="3" t="n"/>
       <c r="AP376" s="3" t="n"/>
       <c r="AQ376" s="3" t="n"/>
+      <c r="AR376" s="3" t="n"/>
+      <c r="AS376" s="3" t="n"/>
+      <c r="AT376" s="3" t="n"/>
+      <c r="AU376" s="3" t="n"/>
+      <c r="AV376" s="3" t="n"/>
+      <c r="AW376" s="3" t="n"/>
+      <c r="AX376" s="3" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="3" t="n"/>
@@ -17857,6 +20559,13 @@
       <c r="AO377" s="3" t="n"/>
       <c r="AP377" s="3" t="n"/>
       <c r="AQ377" s="3" t="n"/>
+      <c r="AR377" s="3" t="n"/>
+      <c r="AS377" s="3" t="n"/>
+      <c r="AT377" s="3" t="n"/>
+      <c r="AU377" s="3" t="n"/>
+      <c r="AV377" s="3" t="n"/>
+      <c r="AW377" s="3" t="n"/>
+      <c r="AX377" s="3" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="3" t="n"/>
@@ -17902,6 +20611,13 @@
       <c r="AO378" s="3" t="n"/>
       <c r="AP378" s="3" t="n"/>
       <c r="AQ378" s="3" t="n"/>
+      <c r="AR378" s="3" t="n"/>
+      <c r="AS378" s="3" t="n"/>
+      <c r="AT378" s="3" t="n"/>
+      <c r="AU378" s="3" t="n"/>
+      <c r="AV378" s="3" t="n"/>
+      <c r="AW378" s="3" t="n"/>
+      <c r="AX378" s="3" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="3" t="n"/>
@@ -17947,6 +20663,13 @@
       <c r="AO379" s="3" t="n"/>
       <c r="AP379" s="3" t="n"/>
       <c r="AQ379" s="3" t="n"/>
+      <c r="AR379" s="3" t="n"/>
+      <c r="AS379" s="3" t="n"/>
+      <c r="AT379" s="3" t="n"/>
+      <c r="AU379" s="3" t="n"/>
+      <c r="AV379" s="3" t="n"/>
+      <c r="AW379" s="3" t="n"/>
+      <c r="AX379" s="3" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="3" t="n"/>
@@ -17992,6 +20715,13 @@
       <c r="AO380" s="3" t="n"/>
       <c r="AP380" s="3" t="n"/>
       <c r="AQ380" s="3" t="n"/>
+      <c r="AR380" s="3" t="n"/>
+      <c r="AS380" s="3" t="n"/>
+      <c r="AT380" s="3" t="n"/>
+      <c r="AU380" s="3" t="n"/>
+      <c r="AV380" s="3" t="n"/>
+      <c r="AW380" s="3" t="n"/>
+      <c r="AX380" s="3" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="3" t="n"/>
@@ -18037,6 +20767,13 @@
       <c r="AO381" s="3" t="n"/>
       <c r="AP381" s="3" t="n"/>
       <c r="AQ381" s="3" t="n"/>
+      <c r="AR381" s="3" t="n"/>
+      <c r="AS381" s="3" t="n"/>
+      <c r="AT381" s="3" t="n"/>
+      <c r="AU381" s="3" t="n"/>
+      <c r="AV381" s="3" t="n"/>
+      <c r="AW381" s="3" t="n"/>
+      <c r="AX381" s="3" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="3" t="n"/>
@@ -18082,6 +20819,13 @@
       <c r="AO382" s="3" t="n"/>
       <c r="AP382" s="3" t="n"/>
       <c r="AQ382" s="3" t="n"/>
+      <c r="AR382" s="3" t="n"/>
+      <c r="AS382" s="3" t="n"/>
+      <c r="AT382" s="3" t="n"/>
+      <c r="AU382" s="3" t="n"/>
+      <c r="AV382" s="3" t="n"/>
+      <c r="AW382" s="3" t="n"/>
+      <c r="AX382" s="3" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="3" t="n"/>
@@ -18127,6 +20871,13 @@
       <c r="AO383" s="3" t="n"/>
       <c r="AP383" s="3" t="n"/>
       <c r="AQ383" s="3" t="n"/>
+      <c r="AR383" s="3" t="n"/>
+      <c r="AS383" s="3" t="n"/>
+      <c r="AT383" s="3" t="n"/>
+      <c r="AU383" s="3" t="n"/>
+      <c r="AV383" s="3" t="n"/>
+      <c r="AW383" s="3" t="n"/>
+      <c r="AX383" s="3" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="3" t="n"/>
@@ -18172,6 +20923,13 @@
       <c r="AO384" s="3" t="n"/>
       <c r="AP384" s="3" t="n"/>
       <c r="AQ384" s="3" t="n"/>
+      <c r="AR384" s="3" t="n"/>
+      <c r="AS384" s="3" t="n"/>
+      <c r="AT384" s="3" t="n"/>
+      <c r="AU384" s="3" t="n"/>
+      <c r="AV384" s="3" t="n"/>
+      <c r="AW384" s="3" t="n"/>
+      <c r="AX384" s="3" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="3" t="n"/>
@@ -18217,6 +20975,13 @@
       <c r="AO385" s="3" t="n"/>
       <c r="AP385" s="3" t="n"/>
       <c r="AQ385" s="3" t="n"/>
+      <c r="AR385" s="3" t="n"/>
+      <c r="AS385" s="3" t="n"/>
+      <c r="AT385" s="3" t="n"/>
+      <c r="AU385" s="3" t="n"/>
+      <c r="AV385" s="3" t="n"/>
+      <c r="AW385" s="3" t="n"/>
+      <c r="AX385" s="3" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="3" t="n"/>
@@ -18262,6 +21027,13 @@
       <c r="AO386" s="3" t="n"/>
       <c r="AP386" s="3" t="n"/>
       <c r="AQ386" s="3" t="n"/>
+      <c r="AR386" s="3" t="n"/>
+      <c r="AS386" s="3" t="n"/>
+      <c r="AT386" s="3" t="n"/>
+      <c r="AU386" s="3" t="n"/>
+      <c r="AV386" s="3" t="n"/>
+      <c r="AW386" s="3" t="n"/>
+      <c r="AX386" s="3" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="3" t="n"/>
@@ -18307,6 +21079,13 @@
       <c r="AO387" s="3" t="n"/>
       <c r="AP387" s="3" t="n"/>
       <c r="AQ387" s="3" t="n"/>
+      <c r="AR387" s="3" t="n"/>
+      <c r="AS387" s="3" t="n"/>
+      <c r="AT387" s="3" t="n"/>
+      <c r="AU387" s="3" t="n"/>
+      <c r="AV387" s="3" t="n"/>
+      <c r="AW387" s="3" t="n"/>
+      <c r="AX387" s="3" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="3" t="n"/>
@@ -18352,6 +21131,13 @@
       <c r="AO388" s="3" t="n"/>
       <c r="AP388" s="3" t="n"/>
       <c r="AQ388" s="3" t="n"/>
+      <c r="AR388" s="3" t="n"/>
+      <c r="AS388" s="3" t="n"/>
+      <c r="AT388" s="3" t="n"/>
+      <c r="AU388" s="3" t="n"/>
+      <c r="AV388" s="3" t="n"/>
+      <c r="AW388" s="3" t="n"/>
+      <c r="AX388" s="3" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="3" t="n"/>
@@ -18397,6 +21183,13 @@
       <c r="AO389" s="3" t="n"/>
       <c r="AP389" s="3" t="n"/>
       <c r="AQ389" s="3" t="n"/>
+      <c r="AR389" s="3" t="n"/>
+      <c r="AS389" s="3" t="n"/>
+      <c r="AT389" s="3" t="n"/>
+      <c r="AU389" s="3" t="n"/>
+      <c r="AV389" s="3" t="n"/>
+      <c r="AW389" s="3" t="n"/>
+      <c r="AX389" s="3" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="3" t="n"/>
@@ -18442,6 +21235,13 @@
       <c r="AO390" s="3" t="n"/>
       <c r="AP390" s="3" t="n"/>
       <c r="AQ390" s="3" t="n"/>
+      <c r="AR390" s="3" t="n"/>
+      <c r="AS390" s="3" t="n"/>
+      <c r="AT390" s="3" t="n"/>
+      <c r="AU390" s="3" t="n"/>
+      <c r="AV390" s="3" t="n"/>
+      <c r="AW390" s="3" t="n"/>
+      <c r="AX390" s="3" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="3" t="n"/>
@@ -18487,6 +21287,13 @@
       <c r="AO391" s="3" t="n"/>
       <c r="AP391" s="3" t="n"/>
       <c r="AQ391" s="3" t="n"/>
+      <c r="AR391" s="3" t="n"/>
+      <c r="AS391" s="3" t="n"/>
+      <c r="AT391" s="3" t="n"/>
+      <c r="AU391" s="3" t="n"/>
+      <c r="AV391" s="3" t="n"/>
+      <c r="AW391" s="3" t="n"/>
+      <c r="AX391" s="3" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="3" t="n"/>
@@ -18532,6 +21339,13 @@
       <c r="AO392" s="3" t="n"/>
       <c r="AP392" s="3" t="n"/>
       <c r="AQ392" s="3" t="n"/>
+      <c r="AR392" s="3" t="n"/>
+      <c r="AS392" s="3" t="n"/>
+      <c r="AT392" s="3" t="n"/>
+      <c r="AU392" s="3" t="n"/>
+      <c r="AV392" s="3" t="n"/>
+      <c r="AW392" s="3" t="n"/>
+      <c r="AX392" s="3" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="3" t="n"/>
@@ -18577,6 +21391,13 @@
       <c r="AO393" s="3" t="n"/>
       <c r="AP393" s="3" t="n"/>
       <c r="AQ393" s="3" t="n"/>
+      <c r="AR393" s="3" t="n"/>
+      <c r="AS393" s="3" t="n"/>
+      <c r="AT393" s="3" t="n"/>
+      <c r="AU393" s="3" t="n"/>
+      <c r="AV393" s="3" t="n"/>
+      <c r="AW393" s="3" t="n"/>
+      <c r="AX393" s="3" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="3" t="n"/>
@@ -18622,6 +21443,13 @@
       <c r="AO394" s="3" t="n"/>
       <c r="AP394" s="3" t="n"/>
       <c r="AQ394" s="3" t="n"/>
+      <c r="AR394" s="3" t="n"/>
+      <c r="AS394" s="3" t="n"/>
+      <c r="AT394" s="3" t="n"/>
+      <c r="AU394" s="3" t="n"/>
+      <c r="AV394" s="3" t="n"/>
+      <c r="AW394" s="3" t="n"/>
+      <c r="AX394" s="3" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="3" t="n"/>
@@ -18667,6 +21495,13 @@
       <c r="AO395" s="3" t="n"/>
       <c r="AP395" s="3" t="n"/>
       <c r="AQ395" s="3" t="n"/>
+      <c r="AR395" s="3" t="n"/>
+      <c r="AS395" s="3" t="n"/>
+      <c r="AT395" s="3" t="n"/>
+      <c r="AU395" s="3" t="n"/>
+      <c r="AV395" s="3" t="n"/>
+      <c r="AW395" s="3" t="n"/>
+      <c r="AX395" s="3" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="3" t="n"/>
@@ -18712,6 +21547,13 @@
       <c r="AO396" s="3" t="n"/>
       <c r="AP396" s="3" t="n"/>
       <c r="AQ396" s="3" t="n"/>
+      <c r="AR396" s="3" t="n"/>
+      <c r="AS396" s="3" t="n"/>
+      <c r="AT396" s="3" t="n"/>
+      <c r="AU396" s="3" t="n"/>
+      <c r="AV396" s="3" t="n"/>
+      <c r="AW396" s="3" t="n"/>
+      <c r="AX396" s="3" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="3" t="n"/>
@@ -18757,6 +21599,13 @@
       <c r="AO397" s="3" t="n"/>
       <c r="AP397" s="3" t="n"/>
       <c r="AQ397" s="3" t="n"/>
+      <c r="AR397" s="3" t="n"/>
+      <c r="AS397" s="3" t="n"/>
+      <c r="AT397" s="3" t="n"/>
+      <c r="AU397" s="3" t="n"/>
+      <c r="AV397" s="3" t="n"/>
+      <c r="AW397" s="3" t="n"/>
+      <c r="AX397" s="3" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="3" t="n"/>
@@ -18802,6 +21651,13 @@
       <c r="AO398" s="3" t="n"/>
       <c r="AP398" s="3" t="n"/>
       <c r="AQ398" s="3" t="n"/>
+      <c r="AR398" s="3" t="n"/>
+      <c r="AS398" s="3" t="n"/>
+      <c r="AT398" s="3" t="n"/>
+      <c r="AU398" s="3" t="n"/>
+      <c r="AV398" s="3" t="n"/>
+      <c r="AW398" s="3" t="n"/>
+      <c r="AX398" s="3" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="3" t="n"/>
@@ -18847,6 +21703,13 @@
       <c r="AO399" s="3" t="n"/>
       <c r="AP399" s="3" t="n"/>
       <c r="AQ399" s="3" t="n"/>
+      <c r="AR399" s="3" t="n"/>
+      <c r="AS399" s="3" t="n"/>
+      <c r="AT399" s="3" t="n"/>
+      <c r="AU399" s="3" t="n"/>
+      <c r="AV399" s="3" t="n"/>
+      <c r="AW399" s="3" t="n"/>
+      <c r="AX399" s="3" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="3" t="n"/>
@@ -18892,6 +21755,13 @@
       <c r="AO400" s="3" t="n"/>
       <c r="AP400" s="3" t="n"/>
       <c r="AQ400" s="3" t="n"/>
+      <c r="AR400" s="3" t="n"/>
+      <c r="AS400" s="3" t="n"/>
+      <c r="AT400" s="3" t="n"/>
+      <c r="AU400" s="3" t="n"/>
+      <c r="AV400" s="3" t="n"/>
+      <c r="AW400" s="3" t="n"/>
+      <c r="AX400" s="3" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="3" t="n"/>
@@ -18937,6 +21807,13 @@
       <c r="AO401" s="3" t="n"/>
       <c r="AP401" s="3" t="n"/>
       <c r="AQ401" s="3" t="n"/>
+      <c r="AR401" s="3" t="n"/>
+      <c r="AS401" s="3" t="n"/>
+      <c r="AT401" s="3" t="n"/>
+      <c r="AU401" s="3" t="n"/>
+      <c r="AV401" s="3" t="n"/>
+      <c r="AW401" s="3" t="n"/>
+      <c r="AX401" s="3" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="3" t="n"/>
@@ -18982,6 +21859,13 @@
       <c r="AO402" s="3" t="n"/>
       <c r="AP402" s="3" t="n"/>
       <c r="AQ402" s="3" t="n"/>
+      <c r="AR402" s="3" t="n"/>
+      <c r="AS402" s="3" t="n"/>
+      <c r="AT402" s="3" t="n"/>
+      <c r="AU402" s="3" t="n"/>
+      <c r="AV402" s="3" t="n"/>
+      <c r="AW402" s="3" t="n"/>
+      <c r="AX402" s="3" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="3" t="n"/>
@@ -19027,6 +21911,13 @@
       <c r="AO403" s="3" t="n"/>
       <c r="AP403" s="3" t="n"/>
       <c r="AQ403" s="3" t="n"/>
+      <c r="AR403" s="3" t="n"/>
+      <c r="AS403" s="3" t="n"/>
+      <c r="AT403" s="3" t="n"/>
+      <c r="AU403" s="3" t="n"/>
+      <c r="AV403" s="3" t="n"/>
+      <c r="AW403" s="3" t="n"/>
+      <c r="AX403" s="3" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="3" t="n"/>
@@ -19072,6 +21963,13 @@
       <c r="AO404" s="3" t="n"/>
       <c r="AP404" s="3" t="n"/>
       <c r="AQ404" s="3" t="n"/>
+      <c r="AR404" s="3" t="n"/>
+      <c r="AS404" s="3" t="n"/>
+      <c r="AT404" s="3" t="n"/>
+      <c r="AU404" s="3" t="n"/>
+      <c r="AV404" s="3" t="n"/>
+      <c r="AW404" s="3" t="n"/>
+      <c r="AX404" s="3" t="n"/>
     </row>
     <row r="405">
       <c r="A405" s="3" t="n"/>
@@ -19117,6 +22015,13 @@
       <c r="AO405" s="3" t="n"/>
       <c r="AP405" s="3" t="n"/>
       <c r="AQ405" s="3" t="n"/>
+      <c r="AR405" s="3" t="n"/>
+      <c r="AS405" s="3" t="n"/>
+      <c r="AT405" s="3" t="n"/>
+      <c r="AU405" s="3" t="n"/>
+      <c r="AV405" s="3" t="n"/>
+      <c r="AW405" s="3" t="n"/>
+      <c r="AX405" s="3" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="3" t="n"/>
@@ -19162,6 +22067,13 @@
       <c r="AO406" s="3" t="n"/>
       <c r="AP406" s="3" t="n"/>
       <c r="AQ406" s="3" t="n"/>
+      <c r="AR406" s="3" t="n"/>
+      <c r="AS406" s="3" t="n"/>
+      <c r="AT406" s="3" t="n"/>
+      <c r="AU406" s="3" t="n"/>
+      <c r="AV406" s="3" t="n"/>
+      <c r="AW406" s="3" t="n"/>
+      <c r="AX406" s="3" t="n"/>
     </row>
     <row r="407">
       <c r="A407" s="3" t="n"/>
@@ -19207,6 +22119,13 @@
       <c r="AO407" s="3" t="n"/>
       <c r="AP407" s="3" t="n"/>
       <c r="AQ407" s="3" t="n"/>
+      <c r="AR407" s="3" t="n"/>
+      <c r="AS407" s="3" t="n"/>
+      <c r="AT407" s="3" t="n"/>
+      <c r="AU407" s="3" t="n"/>
+      <c r="AV407" s="3" t="n"/>
+      <c r="AW407" s="3" t="n"/>
+      <c r="AX407" s="3" t="n"/>
     </row>
     <row r="408">
       <c r="A408" s="3" t="n"/>
@@ -19252,6 +22171,13 @@
       <c r="AO408" s="3" t="n"/>
       <c r="AP408" s="3" t="n"/>
       <c r="AQ408" s="3" t="n"/>
+      <c r="AR408" s="3" t="n"/>
+      <c r="AS408" s="3" t="n"/>
+      <c r="AT408" s="3" t="n"/>
+      <c r="AU408" s="3" t="n"/>
+      <c r="AV408" s="3" t="n"/>
+      <c r="AW408" s="3" t="n"/>
+      <c r="AX408" s="3" t="n"/>
     </row>
     <row r="409">
       <c r="A409" s="3" t="n"/>
@@ -19297,6 +22223,13 @@
       <c r="AO409" s="3" t="n"/>
       <c r="AP409" s="3" t="n"/>
       <c r="AQ409" s="3" t="n"/>
+      <c r="AR409" s="3" t="n"/>
+      <c r="AS409" s="3" t="n"/>
+      <c r="AT409" s="3" t="n"/>
+      <c r="AU409" s="3" t="n"/>
+      <c r="AV409" s="3" t="n"/>
+      <c r="AW409" s="3" t="n"/>
+      <c r="AX409" s="3" t="n"/>
     </row>
     <row r="410">
       <c r="A410" s="3" t="n"/>
@@ -19342,6 +22275,13 @@
       <c r="AO410" s="3" t="n"/>
       <c r="AP410" s="3" t="n"/>
       <c r="AQ410" s="3" t="n"/>
+      <c r="AR410" s="3" t="n"/>
+      <c r="AS410" s="3" t="n"/>
+      <c r="AT410" s="3" t="n"/>
+      <c r="AU410" s="3" t="n"/>
+      <c r="AV410" s="3" t="n"/>
+      <c r="AW410" s="3" t="n"/>
+      <c r="AX410" s="3" t="n"/>
     </row>
     <row r="411">
       <c r="A411" s="3" t="n"/>
@@ -19387,6 +22327,13 @@
       <c r="AO411" s="3" t="n"/>
       <c r="AP411" s="3" t="n"/>
       <c r="AQ411" s="3" t="n"/>
+      <c r="AR411" s="3" t="n"/>
+      <c r="AS411" s="3" t="n"/>
+      <c r="AT411" s="3" t="n"/>
+      <c r="AU411" s="3" t="n"/>
+      <c r="AV411" s="3" t="n"/>
+      <c r="AW411" s="3" t="n"/>
+      <c r="AX411" s="3" t="n"/>
     </row>
     <row r="412">
       <c r="A412" s="3" t="n"/>
@@ -19432,6 +22379,13 @@
       <c r="AO412" s="3" t="n"/>
       <c r="AP412" s="3" t="n"/>
       <c r="AQ412" s="3" t="n"/>
+      <c r="AR412" s="3" t="n"/>
+      <c r="AS412" s="3" t="n"/>
+      <c r="AT412" s="3" t="n"/>
+      <c r="AU412" s="3" t="n"/>
+      <c r="AV412" s="3" t="n"/>
+      <c r="AW412" s="3" t="n"/>
+      <c r="AX412" s="3" t="n"/>
     </row>
     <row r="413">
       <c r="A413" s="3" t="n"/>
@@ -19477,6 +22431,13 @@
       <c r="AO413" s="3" t="n"/>
       <c r="AP413" s="3" t="n"/>
       <c r="AQ413" s="3" t="n"/>
+      <c r="AR413" s="3" t="n"/>
+      <c r="AS413" s="3" t="n"/>
+      <c r="AT413" s="3" t="n"/>
+      <c r="AU413" s="3" t="n"/>
+      <c r="AV413" s="3" t="n"/>
+      <c r="AW413" s="3" t="n"/>
+      <c r="AX413" s="3" t="n"/>
     </row>
     <row r="414">
       <c r="A414" s="3" t="n"/>
@@ -19522,6 +22483,13 @@
       <c r="AO414" s="3" t="n"/>
       <c r="AP414" s="3" t="n"/>
       <c r="AQ414" s="3" t="n"/>
+      <c r="AR414" s="3" t="n"/>
+      <c r="AS414" s="3" t="n"/>
+      <c r="AT414" s="3" t="n"/>
+      <c r="AU414" s="3" t="n"/>
+      <c r="AV414" s="3" t="n"/>
+      <c r="AW414" s="3" t="n"/>
+      <c r="AX414" s="3" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="3" t="n"/>
@@ -19567,6 +22535,13 @@
       <c r="AO415" s="3" t="n"/>
       <c r="AP415" s="3" t="n"/>
       <c r="AQ415" s="3" t="n"/>
+      <c r="AR415" s="3" t="n"/>
+      <c r="AS415" s="3" t="n"/>
+      <c r="AT415" s="3" t="n"/>
+      <c r="AU415" s="3" t="n"/>
+      <c r="AV415" s="3" t="n"/>
+      <c r="AW415" s="3" t="n"/>
+      <c r="AX415" s="3" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="3" t="n"/>
@@ -19612,6 +22587,13 @@
       <c r="AO416" s="3" t="n"/>
       <c r="AP416" s="3" t="n"/>
       <c r="AQ416" s="3" t="n"/>
+      <c r="AR416" s="3" t="n"/>
+      <c r="AS416" s="3" t="n"/>
+      <c r="AT416" s="3" t="n"/>
+      <c r="AU416" s="3" t="n"/>
+      <c r="AV416" s="3" t="n"/>
+      <c r="AW416" s="3" t="n"/>
+      <c r="AX416" s="3" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="3" t="n"/>
@@ -19657,6 +22639,13 @@
       <c r="AO417" s="3" t="n"/>
       <c r="AP417" s="3" t="n"/>
       <c r="AQ417" s="3" t="n"/>
+      <c r="AR417" s="3" t="n"/>
+      <c r="AS417" s="3" t="n"/>
+      <c r="AT417" s="3" t="n"/>
+      <c r="AU417" s="3" t="n"/>
+      <c r="AV417" s="3" t="n"/>
+      <c r="AW417" s="3" t="n"/>
+      <c r="AX417" s="3" t="n"/>
     </row>
     <row r="418">
       <c r="A418" s="3" t="n"/>
@@ -19702,6 +22691,13 @@
       <c r="AO418" s="3" t="n"/>
       <c r="AP418" s="3" t="n"/>
       <c r="AQ418" s="3" t="n"/>
+      <c r="AR418" s="3" t="n"/>
+      <c r="AS418" s="3" t="n"/>
+      <c r="AT418" s="3" t="n"/>
+      <c r="AU418" s="3" t="n"/>
+      <c r="AV418" s="3" t="n"/>
+      <c r="AW418" s="3" t="n"/>
+      <c r="AX418" s="3" t="n"/>
     </row>
     <row r="419">
       <c r="A419" s="3" t="n"/>
@@ -19747,6 +22743,13 @@
       <c r="AO419" s="3" t="n"/>
       <c r="AP419" s="3" t="n"/>
       <c r="AQ419" s="3" t="n"/>
+      <c r="AR419" s="3" t="n"/>
+      <c r="AS419" s="3" t="n"/>
+      <c r="AT419" s="3" t="n"/>
+      <c r="AU419" s="3" t="n"/>
+      <c r="AV419" s="3" t="n"/>
+      <c r="AW419" s="3" t="n"/>
+      <c r="AX419" s="3" t="n"/>
     </row>
     <row r="420">
       <c r="A420" s="3" t="n"/>
@@ -19792,6 +22795,13 @@
       <c r="AO420" s="3" t="n"/>
       <c r="AP420" s="3" t="n"/>
       <c r="AQ420" s="3" t="n"/>
+      <c r="AR420" s="3" t="n"/>
+      <c r="AS420" s="3" t="n"/>
+      <c r="AT420" s="3" t="n"/>
+      <c r="AU420" s="3" t="n"/>
+      <c r="AV420" s="3" t="n"/>
+      <c r="AW420" s="3" t="n"/>
+      <c r="AX420" s="3" t="n"/>
     </row>
     <row r="421">
       <c r="A421" s="3" t="n"/>
@@ -19837,6 +22847,13 @@
       <c r="AO421" s="3" t="n"/>
       <c r="AP421" s="3" t="n"/>
       <c r="AQ421" s="3" t="n"/>
+      <c r="AR421" s="3" t="n"/>
+      <c r="AS421" s="3" t="n"/>
+      <c r="AT421" s="3" t="n"/>
+      <c r="AU421" s="3" t="n"/>
+      <c r="AV421" s="3" t="n"/>
+      <c r="AW421" s="3" t="n"/>
+      <c r="AX421" s="3" t="n"/>
     </row>
     <row r="422">
       <c r="A422" s="3" t="n"/>
@@ -19882,6 +22899,13 @@
       <c r="AO422" s="3" t="n"/>
       <c r="AP422" s="3" t="n"/>
       <c r="AQ422" s="3" t="n"/>
+      <c r="AR422" s="3" t="n"/>
+      <c r="AS422" s="3" t="n"/>
+      <c r="AT422" s="3" t="n"/>
+      <c r="AU422" s="3" t="n"/>
+      <c r="AV422" s="3" t="n"/>
+      <c r="AW422" s="3" t="n"/>
+      <c r="AX422" s="3" t="n"/>
     </row>
     <row r="423">
       <c r="A423" s="3" t="n"/>
@@ -19927,6 +22951,13 @@
       <c r="AO423" s="3" t="n"/>
       <c r="AP423" s="3" t="n"/>
       <c r="AQ423" s="3" t="n"/>
+      <c r="AR423" s="3" t="n"/>
+      <c r="AS423" s="3" t="n"/>
+      <c r="AT423" s="3" t="n"/>
+      <c r="AU423" s="3" t="n"/>
+      <c r="AV423" s="3" t="n"/>
+      <c r="AW423" s="3" t="n"/>
+      <c r="AX423" s="3" t="n"/>
     </row>
     <row r="424">
       <c r="A424" s="3" t="n"/>
@@ -19972,6 +23003,13 @@
       <c r="AO424" s="3" t="n"/>
       <c r="AP424" s="3" t="n"/>
       <c r="AQ424" s="3" t="n"/>
+      <c r="AR424" s="3" t="n"/>
+      <c r="AS424" s="3" t="n"/>
+      <c r="AT424" s="3" t="n"/>
+      <c r="AU424" s="3" t="n"/>
+      <c r="AV424" s="3" t="n"/>
+      <c r="AW424" s="3" t="n"/>
+      <c r="AX424" s="3" t="n"/>
     </row>
     <row r="425">
       <c r="A425" s="3" t="n"/>
@@ -20017,6 +23055,13 @@
       <c r="AO425" s="3" t="n"/>
       <c r="AP425" s="3" t="n"/>
       <c r="AQ425" s="3" t="n"/>
+      <c r="AR425" s="3" t="n"/>
+      <c r="AS425" s="3" t="n"/>
+      <c r="AT425" s="3" t="n"/>
+      <c r="AU425" s="3" t="n"/>
+      <c r="AV425" s="3" t="n"/>
+      <c r="AW425" s="3" t="n"/>
+      <c r="AX425" s="3" t="n"/>
     </row>
     <row r="426">
       <c r="A426" s="3" t="n"/>
@@ -20062,6 +23107,13 @@
       <c r="AO426" s="3" t="n"/>
       <c r="AP426" s="3" t="n"/>
       <c r="AQ426" s="3" t="n"/>
+      <c r="AR426" s="3" t="n"/>
+      <c r="AS426" s="3" t="n"/>
+      <c r="AT426" s="3" t="n"/>
+      <c r="AU426" s="3" t="n"/>
+      <c r="AV426" s="3" t="n"/>
+      <c r="AW426" s="3" t="n"/>
+      <c r="AX426" s="3" t="n"/>
     </row>
     <row r="427">
       <c r="A427" s="3" t="n"/>
@@ -20107,6 +23159,13 @@
       <c r="AO427" s="3" t="n"/>
       <c r="AP427" s="3" t="n"/>
       <c r="AQ427" s="3" t="n"/>
+      <c r="AR427" s="3" t="n"/>
+      <c r="AS427" s="3" t="n"/>
+      <c r="AT427" s="3" t="n"/>
+      <c r="AU427" s="3" t="n"/>
+      <c r="AV427" s="3" t="n"/>
+      <c r="AW427" s="3" t="n"/>
+      <c r="AX427" s="3" t="n"/>
     </row>
     <row r="428">
       <c r="A428" s="3" t="n"/>
@@ -20152,6 +23211,13 @@
       <c r="AO428" s="3" t="n"/>
       <c r="AP428" s="3" t="n"/>
       <c r="AQ428" s="3" t="n"/>
+      <c r="AR428" s="3" t="n"/>
+      <c r="AS428" s="3" t="n"/>
+      <c r="AT428" s="3" t="n"/>
+      <c r="AU428" s="3" t="n"/>
+      <c r="AV428" s="3" t="n"/>
+      <c r="AW428" s="3" t="n"/>
+      <c r="AX428" s="3" t="n"/>
     </row>
     <row r="429">
       <c r="A429" s="3" t="n"/>
@@ -20197,6 +23263,13 @@
       <c r="AO429" s="3" t="n"/>
       <c r="AP429" s="3" t="n"/>
       <c r="AQ429" s="3" t="n"/>
+      <c r="AR429" s="3" t="n"/>
+      <c r="AS429" s="3" t="n"/>
+      <c r="AT429" s="3" t="n"/>
+      <c r="AU429" s="3" t="n"/>
+      <c r="AV429" s="3" t="n"/>
+      <c r="AW429" s="3" t="n"/>
+      <c r="AX429" s="3" t="n"/>
     </row>
     <row r="430">
       <c r="A430" s="3" t="n"/>
@@ -20242,6 +23315,13 @@
       <c r="AO430" s="3" t="n"/>
       <c r="AP430" s="3" t="n"/>
       <c r="AQ430" s="3" t="n"/>
+      <c r="AR430" s="3" t="n"/>
+      <c r="AS430" s="3" t="n"/>
+      <c r="AT430" s="3" t="n"/>
+      <c r="AU430" s="3" t="n"/>
+      <c r="AV430" s="3" t="n"/>
+      <c r="AW430" s="3" t="n"/>
+      <c r="AX430" s="3" t="n"/>
     </row>
     <row r="431">
       <c r="A431" s="3" t="n"/>
@@ -20287,6 +23367,13 @@
       <c r="AO431" s="3" t="n"/>
       <c r="AP431" s="3" t="n"/>
       <c r="AQ431" s="3" t="n"/>
+      <c r="AR431" s="3" t="n"/>
+      <c r="AS431" s="3" t="n"/>
+      <c r="AT431" s="3" t="n"/>
+      <c r="AU431" s="3" t="n"/>
+      <c r="AV431" s="3" t="n"/>
+      <c r="AW431" s="3" t="n"/>
+      <c r="AX431" s="3" t="n"/>
     </row>
     <row r="432">
       <c r="A432" s="3" t="n"/>
@@ -20332,6 +23419,13 @@
       <c r="AO432" s="3" t="n"/>
       <c r="AP432" s="3" t="n"/>
       <c r="AQ432" s="3" t="n"/>
+      <c r="AR432" s="3" t="n"/>
+      <c r="AS432" s="3" t="n"/>
+      <c r="AT432" s="3" t="n"/>
+      <c r="AU432" s="3" t="n"/>
+      <c r="AV432" s="3" t="n"/>
+      <c r="AW432" s="3" t="n"/>
+      <c r="AX432" s="3" t="n"/>
     </row>
     <row r="433">
       <c r="A433" s="3" t="n"/>
@@ -20377,6 +23471,13 @@
       <c r="AO433" s="3" t="n"/>
       <c r="AP433" s="3" t="n"/>
       <c r="AQ433" s="3" t="n"/>
+      <c r="AR433" s="3" t="n"/>
+      <c r="AS433" s="3" t="n"/>
+      <c r="AT433" s="3" t="n"/>
+      <c r="AU433" s="3" t="n"/>
+      <c r="AV433" s="3" t="n"/>
+      <c r="AW433" s="3" t="n"/>
+      <c r="AX433" s="3" t="n"/>
     </row>
     <row r="434">
       <c r="A434" s="3" t="n"/>
@@ -20422,6 +23523,13 @@
       <c r="AO434" s="3" t="n"/>
       <c r="AP434" s="3" t="n"/>
       <c r="AQ434" s="3" t="n"/>
+      <c r="AR434" s="3" t="n"/>
+      <c r="AS434" s="3" t="n"/>
+      <c r="AT434" s="3" t="n"/>
+      <c r="AU434" s="3" t="n"/>
+      <c r="AV434" s="3" t="n"/>
+      <c r="AW434" s="3" t="n"/>
+      <c r="AX434" s="3" t="n"/>
     </row>
     <row r="435">
       <c r="A435" s="3" t="n"/>
@@ -20467,6 +23575,13 @@
       <c r="AO435" s="3" t="n"/>
       <c r="AP435" s="3" t="n"/>
       <c r="AQ435" s="3" t="n"/>
+      <c r="AR435" s="3" t="n"/>
+      <c r="AS435" s="3" t="n"/>
+      <c r="AT435" s="3" t="n"/>
+      <c r="AU435" s="3" t="n"/>
+      <c r="AV435" s="3" t="n"/>
+      <c r="AW435" s="3" t="n"/>
+      <c r="AX435" s="3" t="n"/>
     </row>
     <row r="436">
       <c r="A436" s="3" t="n"/>
@@ -20512,6 +23627,13 @@
       <c r="AO436" s="3" t="n"/>
       <c r="AP436" s="3" t="n"/>
       <c r="AQ436" s="3" t="n"/>
+      <c r="AR436" s="3" t="n"/>
+      <c r="AS436" s="3" t="n"/>
+      <c r="AT436" s="3" t="n"/>
+      <c r="AU436" s="3" t="n"/>
+      <c r="AV436" s="3" t="n"/>
+      <c r="AW436" s="3" t="n"/>
+      <c r="AX436" s="3" t="n"/>
     </row>
     <row r="437">
       <c r="A437" s="3" t="n"/>
@@ -20557,6 +23679,13 @@
       <c r="AO437" s="3" t="n"/>
       <c r="AP437" s="3" t="n"/>
       <c r="AQ437" s="3" t="n"/>
+      <c r="AR437" s="3" t="n"/>
+      <c r="AS437" s="3" t="n"/>
+      <c r="AT437" s="3" t="n"/>
+      <c r="AU437" s="3" t="n"/>
+      <c r="AV437" s="3" t="n"/>
+      <c r="AW437" s="3" t="n"/>
+      <c r="AX437" s="3" t="n"/>
     </row>
     <row r="438">
       <c r="A438" s="3" t="n"/>
@@ -20602,6 +23731,13 @@
       <c r="AO438" s="3" t="n"/>
       <c r="AP438" s="3" t="n"/>
       <c r="AQ438" s="3" t="n"/>
+      <c r="AR438" s="3" t="n"/>
+      <c r="AS438" s="3" t="n"/>
+      <c r="AT438" s="3" t="n"/>
+      <c r="AU438" s="3" t="n"/>
+      <c r="AV438" s="3" t="n"/>
+      <c r="AW438" s="3" t="n"/>
+      <c r="AX438" s="3" t="n"/>
     </row>
     <row r="439">
       <c r="A439" s="3" t="n"/>
@@ -20647,6 +23783,13 @@
       <c r="AO439" s="3" t="n"/>
       <c r="AP439" s="3" t="n"/>
       <c r="AQ439" s="3" t="n"/>
+      <c r="AR439" s="3" t="n"/>
+      <c r="AS439" s="3" t="n"/>
+      <c r="AT439" s="3" t="n"/>
+      <c r="AU439" s="3" t="n"/>
+      <c r="AV439" s="3" t="n"/>
+      <c r="AW439" s="3" t="n"/>
+      <c r="AX439" s="3" t="n"/>
     </row>
     <row r="440">
       <c r="A440" s="3" t="n"/>
@@ -20692,6 +23835,13 @@
       <c r="AO440" s="3" t="n"/>
       <c r="AP440" s="3" t="n"/>
       <c r="AQ440" s="3" t="n"/>
+      <c r="AR440" s="3" t="n"/>
+      <c r="AS440" s="3" t="n"/>
+      <c r="AT440" s="3" t="n"/>
+      <c r="AU440" s="3" t="n"/>
+      <c r="AV440" s="3" t="n"/>
+      <c r="AW440" s="3" t="n"/>
+      <c r="AX440" s="3" t="n"/>
     </row>
     <row r="441">
       <c r="A441" s="3" t="n"/>
@@ -20737,6 +23887,13 @@
       <c r="AO441" s="3" t="n"/>
       <c r="AP441" s="3" t="n"/>
       <c r="AQ441" s="3" t="n"/>
+      <c r="AR441" s="3" t="n"/>
+      <c r="AS441" s="3" t="n"/>
+      <c r="AT441" s="3" t="n"/>
+      <c r="AU441" s="3" t="n"/>
+      <c r="AV441" s="3" t="n"/>
+      <c r="AW441" s="3" t="n"/>
+      <c r="AX441" s="3" t="n"/>
     </row>
     <row r="442">
       <c r="A442" s="3" t="n"/>
@@ -20782,6 +23939,13 @@
       <c r="AO442" s="3" t="n"/>
       <c r="AP442" s="3" t="n"/>
       <c r="AQ442" s="3" t="n"/>
+      <c r="AR442" s="3" t="n"/>
+      <c r="AS442" s="3" t="n"/>
+      <c r="AT442" s="3" t="n"/>
+      <c r="AU442" s="3" t="n"/>
+      <c r="AV442" s="3" t="n"/>
+      <c r="AW442" s="3" t="n"/>
+      <c r="AX442" s="3" t="n"/>
     </row>
     <row r="443">
       <c r="A443" s="3" t="n"/>
@@ -20827,6 +23991,13 @@
       <c r="AO443" s="3" t="n"/>
       <c r="AP443" s="3" t="n"/>
       <c r="AQ443" s="3" t="n"/>
+      <c r="AR443" s="3" t="n"/>
+      <c r="AS443" s="3" t="n"/>
+      <c r="AT443" s="3" t="n"/>
+      <c r="AU443" s="3" t="n"/>
+      <c r="AV443" s="3" t="n"/>
+      <c r="AW443" s="3" t="n"/>
+      <c r="AX443" s="3" t="n"/>
     </row>
     <row r="444">
       <c r="A444" s="3" t="n"/>
@@ -20872,6 +24043,13 @@
       <c r="AO444" s="3" t="n"/>
       <c r="AP444" s="3" t="n"/>
       <c r="AQ444" s="3" t="n"/>
+      <c r="AR444" s="3" t="n"/>
+      <c r="AS444" s="3" t="n"/>
+      <c r="AT444" s="3" t="n"/>
+      <c r="AU444" s="3" t="n"/>
+      <c r="AV444" s="3" t="n"/>
+      <c r="AW444" s="3" t="n"/>
+      <c r="AX444" s="3" t="n"/>
     </row>
     <row r="445">
       <c r="A445" s="3" t="n"/>
@@ -20917,6 +24095,13 @@
       <c r="AO445" s="3" t="n"/>
       <c r="AP445" s="3" t="n"/>
       <c r="AQ445" s="3" t="n"/>
+      <c r="AR445" s="3" t="n"/>
+      <c r="AS445" s="3" t="n"/>
+      <c r="AT445" s="3" t="n"/>
+      <c r="AU445" s="3" t="n"/>
+      <c r="AV445" s="3" t="n"/>
+      <c r="AW445" s="3" t="n"/>
+      <c r="AX445" s="3" t="n"/>
     </row>
     <row r="446">
       <c r="A446" s="3" t="n"/>
@@ -20962,6 +24147,13 @@
       <c r="AO446" s="3" t="n"/>
       <c r="AP446" s="3" t="n"/>
       <c r="AQ446" s="3" t="n"/>
+      <c r="AR446" s="3" t="n"/>
+      <c r="AS446" s="3" t="n"/>
+      <c r="AT446" s="3" t="n"/>
+      <c r="AU446" s="3" t="n"/>
+      <c r="AV446" s="3" t="n"/>
+      <c r="AW446" s="3" t="n"/>
+      <c r="AX446" s="3" t="n"/>
     </row>
     <row r="447">
       <c r="A447" s="3" t="n"/>
@@ -21007,6 +24199,13 @@
       <c r="AO447" s="3" t="n"/>
       <c r="AP447" s="3" t="n"/>
       <c r="AQ447" s="3" t="n"/>
+      <c r="AR447" s="3" t="n"/>
+      <c r="AS447" s="3" t="n"/>
+      <c r="AT447" s="3" t="n"/>
+      <c r="AU447" s="3" t="n"/>
+      <c r="AV447" s="3" t="n"/>
+      <c r="AW447" s="3" t="n"/>
+      <c r="AX447" s="3" t="n"/>
     </row>
     <row r="448">
       <c r="A448" s="3" t="n"/>
@@ -21052,6 +24251,13 @@
       <c r="AO448" s="3" t="n"/>
       <c r="AP448" s="3" t="n"/>
       <c r="AQ448" s="3" t="n"/>
+      <c r="AR448" s="3" t="n"/>
+      <c r="AS448" s="3" t="n"/>
+      <c r="AT448" s="3" t="n"/>
+      <c r="AU448" s="3" t="n"/>
+      <c r="AV448" s="3" t="n"/>
+      <c r="AW448" s="3" t="n"/>
+      <c r="AX448" s="3" t="n"/>
     </row>
     <row r="449">
       <c r="A449" s="3" t="n"/>
@@ -21097,6 +24303,13 @@
       <c r="AO449" s="3" t="n"/>
       <c r="AP449" s="3" t="n"/>
       <c r="AQ449" s="3" t="n"/>
+      <c r="AR449" s="3" t="n"/>
+      <c r="AS449" s="3" t="n"/>
+      <c r="AT449" s="3" t="n"/>
+      <c r="AU449" s="3" t="n"/>
+      <c r="AV449" s="3" t="n"/>
+      <c r="AW449" s="3" t="n"/>
+      <c r="AX449" s="3" t="n"/>
     </row>
     <row r="450">
       <c r="A450" s="3" t="n"/>
@@ -21142,6 +24355,13 @@
       <c r="AO450" s="3" t="n"/>
       <c r="AP450" s="3" t="n"/>
       <c r="AQ450" s="3" t="n"/>
+      <c r="AR450" s="3" t="n"/>
+      <c r="AS450" s="3" t="n"/>
+      <c r="AT450" s="3" t="n"/>
+      <c r="AU450" s="3" t="n"/>
+      <c r="AV450" s="3" t="n"/>
+      <c r="AW450" s="3" t="n"/>
+      <c r="AX450" s="3" t="n"/>
     </row>
     <row r="451">
       <c r="A451" s="3" t="n"/>
@@ -21187,6 +24407,13 @@
       <c r="AO451" s="3" t="n"/>
       <c r="AP451" s="3" t="n"/>
       <c r="AQ451" s="3" t="n"/>
+      <c r="AR451" s="3" t="n"/>
+      <c r="AS451" s="3" t="n"/>
+      <c r="AT451" s="3" t="n"/>
+      <c r="AU451" s="3" t="n"/>
+      <c r="AV451" s="3" t="n"/>
+      <c r="AW451" s="3" t="n"/>
+      <c r="AX451" s="3" t="n"/>
     </row>
     <row r="452">
       <c r="A452" s="3" t="n"/>
@@ -21232,6 +24459,13 @@
       <c r="AO452" s="3" t="n"/>
       <c r="AP452" s="3" t="n"/>
       <c r="AQ452" s="3" t="n"/>
+      <c r="AR452" s="3" t="n"/>
+      <c r="AS452" s="3" t="n"/>
+      <c r="AT452" s="3" t="n"/>
+      <c r="AU452" s="3" t="n"/>
+      <c r="AV452" s="3" t="n"/>
+      <c r="AW452" s="3" t="n"/>
+      <c r="AX452" s="3" t="n"/>
     </row>
     <row r="453">
       <c r="A453" s="3" t="n"/>
@@ -21277,6 +24511,13 @@
       <c r="AO453" s="3" t="n"/>
       <c r="AP453" s="3" t="n"/>
       <c r="AQ453" s="3" t="n"/>
+      <c r="AR453" s="3" t="n"/>
+      <c r="AS453" s="3" t="n"/>
+      <c r="AT453" s="3" t="n"/>
+      <c r="AU453" s="3" t="n"/>
+      <c r="AV453" s="3" t="n"/>
+      <c r="AW453" s="3" t="n"/>
+      <c r="AX453" s="3" t="n"/>
     </row>
     <row r="454">
       <c r="A454" s="3" t="n"/>
@@ -21322,6 +24563,13 @@
       <c r="AO454" s="3" t="n"/>
       <c r="AP454" s="3" t="n"/>
       <c r="AQ454" s="3" t="n"/>
+      <c r="AR454" s="3" t="n"/>
+      <c r="AS454" s="3" t="n"/>
+      <c r="AT454" s="3" t="n"/>
+      <c r="AU454" s="3" t="n"/>
+      <c r="AV454" s="3" t="n"/>
+      <c r="AW454" s="3" t="n"/>
+      <c r="AX454" s="3" t="n"/>
     </row>
     <row r="455">
       <c r="A455" s="3" t="n"/>
@@ -21367,6 +24615,13 @@
       <c r="AO455" s="3" t="n"/>
       <c r="AP455" s="3" t="n"/>
       <c r="AQ455" s="3" t="n"/>
+      <c r="AR455" s="3" t="n"/>
+      <c r="AS455" s="3" t="n"/>
+      <c r="AT455" s="3" t="n"/>
+      <c r="AU455" s="3" t="n"/>
+      <c r="AV455" s="3" t="n"/>
+      <c r="AW455" s="3" t="n"/>
+      <c r="AX455" s="3" t="n"/>
     </row>
     <row r="456">
       <c r="A456" s="3" t="n"/>
@@ -21412,6 +24667,13 @@
       <c r="AO456" s="3" t="n"/>
       <c r="AP456" s="3" t="n"/>
       <c r="AQ456" s="3" t="n"/>
+      <c r="AR456" s="3" t="n"/>
+      <c r="AS456" s="3" t="n"/>
+      <c r="AT456" s="3" t="n"/>
+      <c r="AU456" s="3" t="n"/>
+      <c r="AV456" s="3" t="n"/>
+      <c r="AW456" s="3" t="n"/>
+      <c r="AX456" s="3" t="n"/>
     </row>
     <row r="457">
       <c r="A457" s="3" t="n"/>
@@ -21457,6 +24719,13 @@
       <c r="AO457" s="3" t="n"/>
       <c r="AP457" s="3" t="n"/>
       <c r="AQ457" s="3" t="n"/>
+      <c r="AR457" s="3" t="n"/>
+      <c r="AS457" s="3" t="n"/>
+      <c r="AT457" s="3" t="n"/>
+      <c r="AU457" s="3" t="n"/>
+      <c r="AV457" s="3" t="n"/>
+      <c r="AW457" s="3" t="n"/>
+      <c r="AX457" s="3" t="n"/>
     </row>
     <row r="458">
       <c r="A458" s="3" t="n"/>
@@ -21502,6 +24771,13 @@
       <c r="AO458" s="3" t="n"/>
       <c r="AP458" s="3" t="n"/>
       <c r="AQ458" s="3" t="n"/>
+      <c r="AR458" s="3" t="n"/>
+      <c r="AS458" s="3" t="n"/>
+      <c r="AT458" s="3" t="n"/>
+      <c r="AU458" s="3" t="n"/>
+      <c r="AV458" s="3" t="n"/>
+      <c r="AW458" s="3" t="n"/>
+      <c r="AX458" s="3" t="n"/>
     </row>
     <row r="459">
       <c r="A459" s="3" t="n"/>
@@ -21547,6 +24823,13 @@
       <c r="AO459" s="3" t="n"/>
       <c r="AP459" s="3" t="n"/>
       <c r="AQ459" s="3" t="n"/>
+      <c r="AR459" s="3" t="n"/>
+      <c r="AS459" s="3" t="n"/>
+      <c r="AT459" s="3" t="n"/>
+      <c r="AU459" s="3" t="n"/>
+      <c r="AV459" s="3" t="n"/>
+      <c r="AW459" s="3" t="n"/>
+      <c r="AX459" s="3" t="n"/>
     </row>
     <row r="460">
       <c r="A460" s="3" t="n"/>
@@ -21592,6 +24875,13 @@
       <c r="AO460" s="3" t="n"/>
       <c r="AP460" s="3" t="n"/>
       <c r="AQ460" s="3" t="n"/>
+      <c r="AR460" s="3" t="n"/>
+      <c r="AS460" s="3" t="n"/>
+      <c r="AT460" s="3" t="n"/>
+      <c r="AU460" s="3" t="n"/>
+      <c r="AV460" s="3" t="n"/>
+      <c r="AW460" s="3" t="n"/>
+      <c r="AX460" s="3" t="n"/>
     </row>
     <row r="461">
       <c r="A461" s="3" t="n"/>
@@ -21637,6 +24927,13 @@
       <c r="AO461" s="3" t="n"/>
       <c r="AP461" s="3" t="n"/>
       <c r="AQ461" s="3" t="n"/>
+      <c r="AR461" s="3" t="n"/>
+      <c r="AS461" s="3" t="n"/>
+      <c r="AT461" s="3" t="n"/>
+      <c r="AU461" s="3" t="n"/>
+      <c r="AV461" s="3" t="n"/>
+      <c r="AW461" s="3" t="n"/>
+      <c r="AX461" s="3" t="n"/>
     </row>
     <row r="462">
       <c r="A462" s="3" t="n"/>
@@ -21682,6 +24979,13 @@
       <c r="AO462" s="3" t="n"/>
       <c r="AP462" s="3" t="n"/>
       <c r="AQ462" s="3" t="n"/>
+      <c r="AR462" s="3" t="n"/>
+      <c r="AS462" s="3" t="n"/>
+      <c r="AT462" s="3" t="n"/>
+      <c r="AU462" s="3" t="n"/>
+      <c r="AV462" s="3" t="n"/>
+      <c r="AW462" s="3" t="n"/>
+      <c r="AX462" s="3" t="n"/>
     </row>
     <row r="463">
       <c r="A463" s="3" t="n"/>
@@ -21727,6 +25031,13 @@
       <c r="AO463" s="3" t="n"/>
       <c r="AP463" s="3" t="n"/>
       <c r="AQ463" s="3" t="n"/>
+      <c r="AR463" s="3" t="n"/>
+      <c r="AS463" s="3" t="n"/>
+      <c r="AT463" s="3" t="n"/>
+      <c r="AU463" s="3" t="n"/>
+      <c r="AV463" s="3" t="n"/>
+      <c r="AW463" s="3" t="n"/>
+      <c r="AX463" s="3" t="n"/>
     </row>
     <row r="464">
       <c r="A464" s="3" t="n"/>
@@ -21772,6 +25083,13 @@
       <c r="AO464" s="3" t="n"/>
       <c r="AP464" s="3" t="n"/>
       <c r="AQ464" s="3" t="n"/>
+      <c r="AR464" s="3" t="n"/>
+      <c r="AS464" s="3" t="n"/>
+      <c r="AT464" s="3" t="n"/>
+      <c r="AU464" s="3" t="n"/>
+      <c r="AV464" s="3" t="n"/>
+      <c r="AW464" s="3" t="n"/>
+      <c r="AX464" s="3" t="n"/>
     </row>
     <row r="465">
       <c r="A465" s="3" t="n"/>
@@ -21817,6 +25135,13 @@
       <c r="AO465" s="3" t="n"/>
       <c r="AP465" s="3" t="n"/>
       <c r="AQ465" s="3" t="n"/>
+      <c r="AR465" s="3" t="n"/>
+      <c r="AS465" s="3" t="n"/>
+      <c r="AT465" s="3" t="n"/>
+      <c r="AU465" s="3" t="n"/>
+      <c r="AV465" s="3" t="n"/>
+      <c r="AW465" s="3" t="n"/>
+      <c r="AX465" s="3" t="n"/>
     </row>
     <row r="466">
       <c r="A466" s="3" t="n"/>
@@ -21862,6 +25187,13 @@
       <c r="AO466" s="3" t="n"/>
       <c r="AP466" s="3" t="n"/>
       <c r="AQ466" s="3" t="n"/>
+      <c r="AR466" s="3" t="n"/>
+      <c r="AS466" s="3" t="n"/>
+      <c r="AT466" s="3" t="n"/>
+      <c r="AU466" s="3" t="n"/>
+      <c r="AV466" s="3" t="n"/>
+      <c r="AW466" s="3" t="n"/>
+      <c r="AX466" s="3" t="n"/>
     </row>
     <row r="467">
       <c r="A467" s="3" t="n"/>
@@ -21907,6 +25239,13 @@
       <c r="AO467" s="3" t="n"/>
       <c r="AP467" s="3" t="n"/>
       <c r="AQ467" s="3" t="n"/>
+      <c r="AR467" s="3" t="n"/>
+      <c r="AS467" s="3" t="n"/>
+      <c r="AT467" s="3" t="n"/>
+      <c r="AU467" s="3" t="n"/>
+      <c r="AV467" s="3" t="n"/>
+      <c r="AW467" s="3" t="n"/>
+      <c r="AX467" s="3" t="n"/>
     </row>
     <row r="468">
       <c r="A468" s="3" t="n"/>
@@ -21952,6 +25291,13 @@
       <c r="AO468" s="3" t="n"/>
       <c r="AP468" s="3" t="n"/>
       <c r="AQ468" s="3" t="n"/>
+      <c r="AR468" s="3" t="n"/>
+      <c r="AS468" s="3" t="n"/>
+      <c r="AT468" s="3" t="n"/>
+      <c r="AU468" s="3" t="n"/>
+      <c r="AV468" s="3" t="n"/>
+      <c r="AW468" s="3" t="n"/>
+      <c r="AX468" s="3" t="n"/>
     </row>
     <row r="469">
       <c r="A469" s="3" t="n"/>
@@ -21997,6 +25343,13 @@
       <c r="AO469" s="3" t="n"/>
       <c r="AP469" s="3" t="n"/>
       <c r="AQ469" s="3" t="n"/>
+      <c r="AR469" s="3" t="n"/>
+      <c r="AS469" s="3" t="n"/>
+      <c r="AT469" s="3" t="n"/>
+      <c r="AU469" s="3" t="n"/>
+      <c r="AV469" s="3" t="n"/>
+      <c r="AW469" s="3" t="n"/>
+      <c r="AX469" s="3" t="n"/>
     </row>
     <row r="470">
       <c r="A470" s="3" t="n"/>
@@ -22042,6 +25395,13 @@
       <c r="AO470" s="3" t="n"/>
       <c r="AP470" s="3" t="n"/>
       <c r="AQ470" s="3" t="n"/>
+      <c r="AR470" s="3" t="n"/>
+      <c r="AS470" s="3" t="n"/>
+      <c r="AT470" s="3" t="n"/>
+      <c r="AU470" s="3" t="n"/>
+      <c r="AV470" s="3" t="n"/>
+      <c r="AW470" s="3" t="n"/>
+      <c r="AX470" s="3" t="n"/>
     </row>
     <row r="471">
       <c r="A471" s="3" t="n"/>
@@ -22087,6 +25447,13 @@
       <c r="AO471" s="3" t="n"/>
       <c r="AP471" s="3" t="n"/>
       <c r="AQ471" s="3" t="n"/>
+      <c r="AR471" s="3" t="n"/>
+      <c r="AS471" s="3" t="n"/>
+      <c r="AT471" s="3" t="n"/>
+      <c r="AU471" s="3" t="n"/>
+      <c r="AV471" s="3" t="n"/>
+      <c r="AW471" s="3" t="n"/>
+      <c r="AX471" s="3" t="n"/>
     </row>
     <row r="472">
       <c r="A472" s="3" t="n"/>
@@ -22132,6 +25499,13 @@
       <c r="AO472" s="3" t="n"/>
       <c r="AP472" s="3" t="n"/>
       <c r="AQ472" s="3" t="n"/>
+      <c r="AR472" s="3" t="n"/>
+      <c r="AS472" s="3" t="n"/>
+      <c r="AT472" s="3" t="n"/>
+      <c r="AU472" s="3" t="n"/>
+      <c r="AV472" s="3" t="n"/>
+      <c r="AW472" s="3" t="n"/>
+      <c r="AX472" s="3" t="n"/>
     </row>
     <row r="473">
       <c r="A473" s="3" t="n"/>
@@ -22177,6 +25551,13 @@
       <c r="AO473" s="3" t="n"/>
       <c r="AP473" s="3" t="n"/>
       <c r="AQ473" s="3" t="n"/>
+      <c r="AR473" s="3" t="n"/>
+      <c r="AS473" s="3" t="n"/>
+      <c r="AT473" s="3" t="n"/>
+      <c r="AU473" s="3" t="n"/>
+      <c r="AV473" s="3" t="n"/>
+      <c r="AW473" s="3" t="n"/>
+      <c r="AX473" s="3" t="n"/>
     </row>
     <row r="474">
       <c r="A474" s="3" t="n"/>
@@ -22222,6 +25603,13 @@
       <c r="AO474" s="3" t="n"/>
       <c r="AP474" s="3" t="n"/>
       <c r="AQ474" s="3" t="n"/>
+      <c r="AR474" s="3" t="n"/>
+      <c r="AS474" s="3" t="n"/>
+      <c r="AT474" s="3" t="n"/>
+      <c r="AU474" s="3" t="n"/>
+      <c r="AV474" s="3" t="n"/>
+      <c r="AW474" s="3" t="n"/>
+      <c r="AX474" s="3" t="n"/>
     </row>
     <row r="475">
       <c r="A475" s="3" t="n"/>
@@ -22267,6 +25655,13 @@
       <c r="AO475" s="3" t="n"/>
       <c r="AP475" s="3" t="n"/>
       <c r="AQ475" s="3" t="n"/>
+      <c r="AR475" s="3" t="n"/>
+      <c r="AS475" s="3" t="n"/>
+      <c r="AT475" s="3" t="n"/>
+      <c r="AU475" s="3" t="n"/>
+      <c r="AV475" s="3" t="n"/>
+      <c r="AW475" s="3" t="n"/>
+      <c r="AX475" s="3" t="n"/>
     </row>
     <row r="476">
       <c r="A476" s="3" t="n"/>
@@ -22312,6 +25707,13 @@
       <c r="AO476" s="3" t="n"/>
       <c r="AP476" s="3" t="n"/>
       <c r="AQ476" s="3" t="n"/>
+      <c r="AR476" s="3" t="n"/>
+      <c r="AS476" s="3" t="n"/>
+      <c r="AT476" s="3" t="n"/>
+      <c r="AU476" s="3" t="n"/>
+      <c r="AV476" s="3" t="n"/>
+      <c r="AW476" s="3" t="n"/>
+      <c r="AX476" s="3" t="n"/>
     </row>
     <row r="477">
       <c r="A477" s="3" t="n"/>
@@ -22357,6 +25759,13 @@
       <c r="AO477" s="3" t="n"/>
       <c r="AP477" s="3" t="n"/>
       <c r="AQ477" s="3" t="n"/>
+      <c r="AR477" s="3" t="n"/>
+      <c r="AS477" s="3" t="n"/>
+      <c r="AT477" s="3" t="n"/>
+      <c r="AU477" s="3" t="n"/>
+      <c r="AV477" s="3" t="n"/>
+      <c r="AW477" s="3" t="n"/>
+      <c r="AX477" s="3" t="n"/>
     </row>
     <row r="478">
       <c r="A478" s="3" t="n"/>
@@ -22402,6 +25811,13 @@
       <c r="AO478" s="3" t="n"/>
       <c r="AP478" s="3" t="n"/>
       <c r="AQ478" s="3" t="n"/>
+      <c r="AR478" s="3" t="n"/>
+      <c r="AS478" s="3" t="n"/>
+      <c r="AT478" s="3" t="n"/>
+      <c r="AU478" s="3" t="n"/>
+      <c r="AV478" s="3" t="n"/>
+      <c r="AW478" s="3" t="n"/>
+      <c r="AX478" s="3" t="n"/>
     </row>
     <row r="479">
       <c r="A479" s="3" t="n"/>
@@ -22447,6 +25863,13 @@
       <c r="AO479" s="3" t="n"/>
       <c r="AP479" s="3" t="n"/>
       <c r="AQ479" s="3" t="n"/>
+      <c r="AR479" s="3" t="n"/>
+      <c r="AS479" s="3" t="n"/>
+      <c r="AT479" s="3" t="n"/>
+      <c r="AU479" s="3" t="n"/>
+      <c r="AV479" s="3" t="n"/>
+      <c r="AW479" s="3" t="n"/>
+      <c r="AX479" s="3" t="n"/>
     </row>
     <row r="480">
       <c r="A480" s="3" t="n"/>
@@ -22492,6 +25915,13 @@
       <c r="AO480" s="3" t="n"/>
       <c r="AP480" s="3" t="n"/>
       <c r="AQ480" s="3" t="n"/>
+      <c r="AR480" s="3" t="n"/>
+      <c r="AS480" s="3" t="n"/>
+      <c r="AT480" s="3" t="n"/>
+      <c r="AU480" s="3" t="n"/>
+      <c r="AV480" s="3" t="n"/>
+      <c r="AW480" s="3" t="n"/>
+      <c r="AX480" s="3" t="n"/>
     </row>
     <row r="481">
       <c r="A481" s="3" t="n"/>
@@ -22537,6 +25967,13 @@
       <c r="AO481" s="3" t="n"/>
       <c r="AP481" s="3" t="n"/>
       <c r="AQ481" s="3" t="n"/>
+      <c r="AR481" s="3" t="n"/>
+      <c r="AS481" s="3" t="n"/>
+      <c r="AT481" s="3" t="n"/>
+      <c r="AU481" s="3" t="n"/>
+      <c r="AV481" s="3" t="n"/>
+      <c r="AW481" s="3" t="n"/>
+      <c r="AX481" s="3" t="n"/>
     </row>
     <row r="482">
       <c r="A482" s="3" t="n"/>
@@ -22582,6 +26019,13 @@
       <c r="AO482" s="3" t="n"/>
       <c r="AP482" s="3" t="n"/>
       <c r="AQ482" s="3" t="n"/>
+      <c r="AR482" s="3" t="n"/>
+      <c r="AS482" s="3" t="n"/>
+      <c r="AT482" s="3" t="n"/>
+      <c r="AU482" s="3" t="n"/>
+      <c r="AV482" s="3" t="n"/>
+      <c r="AW482" s="3" t="n"/>
+      <c r="AX482" s="3" t="n"/>
     </row>
     <row r="483">
       <c r="A483" s="3" t="n"/>
@@ -22627,6 +26071,13 @@
       <c r="AO483" s="3" t="n"/>
       <c r="AP483" s="3" t="n"/>
       <c r="AQ483" s="3" t="n"/>
+      <c r="AR483" s="3" t="n"/>
+      <c r="AS483" s="3" t="n"/>
+      <c r="AT483" s="3" t="n"/>
+      <c r="AU483" s="3" t="n"/>
+      <c r="AV483" s="3" t="n"/>
+      <c r="AW483" s="3" t="n"/>
+      <c r="AX483" s="3" t="n"/>
     </row>
     <row r="484">
       <c r="A484" s="3" t="n"/>
@@ -22672,6 +26123,13 @@
       <c r="AO484" s="3" t="n"/>
       <c r="AP484" s="3" t="n"/>
       <c r="AQ484" s="3" t="n"/>
+      <c r="AR484" s="3" t="n"/>
+      <c r="AS484" s="3" t="n"/>
+      <c r="AT484" s="3" t="n"/>
+      <c r="AU484" s="3" t="n"/>
+      <c r="AV484" s="3" t="n"/>
+      <c r="AW484" s="3" t="n"/>
+      <c r="AX484" s="3" t="n"/>
     </row>
     <row r="485">
       <c r="A485" s="3" t="n"/>
@@ -22717,6 +26175,13 @@
       <c r="AO485" s="3" t="n"/>
       <c r="AP485" s="3" t="n"/>
       <c r="AQ485" s="3" t="n"/>
+      <c r="AR485" s="3" t="n"/>
+      <c r="AS485" s="3" t="n"/>
+      <c r="AT485" s="3" t="n"/>
+      <c r="AU485" s="3" t="n"/>
+      <c r="AV485" s="3" t="n"/>
+      <c r="AW485" s="3" t="n"/>
+      <c r="AX485" s="3" t="n"/>
     </row>
     <row r="486">
       <c r="A486" s="3" t="n"/>
@@ -22762,6 +26227,13 @@
       <c r="AO486" s="3" t="n"/>
       <c r="AP486" s="3" t="n"/>
       <c r="AQ486" s="3" t="n"/>
+      <c r="AR486" s="3" t="n"/>
+      <c r="AS486" s="3" t="n"/>
+      <c r="AT486" s="3" t="n"/>
+      <c r="AU486" s="3" t="n"/>
+      <c r="AV486" s="3" t="n"/>
+      <c r="AW486" s="3" t="n"/>
+      <c r="AX486" s="3" t="n"/>
     </row>
     <row r="487">
       <c r="A487" s="3" t="n"/>
@@ -22807,6 +26279,13 @@
       <c r="AO487" s="3" t="n"/>
       <c r="AP487" s="3" t="n"/>
       <c r="AQ487" s="3" t="n"/>
+      <c r="AR487" s="3" t="n"/>
+      <c r="AS487" s="3" t="n"/>
+      <c r="AT487" s="3" t="n"/>
+      <c r="AU487" s="3" t="n"/>
+      <c r="AV487" s="3" t="n"/>
+      <c r="AW487" s="3" t="n"/>
+      <c r="AX487" s="3" t="n"/>
     </row>
     <row r="488">
       <c r="A488" s="3" t="n"/>
@@ -22852,6 +26331,13 @@
       <c r="AO488" s="3" t="n"/>
       <c r="AP488" s="3" t="n"/>
       <c r="AQ488" s="3" t="n"/>
+      <c r="AR488" s="3" t="n"/>
+      <c r="AS488" s="3" t="n"/>
+      <c r="AT488" s="3" t="n"/>
+      <c r="AU488" s="3" t="n"/>
+      <c r="AV488" s="3" t="n"/>
+      <c r="AW488" s="3" t="n"/>
+      <c r="AX488" s="3" t="n"/>
     </row>
     <row r="489">
       <c r="A489" s="3" t="n"/>
@@ -22897,6 +26383,13 @@
       <c r="AO489" s="3" t="n"/>
       <c r="AP489" s="3" t="n"/>
       <c r="AQ489" s="3" t="n"/>
+      <c r="AR489" s="3" t="n"/>
+      <c r="AS489" s="3" t="n"/>
+      <c r="AT489" s="3" t="n"/>
+      <c r="AU489" s="3" t="n"/>
+      <c r="AV489" s="3" t="n"/>
+      <c r="AW489" s="3" t="n"/>
+      <c r="AX489" s="3" t="n"/>
     </row>
     <row r="490">
       <c r="A490" s="3" t="n"/>
@@ -22942,6 +26435,13 @@
       <c r="AO490" s="3" t="n"/>
       <c r="AP490" s="3" t="n"/>
       <c r="AQ490" s="3" t="n"/>
+      <c r="AR490" s="3" t="n"/>
+      <c r="AS490" s="3" t="n"/>
+      <c r="AT490" s="3" t="n"/>
+      <c r="AU490" s="3" t="n"/>
+      <c r="AV490" s="3" t="n"/>
+      <c r="AW490" s="3" t="n"/>
+      <c r="AX490" s="3" t="n"/>
     </row>
     <row r="491">
       <c r="A491" s="3" t="n"/>
@@ -22987,6 +26487,13 @@
       <c r="AO491" s="3" t="n"/>
       <c r="AP491" s="3" t="n"/>
       <c r="AQ491" s="3" t="n"/>
+      <c r="AR491" s="3" t="n"/>
+      <c r="AS491" s="3" t="n"/>
+      <c r="AT491" s="3" t="n"/>
+      <c r="AU491" s="3" t="n"/>
+      <c r="AV491" s="3" t="n"/>
+      <c r="AW491" s="3" t="n"/>
+      <c r="AX491" s="3" t="n"/>
     </row>
     <row r="492">
       <c r="A492" s="3" t="n"/>
@@ -23032,6 +26539,13 @@
       <c r="AO492" s="3" t="n"/>
       <c r="AP492" s="3" t="n"/>
       <c r="AQ492" s="3" t="n"/>
+      <c r="AR492" s="3" t="n"/>
+      <c r="AS492" s="3" t="n"/>
+      <c r="AT492" s="3" t="n"/>
+      <c r="AU492" s="3" t="n"/>
+      <c r="AV492" s="3" t="n"/>
+      <c r="AW492" s="3" t="n"/>
+      <c r="AX492" s="3" t="n"/>
     </row>
     <row r="493">
       <c r="A493" s="3" t="n"/>
@@ -23077,6 +26591,13 @@
       <c r="AO493" s="3" t="n"/>
       <c r="AP493" s="3" t="n"/>
       <c r="AQ493" s="3" t="n"/>
+      <c r="AR493" s="3" t="n"/>
+      <c r="AS493" s="3" t="n"/>
+      <c r="AT493" s="3" t="n"/>
+      <c r="AU493" s="3" t="n"/>
+      <c r="AV493" s="3" t="n"/>
+      <c r="AW493" s="3" t="n"/>
+      <c r="AX493" s="3" t="n"/>
     </row>
     <row r="494">
       <c r="A494" s="3" t="n"/>
@@ -23122,6 +26643,13 @@
       <c r="AO494" s="3" t="n"/>
       <c r="AP494" s="3" t="n"/>
       <c r="AQ494" s="3" t="n"/>
+      <c r="AR494" s="3" t="n"/>
+      <c r="AS494" s="3" t="n"/>
+      <c r="AT494" s="3" t="n"/>
+      <c r="AU494" s="3" t="n"/>
+      <c r="AV494" s="3" t="n"/>
+      <c r="AW494" s="3" t="n"/>
+      <c r="AX494" s="3" t="n"/>
     </row>
     <row r="495">
       <c r="A495" s="3" t="n"/>
@@ -23167,6 +26695,13 @@
       <c r="AO495" s="3" t="n"/>
       <c r="AP495" s="3" t="n"/>
       <c r="AQ495" s="3" t="n"/>
+      <c r="AR495" s="3" t="n"/>
+      <c r="AS495" s="3" t="n"/>
+      <c r="AT495" s="3" t="n"/>
+      <c r="AU495" s="3" t="n"/>
+      <c r="AV495" s="3" t="n"/>
+      <c r="AW495" s="3" t="n"/>
+      <c r="AX495" s="3" t="n"/>
     </row>
     <row r="496">
       <c r="A496" s="3" t="n"/>
@@ -23212,6 +26747,13 @@
       <c r="AO496" s="3" t="n"/>
       <c r="AP496" s="3" t="n"/>
       <c r="AQ496" s="3" t="n"/>
+      <c r="AR496" s="3" t="n"/>
+      <c r="AS496" s="3" t="n"/>
+      <c r="AT496" s="3" t="n"/>
+      <c r="AU496" s="3" t="n"/>
+      <c r="AV496" s="3" t="n"/>
+      <c r="AW496" s="3" t="n"/>
+      <c r="AX496" s="3" t="n"/>
     </row>
     <row r="497">
       <c r="A497" s="3" t="n"/>
@@ -23257,6 +26799,13 @@
       <c r="AO497" s="3" t="n"/>
       <c r="AP497" s="3" t="n"/>
       <c r="AQ497" s="3" t="n"/>
+      <c r="AR497" s="3" t="n"/>
+      <c r="AS497" s="3" t="n"/>
+      <c r="AT497" s="3" t="n"/>
+      <c r="AU497" s="3" t="n"/>
+      <c r="AV497" s="3" t="n"/>
+      <c r="AW497" s="3" t="n"/>
+      <c r="AX497" s="3" t="n"/>
     </row>
     <row r="498">
       <c r="A498" s="3" t="n"/>
@@ -23302,6 +26851,13 @@
       <c r="AO498" s="3" t="n"/>
       <c r="AP498" s="3" t="n"/>
       <c r="AQ498" s="3" t="n"/>
+      <c r="AR498" s="3" t="n"/>
+      <c r="AS498" s="3" t="n"/>
+      <c r="AT498" s="3" t="n"/>
+      <c r="AU498" s="3" t="n"/>
+      <c r="AV498" s="3" t="n"/>
+      <c r="AW498" s="3" t="n"/>
+      <c r="AX498" s="3" t="n"/>
     </row>
     <row r="499">
       <c r="A499" s="3" t="n"/>
@@ -23347,6 +26903,13 @@
       <c r="AO499" s="3" t="n"/>
       <c r="AP499" s="3" t="n"/>
       <c r="AQ499" s="3" t="n"/>
+      <c r="AR499" s="3" t="n"/>
+      <c r="AS499" s="3" t="n"/>
+      <c r="AT499" s="3" t="n"/>
+      <c r="AU499" s="3" t="n"/>
+      <c r="AV499" s="3" t="n"/>
+      <c r="AW499" s="3" t="n"/>
+      <c r="AX499" s="3" t="n"/>
     </row>
     <row r="500">
       <c r="A500" s="3" t="n"/>
@@ -23392,6 +26955,13 @@
       <c r="AO500" s="3" t="n"/>
       <c r="AP500" s="3" t="n"/>
       <c r="AQ500" s="3" t="n"/>
+      <c r="AR500" s="3" t="n"/>
+      <c r="AS500" s="3" t="n"/>
+      <c r="AT500" s="3" t="n"/>
+      <c r="AU500" s="3" t="n"/>
+      <c r="AV500" s="3" t="n"/>
+      <c r="AW500" s="3" t="n"/>
+      <c r="AX500" s="3" t="n"/>
     </row>
     <row r="501">
       <c r="A501" s="3" t="n"/>
@@ -23437,17 +27007,24 @@
       <c r="AO501" s="3" t="n"/>
       <c r="AP501" s="3" t="n"/>
       <c r="AQ501" s="3" t="n"/>
+      <c r="AR501" s="3" t="n"/>
+      <c r="AS501" s="3" t="n"/>
+      <c r="AT501" s="3" t="n"/>
+      <c r="AU501" s="3" t="n"/>
+      <c r="AV501" s="3" t="n"/>
+      <c r="AW501" s="3" t="n"/>
+      <c r="AX501" s="3" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ501"/>
+  <autoFilter ref="A1:AX501"/>
   <dataValidations count="3">
     <dataValidation sqref="D2:D501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Choose a listed value" error="Use the dropdown choices." type="list">
       <formula1>"Full Case Management,One-Time RN Visit - Provider,Vocational"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Choose a listed value" error="Use the dropdown choices." type="list">
+    <dataValidation sqref="M2:M501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Choose a listed value" error="Use the dropdown choices." type="list">
       <formula1>"Male,Female,Unknown"</formula1>
     </dataValidation>
-    <dataValidation sqref="AH2:AH501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Choose a listed value" error="Use the dropdown choices." type="list">
+    <dataValidation sqref="AO2:AO501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Choose a listed value" error="Use the dropdown choices." type="list">
       <formula1>"Adjuster,Customer TCM"</formula1>
     </dataValidation>
   </dataValidations>
